--- a/output/test_cases/MART_SmartSearch_Combined_TestCases_v3.0_20260818_VI.xlsx
+++ b/output/test_cases/MART_SmartSearch_Combined_TestCases_v3.0_20260818_VI.xlsx
@@ -96,7 +96,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -127,6 +127,12 @@
         <bgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+        <bgColor rgb="FFFCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -155,7 +161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -196,6 +202,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -804,7 +813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P70"/>
+  <dimension ref="A1:P85"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2831,7 +2840,7 @@
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>QnA-04</t>
+          <t>QnA-35</t>
         </is>
       </c>
       <c r="M33" s="10" t="n"/>
@@ -2839,7 +2848,7 @@
       <c r="O33" s="10" t="n"/>
       <c r="P33" s="11" t="inlineStr">
         <is>
-          <t>OPEN — QnA-04: xem chi tiết trong file QnA log.</t>
+          <t>OPEN — QnA-35: xem chi tiết trong file QnA log.</t>
         </is>
       </c>
     </row>
@@ -5142,6 +5151,954 @@
       <c r="N70" s="10" t="n"/>
       <c r="O70" s="10" t="n"/>
       <c r="P70" s="9" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC7</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-005</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>E. Search Results — Grid</t>
+        </is>
+      </c>
+      <c r="E71" s="9" t="inlineStr">
+        <is>
+          <t>FR-PR-06</t>
+        </is>
+      </c>
+      <c r="F71" s="9" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="G71" s="9" t="inlineStr">
+        <is>
+          <t>Kiểm tra tiêu chí sắp xếp mặc định khi vào trang kết quả lần đầu (chưa từng đổi Sort).</t>
+        </is>
+      </c>
+      <c r="H71" s="9" t="inlineStr">
+        <is>
+          <t>"sữa" (lần đầu tìm kiếm trong phiên)</t>
+        </is>
+      </c>
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>Khách chưa từng chọn tiêu chí Sắp xếp nào trong phiên/thiết bị hiện tại.</t>
+        </is>
+      </c>
+      <c r="J71" s="9" t="inlineStr">
+        <is>
+          <t>Trang kết quả mặc định áp dụng "Liên quan nhất" (AI Scorecard Ranking); nhãn trên thanh sticky Sort hiển thị đúng "Liên quan nhất" ngay từ lần tải đầu tiên, không cần khách thao tác chọn.</t>
+        </is>
+      </c>
+      <c r="K71" s="9" t="inlineStr">
+        <is>
+          <t>Sort mặc định luôn là "Liên quan nhất" theo FR-PR-06, khớp với trạng thái ban đầu mô tả ở SS-SCR-008-SC2.</t>
+        </is>
+      </c>
+      <c r="L71" s="9" t="n"/>
+      <c r="M71" s="10" t="n"/>
+      <c r="N71" s="10" t="n"/>
+      <c r="O71" s="10" t="n"/>
+      <c r="P71" s="9" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC8</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-005</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>E. Search Results — Grid</t>
+        </is>
+      </c>
+      <c r="E72" s="9" t="inlineStr">
+        <is>
+          <t>FR-SF-04</t>
+        </is>
+      </c>
+      <c r="F72" s="9" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="G72" s="9" t="inlineStr">
+        <is>
+          <t>Kiểm tra trạng thái mặc định của nút "Bộ lọc" khi chưa áp dụng điều kiện lọc nào.</t>
+        </is>
+      </c>
+      <c r="H72" s="9" t="inlineStr">
+        <is>
+          <t>"sữa" (chưa áp dụng filter nào)</t>
+        </is>
+      </c>
+      <c r="I72" s="9" t="inlineStr">
+        <is>
+          <t>Trang kết quả vừa tải, khách chưa mở/áp dụng Bộ lọc chi tiết lần nào.</t>
+        </is>
+      </c>
+      <c r="J72" s="9" t="inlineStr">
+        <is>
+          <t>Nút "Bộ lọc" hiển thị trạng thái mặc định không có badge số lượng (hoặc badge=0 bị ẩn); không có filter chip nào đang active trên trang kết quả; tổng số kết quả là tập đầy đủ chưa lọc.</t>
+        </is>
+      </c>
+      <c r="K72" s="9" t="inlineStr">
+        <is>
+          <t>Badge chỉ xuất hiện khi có ≥1 điều kiện lọc đang áp dụng — nhất quán với hành vi mô tả ở SS-SCR-010-SC3 (badge=0 quay về mặc định).</t>
+        </is>
+      </c>
+      <c r="L72" s="9" t="n"/>
+      <c r="M72" s="10" t="n"/>
+      <c r="N72" s="10" t="n"/>
+      <c r="O72" s="10" t="n"/>
+      <c r="P72" s="9" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="9" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC9</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-005</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>E. Search Results — Grid</t>
+        </is>
+      </c>
+      <c r="E73" s="9" t="inlineStr">
+        <is>
+          <t>FR-SF-01, FR-SF-02, FR-SF-03</t>
+        </is>
+      </c>
+      <c r="F73" s="9" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="G73" s="9" t="inlineStr">
+        <is>
+          <t>Tương tác trực tiếp với Smart Filter Chips ngay trên trang kết quả (không mở bảng Bộ lọc chi tiết).</t>
+        </is>
+      </c>
+      <c r="H73" s="9" t="inlineStr">
+        <is>
+          <t>Tap 1 chip (VD "Hữu cơ") rồi tap thêm 1 chip khác (VD "Không đường")</t>
+        </is>
+      </c>
+      <c r="I73" s="9" t="inlineStr">
+        <is>
+          <t>Trang kết quả đã tải, khối Smart Filter Chips hiển thị theo từ khoá hiện tại (tối đa 10 chip, cấu trúc phẳng — không gom nhóm).</t>
+        </is>
+      </c>
+      <c r="J73" s="9" t="inlineStr">
+        <is>
+          <t>Tap 1 chip áp dụng lọc ngay lập tức (không cần nút "Áp dụng" riêng), chip chuyển trạng thái active, kết quả cập nhật realtime, badge nút "Bộ lọc" tăng tương ứng; tap thêm chip thứ 2 áp dụng lọc kết hợp (AND) cả 2 điều kiện; mọi chip hiển thị luôn đảm bảo trả về ≥1 sản phẩm theo đúng FR-SF-01→03.</t>
+        </is>
+      </c>
+      <c r="K73" s="9" t="inlineStr">
+        <is>
+          <t>Không có chip nào hiển thị mà khi tap vào lại cho 0 kết quả; badge đồng bộ giữa Smart Filter Chips và nút Bộ lọc chi tiết (SS-SCR-009) vì cùng 1 trạng thái lọc.</t>
+        </is>
+      </c>
+      <c r="L73" s="9" t="n"/>
+      <c r="M73" s="10" t="n"/>
+      <c r="N73" s="10" t="n"/>
+      <c r="O73" s="10" t="n"/>
+      <c r="P73" s="9" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-006-SC4</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-006</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="inlineStr">
+        <is>
+          <t>F. Search Results — List</t>
+        </is>
+      </c>
+      <c r="E74" s="9" t="inlineStr">
+        <is>
+          <t>FR-PR-01, FR-PR-07</t>
+        </is>
+      </c>
+      <c r="F74" s="9" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G74" s="9" t="inlineStr">
+        <is>
+          <t>Tap vào Product Card (ngoài vùng nút +) ở chế độ Danh sách để mở PDP.</t>
+        </is>
+      </c>
+      <c r="H74" s="9" t="inlineStr">
+        <is>
+          <t>1 dòng sản phẩm bất kỳ trong chế độ List</t>
+        </is>
+      </c>
+      <c r="I74" s="9" t="inlineStr">
+        <is>
+          <t>Chế độ xem = List, trang kết quả đã tải.</t>
+        </is>
+      </c>
+      <c r="J74" s="9" t="inlineStr">
+        <is>
+          <t>Tap vào vùng ảnh/tên/giá của dòng sản phẩm (ngoài nút +) mở đúng PDP của sản phẩm đó, giống hành vi tương ứng đã có ở chế độ Grid (SS-SCR-005-SC3-TC1); không kích hoạt add-to-cart nhầm.</t>
+        </is>
+      </c>
+      <c r="K74" s="9" t="inlineStr">
+        <is>
+          <t>Hành vi mở PDP nhất quán giữa 2 chế độ xem Grid và List.</t>
+        </is>
+      </c>
+      <c r="L74" s="9" t="n"/>
+      <c r="M74" s="10" t="n"/>
+      <c r="N74" s="10" t="n"/>
+      <c r="O74" s="10" t="n"/>
+      <c r="P74" s="9" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="18" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-006-SC5</t>
+        </is>
+      </c>
+      <c r="C75" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-006</t>
+        </is>
+      </c>
+      <c r="D75" s="18" t="inlineStr">
+        <is>
+          <t>F. Search Results — List</t>
+        </is>
+      </c>
+      <c r="E75" s="18" t="inlineStr">
+        <is>
+          <t>Không có FR ID rõ ràng trong BRD — xem QnA-10</t>
+        </is>
+      </c>
+      <c r="F75" s="18" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G75" s="18" t="inlineStr">
+        <is>
+          <t>Tap nút (+) thêm nhanh vào giỏ ngay tại dòng sản phẩm ở chế độ Danh sách.</t>
+        </is>
+      </c>
+      <c r="H75" s="18" t="inlineStr">
+        <is>
+          <t>Tap (+) trên 1 dòng sản phẩm còn hàng trong chế độ List</t>
+        </is>
+      </c>
+      <c r="I75" s="18" t="inlineStr">
+        <is>
+          <t>Chế độ xem = List, trang kết quả đã tải.</t>
+        </is>
+      </c>
+      <c r="J75" s="18" t="inlineStr">
+        <is>
+          <t>Badge giỏ hàng tăng ngay (optimistic update); Toast xác nhận hiện ở đáy màn hình giống hành vi ở chế độ Grid (SS-SCR-011); không rời trang kết quả, không mở nhầm PDP.</t>
+        </is>
+      </c>
+      <c r="K75" s="18" t="inlineStr">
+        <is>
+          <t>Hành vi add-to-cart nhất quán giữa 2 chế độ xem Grid và List; vùng chạm nút (+) và vùng chạm mở PDP không chồng lấn trong layout dòng ngang của List.</t>
+        </is>
+      </c>
+      <c r="L75" s="18" t="inlineStr">
+        <is>
+          <t>QnA-10</t>
+        </is>
+      </c>
+      <c r="M75" s="10" t="n"/>
+      <c r="N75" s="10" t="n"/>
+      <c r="O75" s="10" t="n"/>
+      <c r="P75" s="18" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-10: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="18" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC6</t>
+        </is>
+      </c>
+      <c r="C76" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-009</t>
+        </is>
+      </c>
+      <c r="D76" s="18" t="inlineStr">
+        <is>
+          <t>H. Smart Filter / Detailed Filter</t>
+        </is>
+      </c>
+      <c r="E76" s="18" t="inlineStr">
+        <is>
+          <t>FR-SF-01, FR-SF-04</t>
+        </is>
+      </c>
+      <c r="F76" s="18" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="G76" s="18" t="inlineStr">
+        <is>
+          <t>Kiểm tra cơ chế đếm số lượng điều kiện đang chọn — badge riêng theo từng tab bên trong Bộ lọc, và badge tổng trên nút "Bộ lọc" ở trang kết quả.</t>
+        </is>
+      </c>
+      <c r="H76" s="18" t="inlineStr">
+        <is>
+          <t>Chọn 1 Danh mục + 3 chip Nhãn + 1 mức Đánh giá + 1 điều kiện Giao hàng + 1 khoảng Giá</t>
+        </is>
+      </c>
+      <c r="I76" s="18" t="inlineStr">
+        <is>
+          <t>Trang kết quả đã tải; chưa áp dụng điều kiện lọc nào.</t>
+        </is>
+      </c>
+      <c r="J76" s="18" t="inlineStr">
+        <is>
+          <t>Theo ảnh Figma thực tế (Text Search.png): mỗi tab bên trái (Danh mục/Nhãn/Giao hàng/Đánh giá/Giá) hiển thị badge số riêng = số điều kiện ĐANG CHỌN TRONG TAB ĐÓ (VD Nhãn chọn 3 chip → badge tab Nhãn = "3"); nút "Áp dụng" ở đáy sheet KHÔNG có số "(n)" kèm theo (chỉ ghi "Áp dụng" trơn). TBD: nút "Bộ lọc" trên trang kết quả (bên ngoài sheet) có badge tổng hay không — xem QnA-39.</t>
+        </is>
+      </c>
+      <c r="K76" s="18" t="inlineStr">
+        <is>
+          <t>Badge từng tab phải khớp chính xác số điều kiện đang active trong tab đó tại mọi thời điểm (kể cả trước khi tap Áp dụng).</t>
+        </is>
+      </c>
+      <c r="L76" s="18" t="inlineStr">
+        <is>
+          <t>QnA-39</t>
+        </is>
+      </c>
+      <c r="M76" s="10" t="n"/>
+      <c r="N76" s="10" t="n"/>
+      <c r="O76" s="10" t="n"/>
+      <c r="P76" s="18" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-39: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC7</t>
+        </is>
+      </c>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-009</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="inlineStr">
+        <is>
+          <t>H. Smart Filter / Detailed Filter</t>
+        </is>
+      </c>
+      <c r="E77" s="9" t="inlineStr">
+        <is>
+          <t>FR-SF-01, FR-SF-04</t>
+        </is>
+      </c>
+      <c r="F77" s="9" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G77" s="9" t="inlineStr">
+        <is>
+          <t>Kiểm tra hành vi chi tiết của nút "Thiết lập lại" (Reset) và nút "Áp dụng" ở thanh hành động cố định đáy sheet.</t>
+        </is>
+      </c>
+      <c r="H77" s="9" t="inlineStr">
+        <is>
+          <t>Tap "Thiết lập lại" sau khi đã chọn nhiều điều kiện; tap "Áp dụng" ở các trạng thái khác nhau</t>
+        </is>
+      </c>
+      <c r="I77" s="9" t="inlineStr">
+        <is>
+          <t>Bảng Bộ lọc đang mở với thanh hành động cố định "Thiết lập lại"/"Áp dụng" hiển thị (theo ảnh Figma thực tế, xem QnA-18).</t>
+        </is>
+      </c>
+      <c r="J77" s="9" t="inlineStr">
+        <is>
+          <t>"Thiết lập lại" xoá toàn bộ lựa chọn đang có TRONG SHEET (chưa áp dụng) về trạng thái trống, nhưng sheet vẫn mở (không tự đóng); "Áp dụng" luôn đóng sheet và chạy lại truy vấn theo đúng trạng thái hiện tại của sheet tại thời điểm tap, kể cả khi trạng thái đó là rỗng (0 điều kiện) hoặc không đổi so với trước.</t>
+        </is>
+      </c>
+      <c r="K77" s="9" t="inlineStr">
+        <is>
+          <t>Hai nút hoạt động độc lập, không gây nhầm lẫn với nút (✕) đóng sheet (không áp dụng, khôi phục trạng thái cũ) đã test ở SC5.</t>
+        </is>
+      </c>
+      <c r="L77" s="9" t="n"/>
+      <c r="M77" s="10" t="n"/>
+      <c r="N77" s="10" t="n"/>
+      <c r="O77" s="10" t="n"/>
+      <c r="P77" s="9" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="9" t="n">
+        <v>78</v>
+      </c>
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC8</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-009</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="inlineStr">
+        <is>
+          <t>H. Smart Filter / Detailed Filter</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
+          <t>FR-SF-04</t>
+        </is>
+      </c>
+      <c r="F78" s="9" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G78" s="9" t="inlineStr">
+        <is>
+          <t>Chuyển đổi qua lại giữa các tab nhóm điều kiện (Danh mục/Nhãn/Giao hàng/Đánh giá/Giá) trong bảng Bộ lọc.</t>
+        </is>
+      </c>
+      <c r="H78" s="9" t="inlineStr">
+        <is>
+          <t>Tap lần lượt từng tab bên trái; chọn điều kiện ở 1 tab rồi chuyển sang tab khác và quay lại</t>
+        </is>
+      </c>
+      <c r="I78" s="9" t="inlineStr">
+        <is>
+          <t>Bảng Bộ lọc đang mở, tab "Danh mục" đang active mặc định.</t>
+        </is>
+      </c>
+      <c r="J78" s="9" t="inlineStr">
+        <is>
+          <t>Tap 1 tab bất kỳ chuyển ngay nội dung panel bên phải sang đúng nhóm điều kiện của tab đó; tab vừa tap được đánh dấu active (viền trái đỏ + chữ đậm màu đỏ, theo đúng ảnh Figma thực tế); các tab khác trở về trạng thái không active; lựa chọn đã chọn ở các tab khác (nếu có) không bị mất khi chuyển tab qua lại, badge riêng của từng tab vẫn giữ nguyên.</t>
+        </is>
+      </c>
+      <c r="K78" s="9" t="inlineStr">
+        <is>
+          <t>Chuyển tab không làm mất lựa chọn đã chọn ở tab khác; đúng 1 tab active tại một thời điểm; nội dung panel phải khớp đúng tab đang active.</t>
+        </is>
+      </c>
+      <c r="L78" s="9" t="n"/>
+      <c r="M78" s="10" t="n"/>
+      <c r="N78" s="10" t="n"/>
+      <c r="O78" s="10" t="n"/>
+      <c r="P78" s="9" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="18" t="n">
+        <v>79</v>
+      </c>
+      <c r="B79" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC9</t>
+        </is>
+      </c>
+      <c r="C79" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-009</t>
+        </is>
+      </c>
+      <c r="D79" s="18" t="inlineStr">
+        <is>
+          <t>H. Smart Filter / Detailed Filter</t>
+        </is>
+      </c>
+      <c r="E79" s="18" t="inlineStr">
+        <is>
+          <t>FR-SF-04</t>
+        </is>
+      </c>
+      <c r="F79" s="18" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="G79" s="18" t="inlineStr">
+        <is>
+          <t>Chọn điều kiện Giao hàng trong tab "Giao hàng".</t>
+        </is>
+      </c>
+      <c r="H79" s="18" t="inlineStr">
+        <is>
+          <t>Chọn "Giao hàng tiêu chuẩn"</t>
+        </is>
+      </c>
+      <c r="I79" s="18" t="inlineStr">
+        <is>
+          <t>Trang kết quả đã tải; chưa áp dụng điều kiện Giao hàng nào.</t>
+        </is>
+      </c>
+      <c r="J79" s="18" t="inlineStr">
+        <is>
+          <t>Storyboard bản cập nhật (v0.1-20260819) xác nhận tab Giao hàng chỉ có ĐÚNG 1 checkbox "Giao hàng tiêu chuẩn" (bật/tắt đơn giản), không có loại hình giao hàng nào khác ở v1. Chọn checkbox áp dụng lọc chỉ hiển thị SKU đủ điều kiện giao hàng tiêu chuẩn; bỏ chọn quay về không lọc theo điều kiện này. Xem QnA-42 (đã Resolved).</t>
+        </is>
+      </c>
+      <c r="K79" s="18" t="inlineStr">
+        <is>
+          <t>Chọn/bỏ chọn điều kiện Giao hàng cập nhật đúng badge tab Giao hàng và kết quả lọc tương ứng.</t>
+        </is>
+      </c>
+      <c r="L79" s="18" t="inlineStr">
+        <is>
+          <t>QnA-42</t>
+        </is>
+      </c>
+      <c r="M79" s="10" t="n"/>
+      <c r="N79" s="10" t="n"/>
+      <c r="O79" s="10" t="n"/>
+      <c r="P79" s="18" t="inlineStr">
+        <is>
+          <t>RESOLVED — QnA-42: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC10</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-009</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>H. Smart Filter / Detailed Filter</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>FR-SF-04</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="G80" s="9" t="inlineStr">
+        <is>
+          <t>Chọn mức Đánh giá (Rating) trong tab "Đánh giá" — 5 mức, độc quyền chỉ chọn 1.</t>
+        </is>
+      </c>
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>Chọn lần lượt "5 sao", "Từ 4 sao trở lên", ...</t>
+        </is>
+      </c>
+      <c r="I80" s="9" t="inlineStr">
+        <is>
+          <t>Trang kết quả đã tải; chưa áp dụng điều kiện Đánh giá nào.</t>
+        </is>
+      </c>
+      <c r="J80" s="9" t="inlineStr">
+        <is>
+          <t>Tab hiển thị đúng 5 mức theo BRD (5 sao / Từ 4 sao trở lên / Từ 3 sao trở lên / Từ 2 sao trở lên / Từ 1 sao trở lên); chỉ chọn được 1 mức tại một thời điểm (độc quyền, giống Danh mục); chọn "Từ N sao trở lên" trả về SKU có rating &gt;= N (bao gồm cả N và cao hơn, không phải chỉ đúng bằng N).</t>
+        </is>
+      </c>
+      <c r="K80" s="9" t="inlineStr">
+        <is>
+          <t>Đổi mức Đánh giá tự động bỏ chọn mức cũ; kết quả trả về đúng ngưỡng &gt;= N sao cho từng mức.</t>
+        </is>
+      </c>
+      <c r="L80" s="9" t="n"/>
+      <c r="M80" s="10" t="n"/>
+      <c r="N80" s="10" t="n"/>
+      <c r="O80" s="10" t="n"/>
+      <c r="P80" s="9" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="18" t="n">
+        <v>50</v>
+      </c>
+      <c r="B81" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-012-SC4</t>
+        </is>
+      </c>
+      <c r="C81" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-012</t>
+        </is>
+      </c>
+      <c r="D81" s="18" t="inlineStr">
+        <is>
+          <t>K. Zero-Result Recovery</t>
+        </is>
+      </c>
+      <c r="E81" s="18" t="inlineStr">
+        <is>
+          <t>FR-ZR-01, FR-ZR-02, FR-SM-07, FR-PR-01 -&gt; FR-PR-05 (Out-of-stock override)</t>
+        </is>
+      </c>
+      <c r="F81" s="18" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="G81" s="18" t="inlineStr">
+        <is>
+          <t>Kiểm tra ranh giới kích hoạt Zero Result Page khi từ khoá khớp chính xác 1/nhiều SKU nhưng đang hết hàng.</t>
+        </is>
+      </c>
+      <c r="H81" s="18" t="inlineStr">
+        <is>
+          <t>Từ khoá khớp chính xác SKU hết hàng (còn SKU khác còn hàng) / Từ khoá mà TẤT CẢ SKU khớp đều hết hàng</t>
+        </is>
+      </c>
+      <c r="I81" s="18" t="inlineStr">
+        <is>
+          <t>Catalogue có SKU khớp trực tiếp từ khoá nhưng ở trạng thái hết hàng (stock=0).</t>
+        </is>
+      </c>
+      <c r="J81" s="18" t="inlineStr">
+        <is>
+          <t>Trường hợp còn SKU khác khớp còn hàng: hệ thống ở lại SS-SCR-005 bình thường, SKU hết hàng bị đẩy xuống đáy danh sách theo quy tắc Out-of-stock override (FR-PR-01→05), Zero Result Page KHÔNG được kích hoạt. Trường hợp TẤT CẢ SKU khớp đều hết hàng: TBD — xem QnA-44.</t>
+        </is>
+      </c>
+      <c r="K81" s="18" t="inlineStr">
+        <is>
+          <t>Khối "Có thể bạn sẽ thích" (đặc trưng riêng của SS-SCR-012) chỉ được xuất hiện khi thực sự rơi vào luồng Zero Result, không xuất hiện lẫn trên SS-SCR-005 khi vẫn còn SKU khớp trực tiếp (dù hết hàng).</t>
+        </is>
+      </c>
+      <c r="L81" s="18" t="inlineStr">
+        <is>
+          <t>QnA-44</t>
+        </is>
+      </c>
+      <c r="M81" s="10" t="n"/>
+      <c r="N81" s="10" t="n"/>
+      <c r="O81" s="10" t="n"/>
+      <c r="P81" s="18" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-44: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="18" t="n">
+        <v>51</v>
+      </c>
+      <c r="B82" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-010-SC4</t>
+        </is>
+      </c>
+      <c r="C82" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-010</t>
+        </is>
+      </c>
+      <c r="D82" s="18" t="inlineStr">
+        <is>
+          <t>I. Filter Applied State</t>
+        </is>
+      </c>
+      <c r="E82" s="18" t="inlineStr">
+        <is>
+          <t>FR-SF-03</t>
+        </is>
+      </c>
+      <c r="F82" s="18" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G82" s="18" t="inlineStr">
+        <is>
+          <t>Kiểm tra bộ lọc tự động xoá khi khách tìm kiếm một từ khoá mới (không phải sửa từ khoá cũ, mà tìm hẳn từ khoá khác).</t>
+        </is>
+      </c>
+      <c r="H82" s="18" t="inlineStr">
+        <is>
+          <t>Đang lọc "Không đường" cho từ khoá "sữa" → tìm từ khoá mới "bia"</t>
+        </is>
+      </c>
+      <c r="I82" s="18" t="inlineStr">
+        <is>
+          <t>Trang kết quả "sữa" đang áp dụng ≥1 điều kiện lọc.</t>
+        </is>
+      </c>
+      <c r="J82" s="18" t="inlineStr">
+        <is>
+          <t>Theo storyboard bản cập nhật (v0.1-20260819, SS-SCR-010): khi khách tìm một từ khoá MỚI (khác hẳn), bộ lọc đang áp dụng cho từ khoá cũ TỰ ĐỘNG XOÁ, không mang theo sang kết quả của từ khoá mới. Badge nút Bộ lọc về 0/ẩn cho từ khoá mới.</t>
+        </is>
+      </c>
+      <c r="K82" s="18" t="inlineStr">
+        <is>
+          <t>Đổi từ khoá luôn khởi động lại trạng thái lọc từ đầu (badge=0); không có filter chip nào của từ khoá cũ còn sót lại trên kết quả từ khoá mới.</t>
+        </is>
+      </c>
+      <c r="L82" s="18" t="inlineStr">
+        <is>
+          <t>QnA-06</t>
+        </is>
+      </c>
+      <c r="M82" s="10" t="n"/>
+      <c r="N82" s="10" t="n"/>
+      <c r="O82" s="10" t="n"/>
+      <c r="P82" s="18" t="inlineStr">
+        <is>
+          <t>RESOLVED — QnA-06: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="18" t="n">
+        <v>56</v>
+      </c>
+      <c r="B83" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-014-SC4</t>
+        </is>
+      </c>
+      <c r="C83" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-014</t>
+        </is>
+      </c>
+      <c r="D83" s="18" t="inlineStr">
+        <is>
+          <t>M. Image Search — Gallery</t>
+        </is>
+      </c>
+      <c r="E83" s="18" t="inlineStr">
+        <is>
+          <t>FR-IS-02, FR-IS-04</t>
+        </is>
+      </c>
+      <c r="F83" s="18" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G83" s="18" t="inlineStr">
+        <is>
+          <t>Đóng khay Gallery Bottom Sheet bằng nút "X" trên header hoặc bằng cách tap vào vùng tối bên ngoài sheet.</t>
+        </is>
+      </c>
+      <c r="H83" s="18" t="inlineStr">
+        <is>
+          <t>Tap nút "X" / Tap vùng nền tối phía sau sheet</t>
+        </is>
+      </c>
+      <c r="I83" s="18" t="inlineStr">
+        <is>
+          <t>Khay Gallery "Ảnh gần đây" đang mở, chưa chọn ảnh nào.</t>
+        </is>
+      </c>
+      <c r="J83" s="18" t="inlineStr">
+        <is>
+          <t>Cả 2 cách đóng đều trả về đúng Camera Screen (SS-SCR-013) mà không chọn ảnh nào, giữ nguyên trạng thái camera đang có (camera trước/sau, flash) — đúng theo mô tả storyboard "Đóng khay → Trở lại màn hình chụp mà không chọn ảnh nào".</t>
+        </is>
+      </c>
+      <c r="K83" s="18" t="inlineStr">
+        <is>
+          <t>Hai cách đóng (nút X / tap ngoài) phải cho kết quả nhất quán với nhau; không có ảnh nào bị chọn nhầm khi đóng.</t>
+        </is>
+      </c>
+      <c r="L83" s="18" t="n"/>
+      <c r="M83" s="10" t="n"/>
+      <c r="N83" s="10" t="n"/>
+      <c r="O83" s="10" t="n"/>
+      <c r="P83" s="18" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="18" t="n">
+        <v>69</v>
+      </c>
+      <c r="B84" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-017-SC4</t>
+        </is>
+      </c>
+      <c r="C84" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-017</t>
+        </is>
+      </c>
+      <c r="D84" s="18" t="inlineStr">
+        <is>
+          <t>P. Voice Search — Listening</t>
+        </is>
+      </c>
+      <c r="E84" s="18" t="inlineStr">
+        <is>
+          <t>FR-VS-01, FR-VS-03</t>
+        </is>
+      </c>
+      <c r="F84" s="18" t="inlineStr">
+        <is>
+          <t>Multilingual</t>
+        </is>
+      </c>
+      <c r="G84" s="18" t="inlineStr">
+        <is>
+          <t>Nhận diện đa ngôn ngữ (EN/KR/CN/RU) và tự động phát hiện ngôn ngữ, không cần khách chọn thủ công.</t>
+        </is>
+      </c>
+      <c r="H84" s="18" t="inlineStr">
+        <is>
+          <t>Nói tiếng Anh / Hàn / Trung / Nga</t>
+        </is>
+      </c>
+      <c r="I84" s="18" t="inlineStr">
+        <is>
+          <t>Quyền Micro đã cấp; đang ở lớp thu âm Listening.</t>
+        </is>
+      </c>
+      <c r="J84" s="18" t="inlineStr">
+        <is>
+          <t>Hệ thống tự động phát hiện đúng ngôn ngữ đang nói (không có UI chọn ngôn ngữ thủ công) và chuyển giọng nói thành văn bản chính xác cho cả 4 ngôn ngữ EN/KR/CN/RU, xử lý y hệt như một truy vấn tiếng Việt (theo FR-VS-01).</t>
+        </is>
+      </c>
+      <c r="K84" s="18" t="inlineStr">
+        <is>
+          <t>Không có bước chọn ngôn ngữ nào chặn luồng; độ chính xác transcribe chấp nhận được cho cả 4 ngôn ngữ; kết quả tìm kiếm trả về sản phẩm liên quan tương ứng.</t>
+        </is>
+      </c>
+      <c r="L84" s="18" t="n"/>
+      <c r="M84" s="10" t="n"/>
+      <c r="N84" s="10" t="n"/>
+      <c r="O84" s="10" t="n"/>
+      <c r="P84" s="18" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="18" t="n">
+        <v>70</v>
+      </c>
+      <c r="B85" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-018-SC3</t>
+        </is>
+      </c>
+      <c r="C85" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-018</t>
+        </is>
+      </c>
+      <c r="D85" s="18" t="inlineStr">
+        <is>
+          <t>Q. Voice Search — Result</t>
+        </is>
+      </c>
+      <c r="E85" s="18" t="inlineStr">
+        <is>
+          <t>FR-VS-08, NFR-005</t>
+        </is>
+      </c>
+      <c r="F85" s="18" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="G85" s="18" t="inlineStr">
+        <is>
+          <t>Đo thời gian phản hồi tìm kiếm giọng nói đầu-cuối (từ khi kết thúc nói tới khi kết quả đầu tiên hiển thị).</t>
+        </is>
+      </c>
+      <c r="H85" s="18" t="inlineStr">
+        <is>
+          <t>Giọng nói chuẩn, điều kiện mạng bình thường</t>
+        </is>
+      </c>
+      <c r="I85" s="18" t="inlineStr">
+        <is>
+          <t>Điều kiện mạng bình thường.</t>
+        </is>
+      </c>
+      <c r="J85" s="18" t="inlineStr">
+        <is>
+          <t>TBD — FR-VS-08 ghi nhận ngưỡng 6.000ms P95, NFR-005 ghi nhận 4.000ms P95 cho cùng phép đo — hai số liệu mâu thuẫn (xem QnA-30, đang mở). Test case đo thực tế P95 nhưng không chấm Pass/Fail cho tới khi BA/TD chốt đúng 1 con số chính thức.</t>
+        </is>
+      </c>
+      <c r="K85" s="18" t="inlineStr">
+        <is>
+          <t>P95 phải nằm trong ngưỡng chính thức MỘT KHI được xác nhận (4.000ms hoặc 6.000ms).</t>
+        </is>
+      </c>
+      <c r="L85" s="18" t="inlineStr">
+        <is>
+          <t>QnA-30</t>
+        </is>
+      </c>
+      <c r="M85" s="10" t="n"/>
+      <c r="N85" s="10" t="n"/>
+      <c r="O85" s="10" t="n"/>
+      <c r="P85" s="18" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-30: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:P70">
@@ -5165,7 +6122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q114"/>
+  <dimension ref="A1:Q177"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5566,42 +6523,42 @@
       <c r="Q6" s="9" t="n"/>
     </row>
     <row r="7" ht="38.25" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>SS-SCR-001-SC2-TC3</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>SS-SCR-001-SC2</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>SS-SCR-001</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="18" t="inlineStr">
         <is>
           <t>FR-SP-02, FR-IS-02, FR-VS-02, FR-PS-01, FR-PS-02, FR-PS-03, FR-PS-04</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>Edge</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="F7" s="18" t="inlineStr">
         <is>
           <t>"Xoá tất cả" chỉ xoá lịch sử cục bộ trên thiết bị đó, không đồng bộ giữa các thiết bị</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G7" s="18" t="inlineStr">
         <is>
           <t>Khách hàng đã đăng nhập cùng 1 tài khoản trên 2 thiết bị khác nhau (Thiết bị A và Thiết bị B), mỗi thiết bị có lịch sử "Tìm kiếm gần đây" lưu cục bộ riêng.</t>
         </is>
       </c>
-      <c r="H7" s="9" t="inlineStr">
+      <c r="H7" s="18" t="inlineStr">
         <is>
           <t>1. Trên Thiết bị A, tạo lịch sử Tìm kiếm gần đây (3-5 từ khoá).
 2. Trên Thiết bị B, đăng nhập cùng tài khoản và tạo lịch sử Tìm kiếm gần đây riêng của thiết bị đó.
@@ -5610,17 +6567,17 @@
 5. Đăng xuất rồi đăng nhập lại trên Thiết bị B (hoặc mở lại app) và kiểm tra lần nữa.</t>
         </is>
       </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="I7" s="18" t="inlineStr">
         <is>
           <t>2 thiết bị cùng 1 tài khoản Thành viên, mỗi thiết bị có cache Tìm kiếm gần đây khác nhau.</t>
         </is>
       </c>
-      <c r="J7" s="9" t="inlineStr">
+      <c r="J7" s="18" t="inlineStr">
         <is>
           <t>TBD — "Xoá tất cả" chỉ xoá local storage trên Thiết bị A. Thiết bị B vẫn giữ nguyên cache riêng của nó ngay sau bước 3/4 (Tìm kiếm gần đây lưu cục bộ trên thiết bị), trừ khi hệ thống có cơ chế đồng bộ server-side, hiện chưa xác nhận. Chưa chốt Pass/Fail cho tới khi BA xác nhận — xem QnA-27.</t>
         </is>
       </c>
-      <c r="K7" s="9" t="inlineStr">
+      <c r="K7" s="18" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5633,12 +6590,12 @@
       </c>
       <c r="N7" s="10" t="n"/>
       <c r="O7" s="10" t="n"/>
-      <c r="P7" s="9" t="inlineStr">
+      <c r="P7" s="18" t="inlineStr">
         <is>
           <t>QnA-27</t>
         </is>
       </c>
-      <c r="Q7" s="9" t="inlineStr">
+      <c r="Q7" s="18" t="inlineStr">
         <is>
           <t>OPEN: hành vi đồng bộ Tìm kiếm gần đây giữa nhiều thiết bị chưa có tài liệu quy định. Đã ghi QnA-27.</t>
         </is>
@@ -5997,59 +6954,59 @@
       <c r="Q12" s="9" t="n"/>
     </row>
     <row r="13" ht="89.25" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>SS-SCR-001-SC4-TC1</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>SS-SCR-001-SC4</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>SS-SCR-001</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D13" s="18" t="inlineStr">
         <is>
           <t>FR-SP-02, FR-IS-02, FR-VS-02, FR-PS-01, FR-PS-02, FR-PS-03, FR-PS-04</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="18" t="inlineStr">
         <is>
           <t>Ranking</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F13" s="18" t="inlineStr">
         <is>
           <t>Xếp hạng "Thường mua" theo số Đơn hàng (Order Count), không theo số lượng SKU</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G13" s="18" t="inlineStr">
         <is>
           <t>OMS có dữ liệu Order History; tồn kho một số SKU = 0.</t>
         </is>
       </c>
-      <c r="H13" s="9" t="inlineStr">
+      <c r="H13" s="18" t="inlineStr">
         <is>
           <t>1. Đăng nhập tài khoản có lịch sử mua: SKU-A mua trong 3 đơn hàng khác nhau (mỗi đơn 1 sản phẩm), SKU-B mua trong 1 đơn hàng (số lượng 5 sản phẩm/đơn).
 2. Vào Pre-search Screen, quan sát khối "Thường mua".
 3. So sánh vị trí SKU-A và SKU-B.</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>SKU-A: 3 đơn hàng x 1 sp; SKU-B: 1 đơn hàng x 5 sp</t>
         </is>
       </c>
-      <c r="J13" s="9" t="inlineStr">
+      <c r="J13" s="18" t="inlineStr">
         <is>
           <t>SKU-A xếp trước SKU-B vì đếm theo SỐ ĐƠN HÀNG (3 &gt; 1), không phải theo tổng số lượng sản phẩm (1x3=3 so với 5) — đúng logic FR-PS-03: "tuyệt đối KHÔNG đếm theo số lượng/quantity bên trong đơn hàng".</t>
         </is>
       </c>
-      <c r="K13" s="9" t="inlineStr">
+      <c r="K13" s="18" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -6062,12 +7019,12 @@
       </c>
       <c r="N13" s="10" t="n"/>
       <c r="O13" s="10" t="n"/>
-      <c r="P13" s="9" t="inlineStr">
+      <c r="P13" s="18" t="inlineStr">
         <is>
           <t>QnA-29</t>
         </is>
       </c>
-      <c r="Q13" s="9" t="inlineStr">
+      <c r="Q13" s="18" t="inlineStr">
         <is>
           <t>Tham chiếu QnA-29 (mâu thuẫn Storyboard vs BRD về cửa sổ thời gian lấy lịch sử đơn hàng) — kết luận SKU-A xếp trước SKU-B (đếm theo số đơn, không theo số lượng) không phụ thuộc vào độ dài cửa sổ cụ thể, ghi nhận để theo dõi/liên kết.</t>
         </is>
@@ -9326,7 +10283,7 @@
       <c r="O59" s="10" t="n"/>
       <c r="P59" s="11" t="inlineStr">
         <is>
-          <t>QnA-04</t>
+          <t>QnA-35</t>
         </is>
       </c>
       <c r="Q59" s="11" t="n"/>
@@ -9805,7 +10762,7 @@
       </c>
       <c r="J66" s="11" t="inlineStr">
         <is>
-          <t>Ảnh Figma thực tế (Text_Search.png, đã tăng sáng để xem — xem QnA-16) cho thấy sheet Bộ lọc THỰC SỰ CÓ thanh hành động cố định ở đáy: nút "Thiết lập lại" (outline) bên trái + nút "Áp dụng" (đỏ, full-width) bên phải. Điều này MÂU THUẪN với ghi chú riêng của storyboard PPTX (Mục cần chốt #3) khẳng định thanh này đang THIẾU. Test case thực thi theo ảnh Figma thật (có thanh hành động); không chấm Pass/Fail cuối cùng cho tới khi BA xác nhận bản nào là nguồn đúng. Xem QnA-18.</t>
+          <t>Ảnh Figma thực tế (Text Search.png) VÀ storyboard bản cập nhật (v0.1-20260819) đều thống nhất xác nhận: sheet Bộ lọc CÓ thanh hành động cố định ở đáy gồm nút "Thiết lập lại" (outline) bên trái + nút "Áp dụng" (đỏ, full-width) bên phải, luôn hiển thị dù cuộn tới đâu (sticky). Đã hết mâu thuẫn nguồn — có thể chấm Pass/Fail bình thường. Xem QnA-18 (đã Resolved).</t>
         </is>
       </c>
       <c r="K66" s="11" t="inlineStr">
@@ -9816,7 +10773,7 @@
       <c r="L66" s="10" t="n"/>
       <c r="M66" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="N66" s="10" t="n"/>
@@ -9828,7 +10785,7 @@
       </c>
       <c r="Q66" s="11" t="inlineStr">
         <is>
-          <t>Phát hiện khi đối chiếu ảnh Figma thật (đã tăng sáng) với PPTX storyboard — 2 nguồn mâu thuẫn nhau về cùng 1 chi tiết UI.</t>
+          <t>RESOLVED — QnA-18: xem chi tiết trong file QnA log. Cả 2 nguồn (Figma + storyboard cập nhật) đã thống nhất.</t>
         </is>
       </c>
     </row>
@@ -11583,7 +12540,7 @@
       </c>
       <c r="J91" s="9" t="inlineStr">
         <is>
-          <t>Hệ thống từ chối trước khi upload, hiển thị đúng Toast lỗi định dạng theo FR-IS-04; không crash, không mở Loading Screen.</t>
+          <t>Hệ thống từ chối trước khi upload, hiển thị Toast đúng nguyên văn theo FR-IS-04: "Định dạng hình ảnh không hợp lệ hoặc dung lượng vượt quá 5MB. Vui lòng thử lại."; không crash, không mở Loading Screen.</t>
         </is>
       </c>
       <c r="K91" s="9" t="inlineStr">
@@ -11918,7 +12875,8 @@
         <is>
           <t>1. Ở trang kết quả ảnh, chạm vào thumbnail ảnh trong ô tìm kiếm.
 2. Quan sát công cụ Crop mở ra.
-3. Kéo khung chữ nhật để thu hẹp vùng quét, xác nhận.</t>
+3. Kéo khung chữ nhật để thu hẹp vùng quét, xác nhận.
+4. Quan sát thumbnail trong ô tìm kiếm sau khi crop có thay đổi theo vùng đã chọn hay vẫn giữ ảnh gốc.</t>
         </is>
       </c>
       <c r="I96" s="9" t="inlineStr">
@@ -11928,7 +12886,7 @@
       </c>
       <c r="J96" s="9" t="inlineStr">
         <is>
-          <t>Công cụ Crop overlay mở đúng, cho phép kéo khung chữ nhật giới hạn vùng quét AI; sau khi xác nhận, hệ thống chạy lại tìm kiếm dựa trên vùng ảnh đã crop.</t>
+          <t>Công cụ Crop overlay mở đúng, cho phép kéo khung chữ nhật giới hạn vùng quét AI; sau khi xác nhận, hệ thống chạy lại tìm kiếm dựa trên vùng ảnh đã crop; đồng thời thumbnail trong ô tìm kiếm cũng phải cập nhật hiển thị ĐÚNG PHẦN ẢNH ĐÃ CROP (không còn hiển thị ảnh gốc đầy đủ chưa cắt) — để khách xác nhận trực quan hệ thống đang tìm theo đúng vùng đã chọn.</t>
         </is>
       </c>
       <c r="K96" s="9" t="inlineStr">
@@ -12266,7 +13224,8 @@
           <t>1. Upload ảnh mờ/out-of-focus.
 2. Quan sát trang kết quả.
 3. Chạm "Thử lại".
-4. Quay lại luồng ảnh, upload lại ảnh mờ, lần này chạm "Tìm bằng từ khoá".</t>
+4. Quay lại luồng ảnh, upload lại ảnh mờ, lần này chạm "Tìm bằng từ khoá".
+5. Quan sát trạng thái màn hình Pre-search vừa chuyển tới: ô tìm kiếm, khối Tìm kiếm gần đây/Xu hướng.</t>
         </is>
       </c>
       <c r="I101" s="9" t="inlineStr">
@@ -12276,7 +13235,7 @@
       </c>
       <c r="J101" s="9" t="inlineStr">
         <is>
-          <t>Bước 2: hiển thị đúng trang lỗi "Không nhận diện được" với hướng dẫn khắc phục cụ thể, không dùng mã lỗi kỹ thuật. Bước 3: quay lại Camera Screen, giữ nguyên chế độ camera trước/sau đã dùng. Bước 4: chuyển đúng sang Pre-search Screen.</t>
+          <t>Bước 2: hiển thị đúng trang lỗi "Không nhận diện được" với hướng dẫn khắc phục cụ thể, không dùng mã lỗi kỹ thuật. Bước 3: quay lại Camera Screen, giữ nguyên chế độ camera trước/sau đã dùng. Bước 4: chuyển đúng sang Pre-search Screen (SS-SCR-001) — không phải quay lại Camera Screen như CTA "Thử lại". Bước 5: Pre-search Screen hiển thị ở trạng thái sạch/bình thường — ô tìm kiếm trống và sẵn sàng nhận input mới, các khối Tìm kiếm gần đây/Xu hướng tìm kiếm hiển thị đầy đủ như một lần vào Pre-search thông thường, không còn dấu vết nào của lượt tìm bằng ảnh thất bại trước đó (không có banner lỗi sót lại).</t>
         </is>
       </c>
       <c r="K101" s="9" t="inlineStr">
@@ -12530,7 +13489,7 @@
       </c>
       <c r="F105" s="11" t="inlineStr">
         <is>
-          <t>Ngưỡng tự động dừng thu âm — mâu thuẫn giữa 6 giây cố định và đề xuất 2s im lặng/15s tối đa</t>
+          <t>Ngưỡng tự động dừng thu âm cố định 6 giây (đã xác nhận, hết mâu thuẫn)</t>
         </is>
       </c>
       <c r="G105" s="11" t="inlineStr">
@@ -12551,7 +13510,7 @@
       </c>
       <c r="J105" s="11" t="inlineStr">
         <is>
-          <t>TBD — storyboard có 2 mô tả mâu thuẫn cho cùng hành vi: mục mô tả màn hình ghi "Tự động dừng sau H giây" (Loading), còn phần "Mục cần chốt" của tài liệu lại đề xuất "2 giây im lặng hoặc tối đa 15 giây". Không thực thi Pass/Fail định lượng cho đến khi TD/BA chốt 1 giá trị chính thức. Xem QnA-05.</t>
+          <t>Storyboard bản cập nhật (v0.1-20260819) đã gỡ bỏ đề xuất "2 giây im lặng / 15 giây tối đa" — chỉ còn giá trị chính thức duy nhất: tự động dừng thu âm sau đúng 6 giây kể từ khi bắt đầu, không phụ thuộc khoảng lặng giữa chừng. Bước 2 (nói rồi im lặng 2 giây) KHÔNG được kích hoạt auto-stop sớm — hệ thống vẫn tiếp tục thu cho tới mốc 6 giây. Xem QnA-05 (đã Resolved).</t>
         </is>
       </c>
       <c r="K105" s="11" t="inlineStr">
@@ -12562,7 +13521,7 @@
       <c r="L105" s="10" t="n"/>
       <c r="M105" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="N105" s="10" t="n"/>
@@ -12574,7 +13533,7 @@
       </c>
       <c r="Q105" s="11" t="inlineStr">
         <is>
-          <t>OPEN — cần TD chốt ngưỡng auto-stop chính thức.</t>
+          <t>RESOLVED — QnA-05: xem chi tiết trong file QnA log.</t>
         </is>
       </c>
     </row>
@@ -12859,58 +13818,58 @@
       <c r="Q109" s="9" t="n"/>
     </row>
     <row r="110">
-      <c r="A110" s="9" t="inlineStr">
+      <c r="A110" s="18" t="inlineStr">
         <is>
           <t>SS-SCR-018-SC1-TC3</t>
         </is>
       </c>
-      <c r="B110" s="9" t="inlineStr">
+      <c r="B110" s="18" t="inlineStr">
         <is>
           <t>SS-SCR-018-SC1</t>
         </is>
       </c>
-      <c r="C110" s="9" t="inlineStr">
+      <c r="C110" s="18" t="inlineStr">
         <is>
           <t>SS-SCR-018</t>
         </is>
       </c>
-      <c r="D110" s="9" t="inlineStr">
+      <c r="D110" s="18" t="inlineStr">
         <is>
           <t>FR-VS-04, FR-VS-05</t>
         </is>
       </c>
-      <c r="E110" s="9" t="inlineStr">
+      <c r="E110" s="18" t="inlineStr">
         <is>
           <t>Edge</t>
         </is>
       </c>
-      <c r="F110" s="9" t="inlineStr">
-        <is>
-          <t>Độ tin cậy nhận diện trung bình-thấp hiển thị banner gợi ý tương tự luồng Text</t>
-        </is>
-      </c>
-      <c r="G110" s="9" t="inlineStr">
+      <c r="F110" s="18" t="inlineStr">
+        <is>
+          <t>Độ tin cậy trung bình-thấp hiển thị banner gợi ý — TBD tính năng có nằm trong scope v1 không</t>
+        </is>
+      </c>
+      <c r="G110" s="18" t="inlineStr">
         <is>
           <t>Voice-to-text xử lý xong.</t>
         </is>
       </c>
-      <c r="H110" s="9" t="inlineStr">
+      <c r="H110" s="18" t="inlineStr">
         <is>
           <t>1. Giả lập giọng nói cho kết quả transcribe có độ tin cậy trung bình-thấp (gần giống nhưng không chắc chắn).
 2. Quan sát UI trang kết quả.</t>
         </is>
       </c>
-      <c r="I110" s="9" t="inlineStr">
+      <c r="I110" s="18" t="inlineStr">
         <is>
           <t>Giọng nói mơ hồ/độ tin cậy trung bình</t>
         </is>
       </c>
-      <c r="J110" s="9" t="inlineStr">
-        <is>
-          <t>Hiển thị banner "Bạn có muốn tìm …?" tương tự cơ chế auto-correct của luồng text (SS-SCR-003) thay vì trả thẳng kết quả có thể sai.</t>
-        </is>
-      </c>
-      <c r="K110" s="9" t="inlineStr">
+      <c r="J110" s="18" t="inlineStr">
+        <is>
+          <t>TBD — BRD (FR-VS-04/FR-VS-05) không nhắc tới cơ chế banner này, chỉ có trong ghi chú riêng của storyboard. Nếu tính năng được xác nhận nằm trong scope: hiển thị banner "Bạn có muốn tìm …?" tương tự cơ chế auto-correct của luồng text (SS-SCR-003) thay vì trả thẳng kết quả có thể sai. Không chấm Pass/Fail cho tới khi BA/TD xác nhận tính năng này có thật trong v1. Xem QnA-51.</t>
+        </is>
+      </c>
+      <c r="K110" s="18" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -12918,13 +13877,21 @@
       <c r="L110" s="10" t="n"/>
       <c r="M110" s="10" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N110" s="10" t="n"/>
       <c r="O110" s="10" t="n"/>
-      <c r="P110" s="9" t="n"/>
-      <c r="Q110" s="9" t="n"/>
+      <c r="P110" s="18" t="inlineStr">
+        <is>
+          <t>QnA-51</t>
+        </is>
+      </c>
+      <c r="Q110" s="18" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-51: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="9" t="inlineStr">
@@ -13103,7 +14070,8 @@
       <c r="H113" s="9" t="inlineStr">
         <is>
           <t>1. Ở màn "Không nhận diện được" của luồng giọng nói.
-2. Chạm CTA phụ "Tìm bằng từ khoá".</t>
+2. Chạm CTA phụ "Tìm bằng từ khoá".
+3. Quan sát trạng thái màn hình Pre-search vừa chuyển tới: ô tìm kiếm, khối Tìm kiếm gần đây/Xu hướng.</t>
         </is>
       </c>
       <c r="I113" s="9" t="inlineStr">
@@ -13113,7 +14081,7 @@
       </c>
       <c r="J113" s="9" t="inlineStr">
         <is>
-          <t>Chuyển đúng sang Pre-search Screen (SS-SCR-001); khách không bao giờ bị kẹt ở màn lỗi mà không có lối thoát sang phương thức tìm kiếm khác.</t>
+          <t>Chuyển đúng sang Pre-search Screen (SS-SCR-001) — không phải mở lại lớp thu âm như CTA "Thử lại"; khách không bao giờ bị kẹt ở màn lỗi mà không có lối thoát sang phương thức tìm kiếm khác. Pre-search Screen hiển thị ở trạng thái sạch/bình thường — ô tìm kiếm trống và sẵn sàng nhận input mới, các khối Tìm kiếm gần đây/Xu hướng tìm kiếm hiển thị đầy đủ như một lần vào Pre-search thông thường, không còn dấu vết nào của lượt tìm bằng giọng nói thất bại trước đó (không có banner lỗi sót lại).</t>
         </is>
       </c>
       <c r="K113" s="9" t="inlineStr">
@@ -13199,6 +14167,4584 @@
       <c r="O114" s="10" t="n"/>
       <c r="P114" s="9" t="n"/>
       <c r="Q114" s="9" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-003-SC1-TC3</t>
+        </is>
+      </c>
+      <c r="B115" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-003-SC1</t>
+        </is>
+      </c>
+      <c r="C115" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-003</t>
+        </is>
+      </c>
+      <c r="D115" s="9" t="inlineStr">
+        <is>
+          <t>FR-AC-01, FR-AC-03</t>
+        </is>
+      </c>
+      <c r="E115" s="9" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+      <c r="F115" s="9" t="inlineStr">
+        <is>
+          <t>Đóng banner bằng "X" rồi gõ nối thêm ký tự — banner không hiện lại (tôn trọng lựa chọn của khách)</t>
+        </is>
+      </c>
+      <c r="G115" s="9" t="inlineStr">
+        <is>
+          <t>Banner gợi ý đang hiển thị cho "sua toui" (đề xuất "sữa tươi").</t>
+        </is>
+      </c>
+      <c r="H115" s="9" t="inlineStr">
+        <is>
+          <t>1. Gõ "sua toui", chờ banner xuất hiện.
+2. Chạm nút "X" đóng banner.
+3. Gõ nối thêm ký tự vào cụm đã lưu, ví dụ thành "sua toui tuoi" (không xoá gì, chỉ gõ thêm).
+4. Quan sát banner có hiện lại không.
+5. Xoá lùi (backspace) một vài ký tự cho tới khi phá vỡ cụm từ gốc đã lưu (VD xoá về "sua to").
+6. Quan sát banner sau bước 5.</t>
+        </is>
+      </c>
+      <c r="I115" s="9" t="inlineStr">
+        <is>
+          <t>"sua toui" → X → "sua toui tuoi" → backspace về "sua to"</t>
+        </is>
+      </c>
+      <c r="J115" s="9" t="inlineStr">
+        <is>
+          <t>Bước 4: banner KHÔNG hiện lại dù chuỗi vẫn còn chứa nguyên "sua toui" đã bị đóng trước đó — hệ thống tôn trọng lựa chọn đóng banner của khách khi khách chỉ gõ nối thêm. Bước 6: sau khi xoá lùi phá vỡ cụm từ đã lưu, quy tắc "đã đóng" được reset — nếu chuỗi còn lại vẫn fuzzy-match được, banner có quyền hiện lại bình thường.</t>
+        </is>
+      </c>
+      <c r="K115" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L115" s="10" t="n"/>
+      <c r="M115" s="10" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N115" s="10" t="n"/>
+      <c r="O115" s="10" t="n"/>
+      <c r="P115" s="9" t="n"/>
+      <c r="Q115" s="9" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-003-SC1-TC4</t>
+        </is>
+      </c>
+      <c r="B116" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-003-SC1</t>
+        </is>
+      </c>
+      <c r="C116" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-003</t>
+        </is>
+      </c>
+      <c r="D116" s="9" t="inlineStr">
+        <is>
+          <t>FR-AC-01, FR-AC-03</t>
+        </is>
+      </c>
+      <c r="E116" s="9" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F116" s="9" t="inlineStr">
+        <is>
+          <t>Từ khoá gợi ý trên banner đảm bảo trả về ≥1 SKU đang Active</t>
+        </is>
+      </c>
+      <c r="G116" s="9" t="inlineStr">
+        <is>
+          <t>Bộ so khớp mờ đang hoạt động; catalogue có SKU active khớp từ khoá đã sửa.</t>
+        </is>
+      </c>
+      <c r="H116" s="9" t="inlineStr">
+        <is>
+          <t>1. Gõ "sua toui", chờ banner xuất hiện đề xuất "sữa tươi".
+2. Chạm vào liên kết từ khoá đã sửa trên banner.
+3. Quan sát trang kết quả trả về.
+4. Kiểm tra số lượng sản phẩm trạng thái Active trong kết quả.</t>
+        </is>
+      </c>
+      <c r="I116" s="9" t="inlineStr">
+        <is>
+          <t>"sua toui" → tap "sữa tươi"</t>
+        </is>
+      </c>
+      <c r="J116" s="9" t="inlineStr">
+        <is>
+          <t>Trang kết quả trả về ≥1 sản phẩm đang ở trạng thái Active (còn bán) cho đúng từ khoá đã sửa; hệ thống không được đề xuất một từ khoá "chính xác hơn" nhưng lại dẫn tới Zero Result hoặc toàn bộ SKU Inactive — banner chỉ được gợi ý các cụm từ đã xác thực có ≥1 SKU Active trong catalogue.</t>
+        </is>
+      </c>
+      <c r="K116" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L116" s="10" t="n"/>
+      <c r="M116" s="10" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N116" s="10" t="n"/>
+      <c r="O116" s="10" t="n"/>
+      <c r="P116" s="9" t="n"/>
+      <c r="Q116" s="9" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-003-SC4-TC2</t>
+        </is>
+      </c>
+      <c r="B117" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-003-SC4</t>
+        </is>
+      </c>
+      <c r="C117" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-003</t>
+        </is>
+      </c>
+      <c r="D117" s="18" t="inlineStr">
+        <is>
+          <t>FR-AC-01, FR-AC-03</t>
+        </is>
+      </c>
+      <c r="E117" s="18" t="inlineStr">
+        <is>
+          <t>Multilingual</t>
+        </is>
+      </c>
+      <c r="F117" s="18" t="inlineStr">
+        <is>
+          <t>Gợi ý song ngữ khi gõ từ tiếng Anh/Nga lúc UI=VI — TBD hành vi</t>
+        </is>
+      </c>
+      <c r="G117" s="18" t="inlineStr">
+        <is>
+          <t>UI language = VI; "moloko" (tiếng Nga, nghĩa "sữa") hoặc "milk" (tiếng Anh) được gõ vào ô tìm kiếm.</t>
+        </is>
+      </c>
+      <c r="H117" s="18" t="inlineStr">
+        <is>
+          <t>1. Đặt UI language = VI.
+2. Gõ "milk" (tiếng Anh, đúng chính tả).
+3. Quan sát nội dung banner/gợi ý.
+4. Lặp lại với từ tiếng Nga "moloko".</t>
+        </is>
+      </c>
+      <c r="I117" s="18" t="inlineStr">
+        <is>
+          <t>"milk" / "moloko" (UI=VI)</t>
+        </is>
+      </c>
+      <c r="J117" s="18" t="inlineStr">
+        <is>
+          <t>TBD — chưa xác nhận: banner có hiển thị đồng thời gợi ý theo ngôn ngữ đang nhập (tiếng Anh/Nga, ưu tiên hiển thị trước) VÀ 1 gợi ý tương đương tiếng Việt ("sữa") hay không. Yêu cầu tối thiểu: không crash, hệ thống trả về kết quả liên quan tới "sữa" dù cơ chế hiển thị gợi ý cụ thể chưa được chốt. Xem QnA-36.</t>
+        </is>
+      </c>
+      <c r="K117" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L117" s="10" t="n"/>
+      <c r="M117" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N117" s="10" t="n"/>
+      <c r="O117" s="10" t="n"/>
+      <c r="P117" s="18" t="inlineStr">
+        <is>
+          <t>QnA-36</t>
+        </is>
+      </c>
+      <c r="Q117" s="18" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-36: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-003-SC4-TC3</t>
+        </is>
+      </c>
+      <c r="B118" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-003-SC4</t>
+        </is>
+      </c>
+      <c r="C118" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-003</t>
+        </is>
+      </c>
+      <c r="D118" s="18" t="inlineStr">
+        <is>
+          <t>FR-AC-01, FR-AC-03</t>
+        </is>
+      </c>
+      <c r="E118" s="18" t="inlineStr">
+        <is>
+          <t>Multilingual</t>
+        </is>
+      </c>
+      <c r="F118" s="18" t="inlineStr">
+        <is>
+          <t>Sai chính tả từ tiếng Việt không dấu — gợi ý kèm từ đồng nghĩa/liên quan tương đương</t>
+        </is>
+      </c>
+      <c r="G118" s="18" t="inlineStr">
+        <is>
+          <t>UI language = VI; "sua tuoiii" là lỗi gõ thừa ký tự của "sua tuoi" (không dấu của "sữa tươi").</t>
+        </is>
+      </c>
+      <c r="H118" s="18" t="inlineStr">
+        <is>
+          <t>1. Đặt UI language = VI.
+2. Gõ "sua tuoiii" (không dấu, sai chính tả).
+3. Quan sát banner gợi ý.
+4. Kiểm tra banner có gợi ý thêm từ đồng nghĩa/từ liên quan nghĩa tương đương (VD "fresh milk", "sữa nước") ngoài từ đã sửa lỗi chính tả trực tiếp hay không.</t>
+        </is>
+      </c>
+      <c r="I118" s="18" t="inlineStr">
+        <is>
+          <t>"sua tuoiii"</t>
+        </is>
+      </c>
+      <c r="J118" s="18" t="inlineStr">
+        <is>
+          <t>TBD — banner phải gợi ý đúng "sữa tươi" (sửa lỗi chính tả + chuẩn hoá không dấu, theo FR-SM-06). Việc có kèm thêm gợi ý mở rộng đồng nghĩa/từ liên quan ngay trên banner (khác với việc hệ thống tự mở rộng ngầm khi tính kết quả theo FR-SM-04) chưa được BRD quy định rõ cho riêng UI banner này. Xem QnA-36.</t>
+        </is>
+      </c>
+      <c r="K118" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L118" s="10" t="n"/>
+      <c r="M118" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N118" s="10" t="n"/>
+      <c r="O118" s="10" t="n"/>
+      <c r="P118" s="18" t="inlineStr">
+        <is>
+          <t>QnA-36</t>
+        </is>
+      </c>
+      <c r="Q118" s="18" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-36: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC1-TC3</t>
+        </is>
+      </c>
+      <c r="B119" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC1</t>
+        </is>
+      </c>
+      <c r="C119" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-005</t>
+        </is>
+      </c>
+      <c r="D119" s="18" t="inlineStr">
+        <is>
+          <t>FR-PR-01, FR-PR-02, FR-PR-05, FR-PR-07, FR-SF-01</t>
+        </is>
+      </c>
+      <c r="E119" s="18" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F119" s="18" t="inlineStr">
+        <is>
+          <t>Chế độ xem (Grid/List) khi Thành viên đăng nhập lần đầu trên thiết bị khác — TBD đồng bộ</t>
+        </is>
+      </c>
+      <c r="G119" s="18" t="inlineStr">
+        <is>
+          <t>Thành viên đã từng chọn chế độ List trên Thiết bị A (đã lưu Local Storage của A).</t>
+        </is>
+      </c>
+      <c r="H119" s="18" t="inlineStr">
+        <is>
+          <t>1. Trên Thiết bị A, đăng nhập Thành viên, đổi chế độ xem sang List.
+2. Đăng nhập cùng tài khoản Thành viên đó trên Thiết bị B (chưa từng mở app/tìm kiếm trên B trước đó).
+3. Vào trang kết quả tìm kiếm lần đầu trên Thiết bị B.
+4. Quan sát chế độ xem mặc định trên Thiết bị B.</t>
+        </is>
+      </c>
+      <c r="I119" s="18" t="inlineStr">
+        <is>
+          <t>Cùng 1 tài khoản, List trên A, lần đầu vào B</t>
+        </is>
+      </c>
+      <c r="J119" s="18" t="inlineStr">
+        <is>
+          <t>TBD — chưa xác nhận Thiết bị B hiển thị theo chế độ đã lưu ở Thiết bị A (đồng bộ server-side theo tài khoản) hay mặc định Grid (vì FR-PR-07 ghi lưu tại Local Storage của thiết bị, không đề cập đồng bộ đa thiết bị). Không chấm Pass/Fail cho tới khi xác nhận. Xem QnA-34.</t>
+        </is>
+      </c>
+      <c r="K119" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L119" s="10" t="n"/>
+      <c r="M119" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N119" s="10" t="n"/>
+      <c r="O119" s="10" t="n"/>
+      <c r="P119" s="18" t="inlineStr">
+        <is>
+          <t>QnA-34</t>
+        </is>
+      </c>
+      <c r="Q119" s="18" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-34: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC1-TC4</t>
+        </is>
+      </c>
+      <c r="B120" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC1</t>
+        </is>
+      </c>
+      <c r="C120" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-005</t>
+        </is>
+      </c>
+      <c r="D120" s="18" t="inlineStr">
+        <is>
+          <t>FR-PR-01, FR-PR-02, FR-PR-05, FR-PR-07, FR-SF-01</t>
+        </is>
+      </c>
+      <c r="E120" s="18" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F120" s="18" t="inlineStr">
+        <is>
+          <t>Chế độ xem khi 2 tài khoản khác nhau đăng nhập lần lượt trên cùng 1 thiết bị — TBD kế thừa</t>
+        </is>
+      </c>
+      <c r="G120" s="18" t="inlineStr">
+        <is>
+          <t>Thiết bị dùng chung; Account 1 đã từng chọn List trên thiết bị này.</t>
+        </is>
+      </c>
+      <c r="H120" s="18" t="inlineStr">
+        <is>
+          <t>1. Account 1 đăng nhập trên thiết bị, đổi chế độ xem sang List, sau đó logout.
+2. Account 2 đăng nhập trên cùng thiết bị (Account 2 chưa từng đổi chế độ xem trước đó).
+3. Vào trang kết quả tìm kiếm.
+4. Quan sát chế độ xem mặc định cho Account 2.</t>
+        </is>
+      </c>
+      <c r="I120" s="18" t="inlineStr">
+        <is>
+          <t>Account 1 (List) logout → Account 2 login, cùng thiết bị</t>
+        </is>
+      </c>
+      <c r="J120" s="18" t="inlineStr">
+        <is>
+          <t>TBD — chưa xác nhận Account 2 kế thừa List (vì cơ chế lưu theo thiết bị, không phân biệt tài khoản) hay có state riêng theo user (mặc định Grid). Không chấm Pass/Fail cho tới khi xác nhận. Xem QnA-34.</t>
+        </is>
+      </c>
+      <c r="K120" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L120" s="10" t="n"/>
+      <c r="M120" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N120" s="10" t="n"/>
+      <c r="O120" s="10" t="n"/>
+      <c r="P120" s="18" t="inlineStr">
+        <is>
+          <t>QnA-34</t>
+        </is>
+      </c>
+      <c r="Q120" s="18" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-34: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC3-TC3</t>
+        </is>
+      </c>
+      <c r="B121" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC3</t>
+        </is>
+      </c>
+      <c r="C121" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-005</t>
+        </is>
+      </c>
+      <c r="D121" s="18" t="inlineStr">
+        <is>
+          <t>FR-PR-01, FR-PR-02, FR-PR-05, FR-PR-07, FR-SF-01</t>
+        </is>
+      </c>
+      <c r="E121" s="18" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+      <c r="F121" s="18" t="inlineStr">
+        <is>
+          <t>Trạng thái trang kết quả phía sau lớp Autocomplete sau khi xoá từ khoá bằng (✕) — TBD giữ filter/kết quả cũ</t>
+        </is>
+      </c>
+      <c r="G121" s="18" t="inlineStr">
+        <is>
+          <t>Trang kết quả đã tải với filter "Không đường" đang active và sort "Giá thấp-cao".</t>
+        </is>
+      </c>
+      <c r="H121" s="18" t="inlineStr">
+        <is>
+          <t>1. Ở trang kết quả "sữa" với filter "Không đường" + sort "Giá thấp-cao" đang áp dụng.
+2. Tap nút (✕) trên Search Bar.
+3. Không gõ từ khoá mới, tap ra ngoài hoặc nhấn Back để đóng lớp Autocomplete.
+4. Quan sát trang kết quả có hiện lại không, và filter chip "Không đường"/sort có còn giữ hay không.</t>
+        </is>
+      </c>
+      <c r="I121" s="18" t="inlineStr">
+        <is>
+          <t>"sữa" + filter/sort active → tap (✕) → đóng Autocomplete không tìm mới</t>
+        </is>
+      </c>
+      <c r="J121" s="18" t="inlineStr">
+        <is>
+          <t>TBD — chưa xác nhận: (a) trang kết quả + filter chip + sort cũ được giữ nguyên ở phía sau, hiện lại y hệt khi đóng Autocomplete mà không tìm từ mới; hay (b) toàn bộ bị xoá/reset ngay khi tap (✕) bất kể có tìm từ mới hay không. Không chấm Pass/Fail cho tới khi xác nhận. Xem QnA-33.</t>
+        </is>
+      </c>
+      <c r="K121" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L121" s="10" t="n"/>
+      <c r="M121" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N121" s="10" t="n"/>
+      <c r="O121" s="10" t="n"/>
+      <c r="P121" s="18" t="inlineStr">
+        <is>
+          <t>QnA-33</t>
+        </is>
+      </c>
+      <c r="Q121" s="18" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-33: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC3-TC4</t>
+        </is>
+      </c>
+      <c r="B122" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC3</t>
+        </is>
+      </c>
+      <c r="C122" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-005</t>
+        </is>
+      </c>
+      <c r="D122" s="9" t="inlineStr">
+        <is>
+          <t>FR-PR-01, FR-PR-02, FR-PR-05, FR-PR-07, FR-SF-01</t>
+        </is>
+      </c>
+      <c r="E122" s="9" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F122" s="9" t="inlineStr">
+        <is>
+          <t>Tap nút (+) trên Product Card thêm giỏ hàng ngay tại trang kết quả, không mở nhầm PDP</t>
+        </is>
+      </c>
+      <c r="G122" s="9" t="inlineStr">
+        <is>
+          <t>Trang kết quả đã tải, ≥1 sản phẩm còn hàng.</t>
+        </is>
+      </c>
+      <c r="H122" s="9" t="inlineStr">
+        <is>
+          <t>1. Ở trang kết quả "sữa", tap chính xác vào nút (+) trên 1 Product Card (không tap vùng ảnh/tên).
+2. Quan sát UI ngay sau khi tap.
+3. Xác nhận trang hiện tại vẫn là trang kết quả (không bị điều hướng sang PDP).</t>
+        </is>
+      </c>
+      <c r="I122" s="9" t="inlineStr">
+        <is>
+          <t>Tap nút (+) trên 1 card còn hàng</t>
+        </is>
+      </c>
+      <c r="J122" s="9" t="inlineStr">
+        <is>
+          <t>Badge giỏ hàng tăng ngay (optimistic update), Toast xác nhận hiện ra (theo hành vi chi tiết đã test đầy đủ ở SS-SCR-011); KHÔNG điều hướng sang PDP; vùng chạm (+) tách biệt hoàn toàn khỏi vùng chạm mở PDP đã test ở SC3-TC1.</t>
+        </is>
+      </c>
+      <c r="K122" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L122" s="10" t="n"/>
+      <c r="M122" s="10" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N122" s="10" t="n"/>
+      <c r="O122" s="10" t="n"/>
+      <c r="P122" s="9" t="n"/>
+      <c r="Q122" s="9" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC7-TC1</t>
+        </is>
+      </c>
+      <c r="B123" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC7</t>
+        </is>
+      </c>
+      <c r="C123" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-005</t>
+        </is>
+      </c>
+      <c r="D123" s="9" t="inlineStr">
+        <is>
+          <t>FR-PR-06</t>
+        </is>
+      </c>
+      <c r="E123" s="9" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F123" s="9" t="inlineStr">
+        <is>
+          <t>Sort mặc định = "Liên quan nhất" khi vào trang kết quả lần đầu</t>
+        </is>
+      </c>
+      <c r="G123" s="9" t="inlineStr">
+        <is>
+          <t>Khách chưa từng chọn Sort trong phiên hiện tại.</t>
+        </is>
+      </c>
+      <c r="H123" s="9" t="inlineStr">
+        <is>
+          <t>1. Tìm kiếm "sữa" lần đầu trong phiên (chưa từng mở Sort sheet trước đó).
+2. Quan sát nhãn trên thanh sticky Sort.
+3. Mở Sort bottom sheet (SS-SCR-008), kiểm tra tiêu chí đang được đánh dấu chọn (selected).</t>
+        </is>
+      </c>
+      <c r="I123" s="9" t="inlineStr">
+        <is>
+          <t>"sữa" (lần đầu trong phiên)</t>
+        </is>
+      </c>
+      <c r="J123" s="9" t="inlineStr">
+        <is>
+          <t>Nhãn sticky hiển thị đúng "Liên quan nhất" ngay từ đầu; khi mở Sort sheet, "Liên quan nhất" đang ở trạng thái được chọn (checked) mà không cần khách thao tác gì trước đó.</t>
+        </is>
+      </c>
+      <c r="K123" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L123" s="10" t="n"/>
+      <c r="M123" s="10" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N123" s="10" t="n"/>
+      <c r="O123" s="10" t="n"/>
+      <c r="P123" s="9" t="n"/>
+      <c r="Q123" s="9" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC8-TC1</t>
+        </is>
+      </c>
+      <c r="B124" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC8</t>
+        </is>
+      </c>
+      <c r="C124" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-005</t>
+        </is>
+      </c>
+      <c r="D124" s="9" t="inlineStr">
+        <is>
+          <t>FR-SF-04</t>
+        </is>
+      </c>
+      <c r="E124" s="9" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F124" s="9" t="inlineStr">
+        <is>
+          <t>Nút "Bộ lọc" ở trạng thái mặc định (không badge) khi chưa áp dụng điều kiện nào</t>
+        </is>
+      </c>
+      <c r="G124" s="9" t="inlineStr">
+        <is>
+          <t>Trang kết quả vừa tải, chưa từng mở/áp dụng Bộ lọc.</t>
+        </is>
+      </c>
+      <c r="H124" s="9" t="inlineStr">
+        <is>
+          <t>1. Tìm kiếm "sữa", quan sát nút "Bộ lọc" trên thanh sticky.
+2. Kiểm tra có badge số lượng hiển thị hay không.
+3. Kiểm tra không có filter chip nào ở trạng thái active trên trang kết quả.</t>
+        </is>
+      </c>
+      <c r="I124" s="9" t="inlineStr">
+        <is>
+          <t>"sữa" (chưa áp dụng filter)</t>
+        </is>
+      </c>
+      <c r="J124" s="9" t="inlineStr">
+        <is>
+          <t>Nút "Bộ lọc" không hiển thị badge (hoặc badge=0 bị ẩn hoàn toàn, giống trạng thái cuối của SS-SCR-010-SC3); không có chip lọc nào active; tổng số kết quả là tập đầy đủ chưa lọc.</t>
+        </is>
+      </c>
+      <c r="K124" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L124" s="10" t="n"/>
+      <c r="M124" s="10" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N124" s="10" t="n"/>
+      <c r="O124" s="10" t="n"/>
+      <c r="P124" s="9" t="n"/>
+      <c r="Q124" s="9" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC9-TC1</t>
+        </is>
+      </c>
+      <c r="B125" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC9</t>
+        </is>
+      </c>
+      <c r="C125" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-005</t>
+        </is>
+      </c>
+      <c r="D125" s="9" t="inlineStr">
+        <is>
+          <t>FR-SF-01, FR-SF-02, FR-SF-03</t>
+        </is>
+      </c>
+      <c r="E125" s="9" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="F125" s="9" t="inlineStr">
+        <is>
+          <t>Tap 1 Smart Filter Chip áp dụng lọc ngay, không cần mở bảng Bộ lọc chi tiết</t>
+        </is>
+      </c>
+      <c r="G125" s="9" t="inlineStr">
+        <is>
+          <t>Trang kết quả đã tải, khối Smart Filter Chips hiển thị ≥1 chip.</t>
+        </is>
+      </c>
+      <c r="H125" s="9" t="inlineStr">
+        <is>
+          <t>1. Tìm kiếm "sữa", quan sát khối Smart Filter Chips ngang phía trên lưới kết quả.
+2. Tap 1 chip bất kỳ (VD "Hữu cơ").
+3. Quan sát trạng thái chip, badge nút Bộ lọc, và số lượng kết quả.</t>
+        </is>
+      </c>
+      <c r="I125" s="9" t="inlineStr">
+        <is>
+          <t>Tap chip "Hữu cơ"</t>
+        </is>
+      </c>
+      <c r="J125" s="9" t="inlineStr">
+        <is>
+          <t>Chip chuyển sang trạng thái active (đổi màu nền) ngay khi tap, không cần nút "Áp dụng" riêng; kết quả cập nhật realtime chỉ còn SKU thoả điều kiện; badge nút "Bộ lọc" tăng thêm 1; kết quả sau lọc luôn ≥1 sản phẩm (đúng FR-SF-01→03).</t>
+        </is>
+      </c>
+      <c r="K125" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L125" s="10" t="n"/>
+      <c r="M125" s="10" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N125" s="10" t="n"/>
+      <c r="O125" s="10" t="n"/>
+      <c r="P125" s="9" t="n"/>
+      <c r="Q125" s="9" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC9-TC2</t>
+        </is>
+      </c>
+      <c r="B126" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC9</t>
+        </is>
+      </c>
+      <c r="C126" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-005</t>
+        </is>
+      </c>
+      <c r="D126" s="9" t="inlineStr">
+        <is>
+          <t>FR-SF-01, FR-SF-02, FR-SF-03</t>
+        </is>
+      </c>
+      <c r="E126" s="9" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="F126" s="9" t="inlineStr">
+        <is>
+          <t>Tap thêm chip thứ 2 kết hợp điều kiện lọc (AND) trên Smart Filter Chips</t>
+        </is>
+      </c>
+      <c r="G126" s="9" t="inlineStr">
+        <is>
+          <t>Đã có 1 chip "Hữu cơ" đang active.</t>
+        </is>
+      </c>
+      <c r="H126" s="9" t="inlineStr">
+        <is>
+          <t>1. Từ trạng thái đã lọc "Hữu cơ", tap thêm chip "Không đường".
+2. Quan sát kết quả và badge sau khi cả 2 chip active.
+3. Bỏ chọn lại chip "Hữu cơ", quan sát kết quả chỉ còn lọc theo "Không đường".</t>
+        </is>
+      </c>
+      <c r="I126" s="9" t="inlineStr">
+        <is>
+          <t>Chip "Hữu cơ" + "Không đường", sau đó bỏ "Hữu cơ"</t>
+        </is>
+      </c>
+      <c r="J126" s="9" t="inlineStr">
+        <is>
+          <t>Cả 2 chip active đồng thời áp dụng lọc kết hợp (AND); badge = 2; bỏ chọn 1 chip giữ nguyên chip còn lại, kết quả tự cập nhật theo đúng 1 điều kiện còn active, badge giảm về 1 — đồng bộ với hành vi bỏ chip đã test ở SS-SCR-010-SC2.</t>
+        </is>
+      </c>
+      <c r="K126" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L126" s="10" t="n"/>
+      <c r="M126" s="10" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N126" s="10" t="n"/>
+      <c r="O126" s="10" t="n"/>
+      <c r="P126" s="9" t="n"/>
+      <c r="Q126" s="9" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-006-SC1-TC3</t>
+        </is>
+      </c>
+      <c r="B127" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-006-SC1</t>
+        </is>
+      </c>
+      <c r="C127" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-006</t>
+        </is>
+      </c>
+      <c r="D127" s="18" t="inlineStr">
+        <is>
+          <t>FR-PR-01, FR-PR-07</t>
+        </is>
+      </c>
+      <c r="E127" s="18" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F127" s="18" t="inlineStr">
+        <is>
+          <t>Chế độ List khi Thành viên đăng nhập lần đầu trên thiết bị khác — TBD đồng bộ (song song SS-SCR-005-SC1-TC3)</t>
+        </is>
+      </c>
+      <c r="G127" s="18" t="inlineStr">
+        <is>
+          <t>Thành viên đã từng chọn List trên Thiết bị A.</t>
+        </is>
+      </c>
+      <c r="H127" s="18" t="inlineStr">
+        <is>
+          <t>1. Trên Thiết bị A, đổi chế độ xem sang List.
+2. Đăng nhập cùng tài khoản trên Thiết bị B (lần đầu).
+3. Vào trang kết quả trên Thiết bị B, quan sát chế độ xem mặc định.</t>
+        </is>
+      </c>
+      <c r="I127" s="18" t="inlineStr">
+        <is>
+          <t>Cùng cơ chế với SS-SCR-005-SC1-TC3, kiểm chứng lại ở chiều List→thiết bị mới</t>
+        </is>
+      </c>
+      <c r="J127" s="18" t="inlineStr">
+        <is>
+          <t>TBD — cùng câu hỏi mở với SS-SCR-005-SC1-TC3 vì 2 màn hình dùng chung 1 cơ chế lưu trạng thái theo FR-PR-07. Không chấm Pass/Fail cho tới khi xác nhận. Xem QnA-34.</t>
+        </is>
+      </c>
+      <c r="K127" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L127" s="10" t="n"/>
+      <c r="M127" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N127" s="10" t="n"/>
+      <c r="O127" s="10" t="n"/>
+      <c r="P127" s="18" t="inlineStr">
+        <is>
+          <t>QnA-34</t>
+        </is>
+      </c>
+      <c r="Q127" s="18" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-34: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-006-SC1-TC4</t>
+        </is>
+      </c>
+      <c r="B128" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-006-SC1</t>
+        </is>
+      </c>
+      <c r="C128" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-006</t>
+        </is>
+      </c>
+      <c r="D128" s="18" t="inlineStr">
+        <is>
+          <t>FR-PR-01, FR-PR-07</t>
+        </is>
+      </c>
+      <c r="E128" s="18" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F128" s="18" t="inlineStr">
+        <is>
+          <t>Chế độ List khi 2 tài khoản đăng nhập lần lượt trên cùng thiết bị — TBD kế thừa (song song SS-SCR-005-SC1-TC4)</t>
+        </is>
+      </c>
+      <c r="G128" s="18" t="inlineStr">
+        <is>
+          <t>Account 1 đã chọn List trên thiết bị dùng chung.</t>
+        </is>
+      </c>
+      <c r="H128" s="18" t="inlineStr">
+        <is>
+          <t>1. Account 1 chọn List, logout.
+2. Account 2 login trên cùng thiết bị, vào trang kết quả.
+3. Quan sát chế độ xem mặc định cho Account 2.</t>
+        </is>
+      </c>
+      <c r="I128" s="18" t="inlineStr">
+        <is>
+          <t>Cùng cơ chế với SS-SCR-005-SC1-TC4</t>
+        </is>
+      </c>
+      <c r="J128" s="18" t="inlineStr">
+        <is>
+          <t>TBD — cùng câu hỏi mở với SS-SCR-005-SC1-TC4. Không chấm Pass/Fail cho tới khi xác nhận. Xem QnA-34.</t>
+        </is>
+      </c>
+      <c r="K128" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L128" s="10" t="n"/>
+      <c r="M128" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N128" s="10" t="n"/>
+      <c r="O128" s="10" t="n"/>
+      <c r="P128" s="18" t="inlineStr">
+        <is>
+          <t>QnA-34</t>
+        </is>
+      </c>
+      <c r="Q128" s="18" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-34: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-006-SC4-TC1</t>
+        </is>
+      </c>
+      <c r="B129" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-006-SC4</t>
+        </is>
+      </c>
+      <c r="C129" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-006</t>
+        </is>
+      </c>
+      <c r="D129" s="9" t="inlineStr">
+        <is>
+          <t>FR-PR-01, FR-PR-07</t>
+        </is>
+      </c>
+      <c r="E129" s="9" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F129" s="9" t="inlineStr">
+        <is>
+          <t>Tap Product Card (ngoài nút +) ở chế độ List mở đúng PDP</t>
+        </is>
+      </c>
+      <c r="G129" s="9" t="inlineStr">
+        <is>
+          <t>Chế độ xem = List, trang kết quả đã tải.</t>
+        </is>
+      </c>
+      <c r="H129" s="9" t="inlineStr">
+        <is>
+          <t>1. Ở trang kết quả "sữa", chế độ List, tap vào vùng ảnh/tên của 1 dòng sản phẩm (không tap nút +).
+2. Quan sát trang mở ra.</t>
+        </is>
+      </c>
+      <c r="I129" s="9" t="inlineStr">
+        <is>
+          <t>1 dòng sản phẩm bất kỳ (List)</t>
+        </is>
+      </c>
+      <c r="J129" s="9" t="inlineStr">
+        <is>
+          <t>Mở đúng PDP của sản phẩm đã tap, hành vi nhất quán với SS-SCR-005-SC3-TC1 (Grid); không kích hoạt add-to-cart nhầm.</t>
+        </is>
+      </c>
+      <c r="K129" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L129" s="10" t="n"/>
+      <c r="M129" s="10" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N129" s="10" t="n"/>
+      <c r="O129" s="10" t="n"/>
+      <c r="P129" s="9" t="n"/>
+      <c r="Q129" s="9" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-006-SC5-TC1</t>
+        </is>
+      </c>
+      <c r="B130" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-006-SC5</t>
+        </is>
+      </c>
+      <c r="C130" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-006</t>
+        </is>
+      </c>
+      <c r="D130" s="18" t="inlineStr">
+        <is>
+          <t>Không có FR ID rõ ràng trong BRD — xem QnA-10</t>
+        </is>
+      </c>
+      <c r="E130" s="18" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F130" s="18" t="inlineStr">
+        <is>
+          <t>Tap nút (+) thêm giỏ hàng ở chế độ List, không mở nhầm PDP</t>
+        </is>
+      </c>
+      <c r="G130" s="18" t="inlineStr">
+        <is>
+          <t>Chế độ xem = List, ≥1 sản phẩm còn hàng.</t>
+        </is>
+      </c>
+      <c r="H130" s="18" t="inlineStr">
+        <is>
+          <t>1. Ở trang kết quả "sữa", chế độ List, tap chính xác vào nút (+) của 1 dòng sản phẩm.
+2. Quan sát badge giỏ hàng và Toast xác nhận.
+3. Xác nhận vẫn ở trang kết quả (không bị điều hướng PDP).</t>
+        </is>
+      </c>
+      <c r="I130" s="18" t="inlineStr">
+        <is>
+          <t>Tap (+) trên 1 dòng còn hàng (List)</t>
+        </is>
+      </c>
+      <c r="J130" s="18" t="inlineStr">
+        <is>
+          <t>Badge tăng ngay, Toast xác nhận hiện ra (theo hành vi chi tiết đã test ở SS-SCR-011); không điều hướng sang PDP; hành vi nhất quán với SS-SCR-005-SC3-TC4 (Grid).</t>
+        </is>
+      </c>
+      <c r="K130" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L130" s="10" t="n"/>
+      <c r="M130" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N130" s="10" t="n"/>
+      <c r="O130" s="10" t="n"/>
+      <c r="P130" s="18" t="inlineStr">
+        <is>
+          <t>QnA-10</t>
+        </is>
+      </c>
+      <c r="Q130" s="18" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-10: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-008-SC1-TC3</t>
+        </is>
+      </c>
+      <c r="B131" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-008-SC1</t>
+        </is>
+      </c>
+      <c r="C131" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-008</t>
+        </is>
+      </c>
+      <c r="D131" s="18" t="inlineStr">
+        <is>
+          <t>FR-SF-02, FR-PR-06</t>
+        </is>
+      </c>
+      <c r="E131" s="18" t="inlineStr">
+        <is>
+          <t>Ranking</t>
+        </is>
+      </c>
+      <c r="F131" s="18" t="inlineStr">
+        <is>
+          <t>Verify "Liên quan nhất" không rơi về sắp xếp mặc định khác (sanity-check AI ranking)</t>
+        </is>
+      </c>
+      <c r="G131" s="18" t="inlineStr">
+        <is>
+          <t>Kết quả "sữa" có nhiều sản phẩm với giá/rating/mức giảm giá khác nhau.</t>
+        </is>
+      </c>
+      <c r="H131" s="18" t="inlineStr">
+        <is>
+          <t>1. Tìm "sữa", giữ nguyên sort mặc định "Liên quan nhất".
+2. Ghi lại thứ tự Top 10 sản phẩm.
+3. So sánh thứ tự này với thứ tự nếu sắp theo Giá tăng dần và theo Tên A-Z.
+4. Xác nhận thứ tự "Liên quan nhất" không trùng khớp hoàn toàn với 2 cách sắp xếp đơn giản trên.</t>
+        </is>
+      </c>
+      <c r="I131" s="18" t="inlineStr">
+        <is>
+          <t>"sữa" (Top 10)</t>
+        </is>
+      </c>
+      <c r="J131" s="18" t="inlineStr">
+        <is>
+          <t>Thứ tự Top 10 theo "Liên quan nhất" khác với thứ tự theo Giá tăng dần và khác thứ tự theo Tên A-Z (trừ trùng ngẫu nhiên hiếm gặp) — xác nhận hệ thống đang áp dụng AI Scorecard Ranking (Relevance/Purchase Affinity/Margin/Promotion/Trending theo BRD) chứ không lặng lẽ fallback về sort đơn giản. Trọng số cụ thể không thể verify độc lập bởi QC — xem QnA-37.</t>
+        </is>
+      </c>
+      <c r="K131" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L131" s="10" t="n"/>
+      <c r="M131" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N131" s="10" t="n"/>
+      <c r="O131" s="10" t="n"/>
+      <c r="P131" s="18" t="inlineStr">
+        <is>
+          <t>QnA-37</t>
+        </is>
+      </c>
+      <c r="Q131" s="18" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-37: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-008-SC1-TC4</t>
+        </is>
+      </c>
+      <c r="B132" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-008-SC1</t>
+        </is>
+      </c>
+      <c r="C132" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-008</t>
+        </is>
+      </c>
+      <c r="D132" s="18" t="inlineStr">
+        <is>
+          <t>FR-SF-02, FR-PR-06</t>
+        </is>
+      </c>
+      <c r="E132" s="18" t="inlineStr">
+        <is>
+          <t>Ranking</t>
+        </is>
+      </c>
+      <c r="F132" s="18" t="inlineStr">
+        <is>
+          <t>Verify "Bán chạy nhất" sắp theo Lượt mua cao nhất giảm dần</t>
+        </is>
+      </c>
+      <c r="G132" s="18" t="inlineStr">
+        <is>
+          <t>Có dữ liệu lượt mua (order/purchase count) khác nhau giữa các SKU trong tập kết quả.</t>
+        </is>
+      </c>
+      <c r="H132" s="18" t="inlineStr">
+        <is>
+          <t>1. Tìm "sữa", chọn Sort = "Bán chạy nhất".
+2. Ghi lại lượt mua (nếu expose được qua API/trang admin) của 5 SKU đầu tiên.
+3. Xác nhận thứ tự giảm dần.</t>
+        </is>
+      </c>
+      <c r="I132" s="18" t="inlineStr">
+        <is>
+          <t>Sort = "Bán chạy nhất"</t>
+        </is>
+      </c>
+      <c r="J132" s="18" t="inlineStr">
+        <is>
+          <t>TBD — 5 SKU đầu tiên phải có lượt mua giảm dần liên tục (SKU sau &lt;= SKU trước); chưa xác định "Lượt mua" tính theo Order Count (giống FR-PS-03) hay Item Quantity, và khung thời gian tính (all-time hay rolling window). Xem QnA-37.</t>
+        </is>
+      </c>
+      <c r="K132" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L132" s="10" t="n"/>
+      <c r="M132" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N132" s="10" t="n"/>
+      <c r="O132" s="10" t="n"/>
+      <c r="P132" s="18" t="inlineStr">
+        <is>
+          <t>QnA-37</t>
+        </is>
+      </c>
+      <c r="Q132" s="18" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-37: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-008-SC1-TC5</t>
+        </is>
+      </c>
+      <c r="B133" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-008-SC1</t>
+        </is>
+      </c>
+      <c r="C133" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-008</t>
+        </is>
+      </c>
+      <c r="D133" s="18" t="inlineStr">
+        <is>
+          <t>FR-SF-02, FR-PR-06</t>
+        </is>
+      </c>
+      <c r="E133" s="18" t="inlineStr">
+        <is>
+          <t>Ranking</t>
+        </is>
+      </c>
+      <c r="F133" s="18" t="inlineStr">
+        <is>
+          <t>Verify "Xem nhiều nhất" sắp theo lượt xem/quan tâm giảm dần</t>
+        </is>
+      </c>
+      <c r="G133" s="18" t="inlineStr">
+        <is>
+          <t>Có dữ liệu lượt xem sản phẩm (page view/PDP view count) khác nhau.</t>
+        </is>
+      </c>
+      <c r="H133" s="18" t="inlineStr">
+        <is>
+          <t>1. Tìm "sữa", chọn Sort = "Xem nhiều nhất".
+2. Ghi lại lượt xem của 5 SKU đầu (nếu expose được).
+3. Xác nhận thứ tự giảm dần.</t>
+        </is>
+      </c>
+      <c r="I133" s="18" t="inlineStr">
+        <is>
+          <t>Sort = "Xem nhiều nhất"</t>
+        </is>
+      </c>
+      <c r="J133" s="18" t="inlineStr">
+        <is>
+          <t>TBD — 5 SKU đầu giảm dần theo lượt xem; chưa rõ "được quan tâm nhiều" tính theo lượt xem PDP, lượt xuất hiện trong kết quả tìm kiếm (impression), hay cả hai, và khung thời gian tính. Xem QnA-37.</t>
+        </is>
+      </c>
+      <c r="K133" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L133" s="10" t="n"/>
+      <c r="M133" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N133" s="10" t="n"/>
+      <c r="O133" s="10" t="n"/>
+      <c r="P133" s="18" t="inlineStr">
+        <is>
+          <t>QnA-37</t>
+        </is>
+      </c>
+      <c r="Q133" s="18" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-37: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-008-SC1-TC6</t>
+        </is>
+      </c>
+      <c r="B134" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-008-SC1</t>
+        </is>
+      </c>
+      <c r="C134" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-008</t>
+        </is>
+      </c>
+      <c r="D134" s="9" t="inlineStr">
+        <is>
+          <t>FR-SF-02, FR-PR-06</t>
+        </is>
+      </c>
+      <c r="E134" s="9" t="inlineStr">
+        <is>
+          <t>Ranking</t>
+        </is>
+      </c>
+      <c r="F134" s="9" t="inlineStr">
+        <is>
+          <t>Verify "Giảm giá nhiều nhất" sắp theo % khuyến mãi giảm dần</t>
+        </is>
+      </c>
+      <c r="G134" s="9" t="inlineStr">
+        <is>
+          <t>Có SKU với % giảm giá khác nhau (kể cả SKU không giảm giá = 0%) trong tập kết quả.</t>
+        </is>
+      </c>
+      <c r="H134" s="9" t="inlineStr">
+        <is>
+          <t>1. Tìm "sữa", chọn Sort = "Giảm giá nhiều nhất".
+2. Ghi lại % giảm giá hiển thị trên badge của 5-10 SKU đầu.
+3. Xác nhận thứ tự % giảm dần; kiểm tra SKU 0% giảm giá bị đẩy xuống cuối.</t>
+        </is>
+      </c>
+      <c r="I134" s="9" t="inlineStr">
+        <is>
+          <t>Sort = "Giảm giá nhiều nhất"</t>
+        </is>
+      </c>
+      <c r="J134" s="9" t="inlineStr">
+        <is>
+          <t>% giảm giá giảm dần liên tục từ SKU đầu; SKU không có khuyến mãi (0%) nằm ở cuối danh sách, không xen giữa các SKU có giảm giá.</t>
+        </is>
+      </c>
+      <c r="K134" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L134" s="10" t="n"/>
+      <c r="M134" s="10" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N134" s="10" t="n"/>
+      <c r="O134" s="10" t="n"/>
+      <c r="P134" s="9" t="n"/>
+      <c r="Q134" s="9" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-008-SC1-TC7</t>
+        </is>
+      </c>
+      <c r="B135" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-008-SC1</t>
+        </is>
+      </c>
+      <c r="C135" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-008</t>
+        </is>
+      </c>
+      <c r="D135" s="18" t="inlineStr">
+        <is>
+          <t>FR-SF-02, FR-PR-06</t>
+        </is>
+      </c>
+      <c r="E135" s="18" t="inlineStr">
+        <is>
+          <t>Ranking</t>
+        </is>
+      </c>
+      <c r="F135" s="18" t="inlineStr">
+        <is>
+          <t>Verify "Đánh giá cao nhất" sắp theo sao trung bình giảm dần</t>
+        </is>
+      </c>
+      <c r="G135" s="18" t="inlineStr">
+        <is>
+          <t>Có SKU với số sao trung bình và số lượng review khác nhau (kể cả SKU 5 sao nhưng chỉ 1 review, và SKU 4.8 sao với 1000 review).</t>
+        </is>
+      </c>
+      <c r="H135" s="18" t="inlineStr">
+        <is>
+          <t>1. Tìm "sữa", chọn Sort = "Đánh giá cao nhất".
+2. Ghi lại sao trung bình của 5-10 SKU đầu.
+3. Kiểm tra SKU có rất ít review (VD 1 review 5 sao) có đứng trên SKU nhiều review hơn nhưng sao trung bình thấp hơn một chút không.</t>
+        </is>
+      </c>
+      <c r="I135" s="18" t="inlineStr">
+        <is>
+          <t>Sort = "Đánh giá cao nhất"</t>
+        </is>
+      </c>
+      <c r="J135" s="18" t="inlineStr">
+        <is>
+          <t>TBD — sao trung bình phải giảm dần; chưa xác nhận có áp dụng cơ chế làm mượt theo số lượng review (Bayesian/weighted average) để tránh 1 SKU-1-review-5-sao áp đảo SKU nhiều review hơn nhưng trung bình thấp hơn một chút, hay chỉ lấy đúng giá trị trung bình thô. Xem QnA-37.</t>
+        </is>
+      </c>
+      <c r="K135" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L135" s="10" t="n"/>
+      <c r="M135" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N135" s="10" t="n"/>
+      <c r="O135" s="10" t="n"/>
+      <c r="P135" s="18" t="inlineStr">
+        <is>
+          <t>QnA-37</t>
+        </is>
+      </c>
+      <c r="Q135" s="18" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-37: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-008-SC1-TC8</t>
+        </is>
+      </c>
+      <c r="B136" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-008-SC1</t>
+        </is>
+      </c>
+      <c r="C136" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-008</t>
+        </is>
+      </c>
+      <c r="D136" s="18" t="inlineStr">
+        <is>
+          <t>FR-SF-02, FR-PR-06</t>
+        </is>
+      </c>
+      <c r="E136" s="18" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F136" s="18" t="inlineStr">
+        <is>
+          <t>Verify "Giá từ thấp đến cao" sắp theo giá tăng dần, có xử lý trùng giá</t>
+        </is>
+      </c>
+      <c r="G136" s="18" t="inlineStr">
+        <is>
+          <t>Có ≥2 SKU trùng giá chính xác trong tập kết quả.</t>
+        </is>
+      </c>
+      <c r="H136" s="18" t="inlineStr">
+        <is>
+          <t>1. Tìm "sữa", chọn Sort = "Giá từ thấp đến cao".
+2. Ghi lại giá của toàn bộ Top 10.
+3. Xác nhận giá tăng dần liên tục (SKU sau &gt;= SKU trước).
+4. Với các SKU trùng giá, ghi nhận thứ tự phụ (tie-break) hiện tại.</t>
+        </is>
+      </c>
+      <c r="I136" s="18" t="inlineStr">
+        <is>
+          <t>Sort = "Giá từ thấp đến cao"</t>
+        </is>
+      </c>
+      <c r="J136" s="18" t="inlineStr">
+        <is>
+          <t>TBD — giá phải tăng dần liên tục trong toàn bộ danh sách; quy tắc tie-break khi nhiều SKU trùng giá chính xác (theo Relevance? theo thời gian tạo SKU? theo Product ID?) chưa được BRD quy định. Xem QnA-37.</t>
+        </is>
+      </c>
+      <c r="K136" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L136" s="10" t="n"/>
+      <c r="M136" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N136" s="10" t="n"/>
+      <c r="O136" s="10" t="n"/>
+      <c r="P136" s="18" t="inlineStr">
+        <is>
+          <t>QnA-37</t>
+        </is>
+      </c>
+      <c r="Q136" s="18" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-37: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-008-SC1-TC9</t>
+        </is>
+      </c>
+      <c r="B137" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-008-SC1</t>
+        </is>
+      </c>
+      <c r="C137" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-008</t>
+        </is>
+      </c>
+      <c r="D137" s="9" t="inlineStr">
+        <is>
+          <t>FR-SF-02, FR-PR-06</t>
+        </is>
+      </c>
+      <c r="E137" s="9" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F137" s="9" t="inlineStr">
+        <is>
+          <t>Verify "Giá từ cao đến thấp" sắp theo giá giảm dần</t>
+        </is>
+      </c>
+      <c r="G137" s="9" t="inlineStr">
+        <is>
+          <t>Tập kết quả có biên độ giá đa dạng.</t>
+        </is>
+      </c>
+      <c r="H137" s="9" t="inlineStr">
+        <is>
+          <t>1. Tìm "sữa", chọn Sort = "Giá từ cao đến thấp".
+2. Ghi lại giá Top 10.
+3. Xác nhận giá giảm dần liên tục, và đúng là thứ tự đảo ngược so với TC8 ("Giá thấp-cao") trên cùng tập kết quả.</t>
+        </is>
+      </c>
+      <c r="I137" s="9" t="inlineStr">
+        <is>
+          <t>Sort = "Giá từ cao đến thấp"</t>
+        </is>
+      </c>
+      <c r="J137" s="9" t="inlineStr">
+        <is>
+          <t>Giá giảm dần liên tục; thứ tự SKU đúng bằng thứ tự đảo ngược của Sort "Giá thấp-cao" trên cùng 1 tập kết quả (không lệch SKU nào).</t>
+        </is>
+      </c>
+      <c r="K137" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L137" s="10" t="n"/>
+      <c r="M137" s="10" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N137" s="10" t="n"/>
+      <c r="O137" s="10" t="n"/>
+      <c r="P137" s="9" t="n"/>
+      <c r="Q137" s="9" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-008-SC1-TC10</t>
+        </is>
+      </c>
+      <c r="B138" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-008-SC1</t>
+        </is>
+      </c>
+      <c r="C138" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-008</t>
+        </is>
+      </c>
+      <c r="D138" s="9" t="inlineStr">
+        <is>
+          <t>FR-SF-02, FR-PR-06</t>
+        </is>
+      </c>
+      <c r="E138" s="9" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F138" s="9" t="inlineStr">
+        <is>
+          <t>Verify "Tên sản phẩm (A-Z)" sắp theo bảng chữ cái, xử lý dấu tiếng Việt</t>
+        </is>
+      </c>
+      <c r="G138" s="9" t="inlineStr">
+        <is>
+          <t>Tập kết quả có tên SKU bắt đầu bằng cả chữ có dấu và không dấu, hoặc chữ hoa/thường lẫn lộn.</t>
+        </is>
+      </c>
+      <c r="H138" s="9" t="inlineStr">
+        <is>
+          <t>1. Tìm "sữa", chọn Sort = "Tên sản phẩm (A-Z)".
+2. Ghi lại tên Top 10-15 SKU.
+3. Xác nhận thứ tự đúng bảng chữ cái tiếng Việt (xử lý dấu: a, à, á, ả, ã, ạ, ă,... đúng vị trí theo chuẩn sắp xếp tiếng Việt, không phải theo mã Unicode thô).</t>
+        </is>
+      </c>
+      <c r="I138" s="9" t="inlineStr">
+        <is>
+          <t>Sort = "Tên sản phẩm (A-Z)"</t>
+        </is>
+      </c>
+      <c r="J138" s="9" t="inlineStr">
+        <is>
+          <t>Thứ tự đúng chuẩn sắp xếp bảng chữ cái tiếng Việt (collation), không sắp theo mã Unicode thô (dễ sai vì ký tự có dấu nằm sau ký tự ASCII trong bảng Unicode); không phân biệt hoa/thường gây lệch thứ tự bất hợp lý.</t>
+        </is>
+      </c>
+      <c r="K138" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L138" s="10" t="n"/>
+      <c r="M138" s="10" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N138" s="10" t="n"/>
+      <c r="O138" s="10" t="n"/>
+      <c r="P138" s="9" t="n"/>
+      <c r="Q138" s="9" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-008-SC2-TC2</t>
+        </is>
+      </c>
+      <c r="B139" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-008-SC2</t>
+        </is>
+      </c>
+      <c r="C139" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-008</t>
+        </is>
+      </c>
+      <c r="D139" s="9" t="inlineStr">
+        <is>
+          <t>FR-SF-02, FR-PR-06</t>
+        </is>
+      </c>
+      <c r="E139" s="9" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F139" s="9" t="inlineStr">
+        <is>
+          <t>Chạm nút "X" trên header Sort sheet đóng lại, giữ nguyên lựa chọn cũ (song song hành vi tap ra ngoài ở TC1)</t>
+        </is>
+      </c>
+      <c r="G139" s="9" t="inlineStr">
+        <is>
+          <t>Sort bottom sheet đang mở, tiêu chí hiện tại = "Liên quan nhất".</t>
+        </is>
+      </c>
+      <c r="H139" s="9" t="inlineStr">
+        <is>
+          <t>1. Mở Sort sheet (đang chọn "Liên quan nhất").
+2. Chạm nút "X" ở góc trên bên phải header sheet (không chọn tiêu chí nào khác, không tap ra ngoài).
+3. Quan sát nhãn trên thanh sticky sau khi sheet đóng.</t>
+        </is>
+      </c>
+      <c r="I139" s="9" t="inlineStr">
+        <is>
+          <t>Tap "X" trên header</t>
+        </is>
+      </c>
+      <c r="J139" s="9" t="inlineStr">
+        <is>
+          <t>Sheet đóng lại; nhãn trên thanh sticky vẫn là "Liên quan nhất"; không có truy vấn mới nào được gọi — hành vi giống hệt cách đóng bằng tap-ra-ngoài đã test ở SC2-TC1, đảm bảo cả 2 cách đóng (tap ngoài / nút X) đều nhất quán.</t>
+        </is>
+      </c>
+      <c r="K139" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L139" s="10" t="n"/>
+      <c r="M139" s="10" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N139" s="10" t="n"/>
+      <c r="O139" s="10" t="n"/>
+      <c r="P139" s="9" t="n"/>
+      <c r="Q139" s="9" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC3-TC2</t>
+        </is>
+      </c>
+      <c r="B140" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC3</t>
+        </is>
+      </c>
+      <c r="C140" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-009</t>
+        </is>
+      </c>
+      <c r="D140" s="18" t="inlineStr">
+        <is>
+          <t>FR-SF-01, FR-SF-04</t>
+        </is>
+      </c>
+      <c r="E140" s="18" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="F140" s="18" t="inlineStr">
+        <is>
+          <t>Verify quy tắc sinh &amp; sắp xếp chip Nhãn (Information Gain) — TBD</t>
+        </is>
+      </c>
+      <c r="G140" s="18" t="inlineStr">
+        <is>
+          <t>Tab Nhãn hiển thị danh sách chip (nguồn dữ liệu chung với Smart Filter Chips trên trang kết quả, theo FR-SF-04 "Dựa vào danh sách smart filter").</t>
+        </is>
+      </c>
+      <c r="H140" s="18" t="inlineStr">
+        <is>
+          <t>1. Tìm "sữa", mở Bộ lọc, chuyển tab Nhãn.
+2. Ghi lại thứ tự hiển thị của toàn bộ chip trong tab.
+3. So sánh thứ tự này với khối Smart Filter Chips hiển thị trực tiếp trên trang kết quả (SS-SCR-005-SC9) cho cùng từ khoá.
+4. Đổi sang từ khoá khác (VD "bia"), lặp lại bước 1-2, quan sát bộ chip sinh ra có đổi theo đúng từ khoá mới không.</t>
+        </is>
+      </c>
+      <c r="I140" s="18" t="inlineStr">
+        <is>
+          <t>"sữa" vs "bia"</t>
+        </is>
+      </c>
+      <c r="J140" s="18" t="inlineStr">
+        <is>
+          <t>TBD — FR-SF-03 chỉ mô tả "AI bốc ra tối đa 10 Tag lọc thông minh có Information Gain cao nhất... cấu trúc phẳng", không mô tả công thức tính, ngưỡng tối thiểu, hay thứ tự hiển thị. Yêu cầu tối thiểu: bộ chip phải đổi theo đúng từ khoá (không static), và thứ tự chip giữa tab Nhãn và khối Smart Filter Chips trên trang kết quả phải nhất quán với nhau (cùng 1 nguồn dữ liệu). Không chấm Pass/Fail chi tiết cho tới khi xác nhận công thức. Xem QnA-38.</t>
+        </is>
+      </c>
+      <c r="K140" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L140" s="10" t="n"/>
+      <c r="M140" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N140" s="10" t="n"/>
+      <c r="O140" s="10" t="n"/>
+      <c r="P140" s="18" t="inlineStr">
+        <is>
+          <t>QnA-38</t>
+        </is>
+      </c>
+      <c r="Q140" s="18" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-38: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC6-TC1</t>
+        </is>
+      </c>
+      <c r="B141" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC6</t>
+        </is>
+      </c>
+      <c r="C141" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-009</t>
+        </is>
+      </c>
+      <c r="D141" s="9" t="inlineStr">
+        <is>
+          <t>FR-SF-01, FR-SF-04</t>
+        </is>
+      </c>
+      <c r="E141" s="9" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F141" s="9" t="inlineStr">
+        <is>
+          <t>Badge tab độc quyền (Danh mục/Giao hàng/Đánh giá/Giá) luôn tối đa 1</t>
+        </is>
+      </c>
+      <c r="G141" s="9" t="inlineStr">
+        <is>
+          <t>Chưa chọn điều kiện nào trong 4 tab độc quyền (chỉ chọn 1 giá trị/tab).</t>
+        </is>
+      </c>
+      <c r="H141" s="9" t="inlineStr">
+        <is>
+          <t>1. Mở Bộ lọc.
+2. Chọn 1 nhánh Danh mục, quan sát badge tab Danh mục.
+3. Chọn 1 mức Đánh giá, quan sát badge tab Đánh giá.
+4. Chọn 1 điều kiện Giao hàng và 1 khoảng Giá, quan sát badge 2 tab tương ứng.
+5. Chọn nhánh Danh mục khác (thay thế), quan sát badge tab Danh mục có tăng lên 2 không.</t>
+        </is>
+      </c>
+      <c r="I141" s="9" t="inlineStr">
+        <is>
+          <t>1 lựa chọn/tab, sau đó đổi Danh mục</t>
+        </is>
+      </c>
+      <c r="J141" s="9" t="inlineStr">
+        <is>
+          <t>Mỗi tab độc quyền hiển thị badge đúng "1" khi có 1 lựa chọn; bước 5: đổi sang nhánh Danh mục khác KHÔNG làm badge tăng lên "2" (vẫn là "1", vì thay thế chứ không cộng dồn — đúng bản chất độc quyền/chỉ chọn 1 của tab này).</t>
+        </is>
+      </c>
+      <c r="K141" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L141" s="10" t="n"/>
+      <c r="M141" s="10" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N141" s="10" t="n"/>
+      <c r="O141" s="10" t="n"/>
+      <c r="P141" s="9" t="n"/>
+      <c r="Q141" s="9" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC6-TC2</t>
+        </is>
+      </c>
+      <c r="B142" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC6</t>
+        </is>
+      </c>
+      <c r="C142" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-009</t>
+        </is>
+      </c>
+      <c r="D142" s="9" t="inlineStr">
+        <is>
+          <t>FR-SF-01, FR-SF-04</t>
+        </is>
+      </c>
+      <c r="E142" s="9" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F142" s="9" t="inlineStr">
+        <is>
+          <t>Badge tab Nhãn (đa chọn) đếm đúng số chip đang active</t>
+        </is>
+      </c>
+      <c r="G142" s="9" t="inlineStr">
+        <is>
+          <t>Chưa chọn chip Nhãn nào.</t>
+        </is>
+      </c>
+      <c r="H142" s="9" t="inlineStr">
+        <is>
+          <t>1. Mở Bộ lọc, tab Nhãn.
+2. Chọn lần lượt "Không đường", "Ít đường", "Hữu cơ" — quan sát badge tab Nhãn sau mỗi lần chọn.
+3. Bỏ chọn "Ít đường", quan sát badge.</t>
+        </is>
+      </c>
+      <c r="I142" s="9" t="inlineStr">
+        <is>
+          <t>Chọn 3 chip → bỏ 1 chip</t>
+        </is>
+      </c>
+      <c r="J142" s="9" t="inlineStr">
+        <is>
+          <t>Badge tab Nhãn tăng đúng theo số chip: 0→1→2→3 sau mỗi lần chọn; giảm về 2 sau khi bỏ "Ít đường" — khớp với ảnh Figma thực tế (3 chip active → badge tab Nhãn hiển thị đúng "3").</t>
+        </is>
+      </c>
+      <c r="K142" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L142" s="10" t="n"/>
+      <c r="M142" s="10" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N142" s="10" t="n"/>
+      <c r="O142" s="10" t="n"/>
+      <c r="P142" s="9" t="n"/>
+      <c r="Q142" s="9" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC6-TC3</t>
+        </is>
+      </c>
+      <c r="B143" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC6</t>
+        </is>
+      </c>
+      <c r="C143" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-009</t>
+        </is>
+      </c>
+      <c r="D143" s="18" t="inlineStr">
+        <is>
+          <t>FR-SF-01, FR-SF-04</t>
+        </is>
+      </c>
+      <c r="E143" s="18" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F143" s="18" t="inlineStr">
+        <is>
+          <t>Badge tổng trên nút "Bộ lọc" ở trang kết quả — TBD có tồn tại hay không</t>
+        </is>
+      </c>
+      <c r="G143" s="18" t="inlineStr">
+        <is>
+          <t>Đã áp dụng 3 điều kiện (Nhãn: Không đường + Ít đường + Hữu cơ) và tap "Áp dụng".</t>
+        </is>
+      </c>
+      <c r="H143" s="18" t="inlineStr">
+        <is>
+          <t>1. Áp dụng 3 chip Nhãn như trên, tap "Áp dụng".
+2. Quan sát nút "Bộ lọc" trên thanh sticky của trang kết quả (bên ngoài sheet).
+3. Kiểm tra có badge số nào hiển thị cạnh nút "Bộ lọc" hay không.</t>
+        </is>
+      </c>
+      <c r="I143" s="18" t="inlineStr">
+        <is>
+          <t>3 điều kiện đã áp dụng</t>
+        </is>
+      </c>
+      <c r="J143" s="18" t="inlineStr">
+        <is>
+          <t>TBD — ảnh Figma thực tế (Text Search.png) cho thấy nút "Bộ lọc" trên trang kết quả KHÔNG có badge số nào ngay cả khi đã áp dụng 3 điều kiện, mâu thuẫn với giả định "badge nút Bộ lọc = tổng số điều kiện" đang dùng trong SS-SCR-009-SC1-TC1 và toàn bộ SS-SCR-010. Không chấm Pass/Fail cho tới khi BA/UX xác nhận phiên bản Figma nào là chính thức. Xem QnA-39.</t>
+        </is>
+      </c>
+      <c r="K143" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L143" s="10" t="n"/>
+      <c r="M143" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N143" s="10" t="n"/>
+      <c r="O143" s="10" t="n"/>
+      <c r="P143" s="18" t="inlineStr">
+        <is>
+          <t>QnA-39</t>
+        </is>
+      </c>
+      <c r="Q143" s="18" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-39: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC7-TC1</t>
+        </is>
+      </c>
+      <c r="B144" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC7</t>
+        </is>
+      </c>
+      <c r="C144" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-009</t>
+        </is>
+      </c>
+      <c r="D144" s="9" t="inlineStr">
+        <is>
+          <t>FR-SF-01, FR-SF-04</t>
+        </is>
+      </c>
+      <c r="E144" s="9" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F144" s="9" t="inlineStr">
+        <is>
+          <t>"Thiết lập lại" xoá toàn bộ lựa chọn trong sheet, sheet vẫn mở</t>
+        </is>
+      </c>
+      <c r="G144" s="9" t="inlineStr">
+        <is>
+          <t>Đã chọn nhiều điều kiện ở nhiều tab (Danh mục, Nhãn x3, Đánh giá) nhưng CHƯA tap Áp dụng.</t>
+        </is>
+      </c>
+      <c r="H144" s="9" t="inlineStr">
+        <is>
+          <t>1. Chọn 1 Danh mục + 3 chip Nhãn + 1 mức Đánh giá trong Bộ lọc (chưa Áp dụng).
+2. Tap nút "Thiết lập lại".
+3. Quan sát trạng thái các tab (badge, chip, radio) và trạng thái sheet (đóng hay vẫn mở) ngay sau khi tap.</t>
+        </is>
+      </c>
+      <c r="I144" s="9" t="inlineStr">
+        <is>
+          <t>5 điều kiện đã chọn → tap Thiết lập lại</t>
+        </is>
+      </c>
+      <c r="J144" s="9" t="inlineStr">
+        <is>
+          <t>Toàn bộ badge từng tab về 0/ẩn; toàn bộ chip/radio đã chọn quay về trạng thái chưa chọn; sheet KHÔNG tự đóng, khách vẫn đang ở Bộ lọc với danh sách trống để chọn lại từ đầu nếu muốn.</t>
+        </is>
+      </c>
+      <c r="K144" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L144" s="10" t="n"/>
+      <c r="M144" s="10" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N144" s="10" t="n"/>
+      <c r="O144" s="10" t="n"/>
+      <c r="P144" s="9" t="n"/>
+      <c r="Q144" s="9" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC7-TC2</t>
+        </is>
+      </c>
+      <c r="B145" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC7</t>
+        </is>
+      </c>
+      <c r="C145" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-009</t>
+        </is>
+      </c>
+      <c r="D145" s="9" t="inlineStr">
+        <is>
+          <t>FR-SF-01, FR-SF-04</t>
+        </is>
+      </c>
+      <c r="E145" s="9" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F145" s="9" t="inlineStr">
+        <is>
+          <t>Tap "Áp dụng" ngay sau "Thiết lập lại" (0 điều kiện) trả kết quả về tập đầy đủ</t>
+        </is>
+      </c>
+      <c r="G145" s="9" t="inlineStr">
+        <is>
+          <t>Đang có 1 filter cũ active ("Không đường") trên trang kết quả trước khi mở lại Bộ lọc.</t>
+        </is>
+      </c>
+      <c r="H145" s="9" t="inlineStr">
+        <is>
+          <t>1. Trên trang kết quả đang lọc "Không đường", mở lại Bộ lọc.
+2. Tap "Thiết lập lại" (xoá "Không đường" khỏi sheet).
+3. Tap "Áp dụng".
+4. Quan sát trang kết quả và badge nút Bộ lọc/tab.</t>
+        </is>
+      </c>
+      <c r="I145" s="9" t="inlineStr">
+        <is>
+          <t>Filter cũ="Không đường" → Thiết lập lại → Áp dụng</t>
+        </is>
+      </c>
+      <c r="J145" s="9" t="inlineStr">
+        <is>
+          <t>Sheet đóng; trang kết quả quay về tập đầy đủ chưa lọc (tương đương trạng thái "Xoá bộ lọc" ở SS-SCR-010-SC3); không còn chip "Không đường" nào active trên trang kết quả.</t>
+        </is>
+      </c>
+      <c r="K145" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L145" s="10" t="n"/>
+      <c r="M145" s="10" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N145" s="10" t="n"/>
+      <c r="O145" s="10" t="n"/>
+      <c r="P145" s="9" t="n"/>
+      <c r="Q145" s="9" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC7-TC3</t>
+        </is>
+      </c>
+      <c r="B146" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC7</t>
+        </is>
+      </c>
+      <c r="C146" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-009</t>
+        </is>
+      </c>
+      <c r="D146" s="9" t="inlineStr">
+        <is>
+          <t>FR-SF-01, FR-SF-04</t>
+        </is>
+      </c>
+      <c r="E146" s="9" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F146" s="9" t="inlineStr">
+        <is>
+          <t>Tap "Áp dụng" khi không đổi gì so với trạng thái đang áp dụng (no-op)</t>
+        </is>
+      </c>
+      <c r="G146" s="9" t="inlineStr">
+        <is>
+          <t>Đang áp dụng filter "Hữu cơ" trên trang kết quả.</t>
+        </is>
+      </c>
+      <c r="H146" s="9" t="inlineStr">
+        <is>
+          <t>1. Mở lại Bộ lọc trong khi "Hữu cơ" đang active.
+2. Không thay đổi gì, tap thẳng "Áp dụng".
+3. Quan sát UI (có giật/nhấp nháy không) và kết quả.</t>
+        </is>
+      </c>
+      <c r="I146" s="9" t="inlineStr">
+        <is>
+          <t>Filter="Hữu cơ" không đổi → tap Áp dụng</t>
+        </is>
+      </c>
+      <c r="J146" s="9" t="inlineStr">
+        <is>
+          <t>Sheet đóng bình thường, không có lỗi/giật UI; kết quả và badge giữ nguyên như trước khi mở sheet — hành vi no-op nhất quán với cách xử lý đã test ở SS-SCR-008-SC3 (chọn lại tiêu chí Sort đang active).</t>
+        </is>
+      </c>
+      <c r="K146" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L146" s="10" t="n"/>
+      <c r="M146" s="10" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N146" s="10" t="n"/>
+      <c r="O146" s="10" t="n"/>
+      <c r="P146" s="9" t="n"/>
+      <c r="Q146" s="9" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC8-TC1</t>
+        </is>
+      </c>
+      <c r="B147" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC8</t>
+        </is>
+      </c>
+      <c r="C147" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-009</t>
+        </is>
+      </c>
+      <c r="D147" s="9" t="inlineStr">
+        <is>
+          <t>FR-SF-04</t>
+        </is>
+      </c>
+      <c r="E147" s="9" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F147" s="9" t="inlineStr">
+        <is>
+          <t>Tap 1 tab chuyển đúng nội dung panel và cập nhật trạng thái active</t>
+        </is>
+      </c>
+      <c r="G147" s="9" t="inlineStr">
+        <is>
+          <t>Bảng Bộ lọc vừa mở, tab "Danh mục" đang active mặc định.</t>
+        </is>
+      </c>
+      <c r="H147" s="9" t="inlineStr">
+        <is>
+          <t>1. Mở Bộ lọc, quan sát tab "Danh mục" đang active (viền trái đỏ, chữ đậm đỏ) và panel bên phải hiển thị nội dung Danh mục.
+2. Tap tab "Nhãn".
+3. Quan sát tab "Nhãn" có chuyển sang active không, tab "Danh mục" có về trạng thái không active không, và panel bên phải có đổi sang nội dung Nhãn không.
+4. Lặp lại với tab "Giao hàng", "Đánh giá", "Giá".</t>
+        </is>
+      </c>
+      <c r="I147" s="9" t="inlineStr">
+        <is>
+          <t>Tap lần lượt 5 tab</t>
+        </is>
+      </c>
+      <c r="J147" s="9" t="inlineStr">
+        <is>
+          <t>Mỗi lần tap, đúng 1 tab được đánh dấu active (viền trái đỏ + chữ đậm đỏ), các tab còn lại về trạng thái mặc định; panel bên phải luôn hiển thị đúng nội dung của tab đang active, không có độ trễ/nội dung tab cũ còn sót lại.</t>
+        </is>
+      </c>
+      <c r="K147" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L147" s="10" t="n"/>
+      <c r="M147" s="10" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N147" s="10" t="n"/>
+      <c r="O147" s="10" t="n"/>
+      <c r="P147" s="9" t="n"/>
+      <c r="Q147" s="9" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC8-TC2</t>
+        </is>
+      </c>
+      <c r="B148" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC8</t>
+        </is>
+      </c>
+      <c r="C148" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-009</t>
+        </is>
+      </c>
+      <c r="D148" s="9" t="inlineStr">
+        <is>
+          <t>FR-SF-04</t>
+        </is>
+      </c>
+      <c r="E148" s="9" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F148" s="9" t="inlineStr">
+        <is>
+          <t>Chuyển tab qua lại không làm mất lựa chọn/badge của tab đã chọn trước đó</t>
+        </is>
+      </c>
+      <c r="G148" s="9" t="inlineStr">
+        <is>
+          <t>Bảng Bộ lọc đang mở.</t>
+        </is>
+      </c>
+      <c r="H148" s="9" t="inlineStr">
+        <is>
+          <t>1. Ở tab "Nhãn", chọn 2 chip "Không đường" và "Hữu cơ" (badge tab Nhãn = 2).
+2. Chuyển sang tab "Đánh giá", chọn "Từ 4 sao trở lên" (badge tab Đánh giá = 1).
+3. Chuyển sang tab "Giá", không chọn gì.
+4. Quay lại tab "Nhãn", kiểm tra 2 chip đã chọn trước đó và badge.
+5. Quay lại tab "Đánh giá", kiểm tra lựa chọn và badge.</t>
+        </is>
+      </c>
+      <c r="I148" s="9" t="inlineStr">
+        <is>
+          <t>Nhãn=2 chip, Đánh giá=1 mức, chuyển qua Giá rồi quay lại</t>
+        </is>
+      </c>
+      <c r="J148" s="9" t="inlineStr">
+        <is>
+          <t>Sau khi chuyển qua nhiều tab và quay lại, tab "Nhãn" vẫn hiển thị đúng 2 chip đã chọn ở trạng thái active và badge vẫn = 2; tab "Đánh giá" vẫn giữ đúng lựa chọn "Từ 4 sao trở lên" và badge = 1 — không có lựa chọn nào bị mất hay reset khi chuyển tab qua lại (chỉ mất khi tap "Thiết lập lại" hoặc đóng bằng (✕), đã test riêng ở SC7/SC5).</t>
+        </is>
+      </c>
+      <c r="K148" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L148" s="10" t="n"/>
+      <c r="M148" s="10" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N148" s="10" t="n"/>
+      <c r="O148" s="10" t="n"/>
+      <c r="P148" s="9" t="n"/>
+      <c r="Q148" s="9" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC4-TC2</t>
+        </is>
+      </c>
+      <c r="B149" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC4</t>
+        </is>
+      </c>
+      <c r="C149" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-009</t>
+        </is>
+      </c>
+      <c r="D149" s="9" t="inlineStr">
+        <is>
+          <t>FR-SF-01, FR-SF-04</t>
+        </is>
+      </c>
+      <c r="E149" s="9" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F149" s="9" t="inlineStr">
+        <is>
+          <t>Chọn danh mục cha hiển thị đúng "Tất cả trong [Tên danh mục]", áp dụng cho toàn bộ nhánh</t>
+        </is>
+      </c>
+      <c r="G149" s="9" t="inlineStr">
+        <is>
+          <t>Cây danh mục có ≥1 nhánh cấp cha với nhiều danh mục con.</t>
+        </is>
+      </c>
+      <c r="H149" s="9" t="inlineStr">
+        <is>
+          <t>1. Ở tab Danh mục, drill-down vào "Thực phẩm &amp; Đồ uống" › "Sữa &amp; Trứng".
+2. Quan sát lựa chọn đầu tiên trong danh sách danh mục con.
+3. Chọn lựa chọn đó, tap Áp dụng.
+4. Kiểm tra phạm vi kết quả trả về (có gồm cả Sữa tươi, Sữa hạt, Sữa đậu nành, Sữa chua, Trứng hay chỉ 1 danh mục con cụ thể).</t>
+        </is>
+      </c>
+      <c r="I149" s="9" t="inlineStr">
+        <is>
+          <t>Drill-down "Sữa &amp; Trứng" → chọn "Tất cả trong 'Sữa &amp; Trứng'"</t>
+        </is>
+      </c>
+      <c r="J149" s="9" t="inlineStr">
+        <is>
+          <t>Danh sách con hiển thị đúng 1 lựa chọn radio "Tất cả trong 'Sữa &amp; Trứng'" ở đầu (mặc định được chọn sẵn), phía trên các danh mục con cụ thể (Sữa tươi, Sữa hạt, Sữa đậu nành, Sữa chua, Trứng) — khớp với ảnh Figma thực tế; chọn lựa chọn này trả về kết quả thuộc TOÀN BỘ nhánh "Sữa &amp; Trứng" (gồm mọi danh mục con), không thu hẹp về 1 danh mục con riêng lẻ nào.</t>
+        </is>
+      </c>
+      <c r="K149" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L149" s="10" t="n"/>
+      <c r="M149" s="10" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N149" s="10" t="n"/>
+      <c r="O149" s="10" t="n"/>
+      <c r="P149" s="9" t="n"/>
+      <c r="Q149" s="9" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC4-TC3</t>
+        </is>
+      </c>
+      <c r="B150" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC4</t>
+        </is>
+      </c>
+      <c r="C150" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-009</t>
+        </is>
+      </c>
+      <c r="D150" s="18" t="inlineStr">
+        <is>
+          <t>FR-SF-01, FR-SF-04</t>
+        </is>
+      </c>
+      <c r="E150" s="18" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+      <c r="F150" s="18" t="inlineStr">
+        <is>
+          <t>Tap breadcrumb "‹ Tất cả danh mục" — TBD hành vi quay về root và có bỏ chọn Danh mục hay không</t>
+        </is>
+      </c>
+      <c r="G150" s="18" t="inlineStr">
+        <is>
+          <t>Đang ở cấp con sâu (VD "Thực phẩm &amp; Đồ uống › Sữa &amp; Trứng") với "Tất cả trong 'Sữa &amp; Trứng'" đã được chọn.</t>
+        </is>
+      </c>
+      <c r="H150" s="18" t="inlineStr">
+        <is>
+          <t>1. Drill-down vào "Thực phẩm &amp; Đồ uống › Sữa &amp; Trứng", chọn "Tất cả trong 'Sữa &amp; Trứng'" (chưa tap Áp dụng).
+2. Tap breadcrumb "‹ Tất cả danh mục" ở đầu.
+3. Quan sát danh sách hiển thị lại (có về đúng cấp cao nhất: Thực phẩm &amp; Đồ uống, Mẹ &amp; Bé, Tươi sống... không).
+4. Kiểm tra badge tab Danh mục và trạng thái lựa chọn "Tất cả trong 'Sữa &amp; Trứng'" còn được đánh dấu chọn hay không.</t>
+        </is>
+      </c>
+      <c r="I150" s="18" t="inlineStr">
+        <is>
+          <t>Tap "‹ Tất cả danh mục" sau khi đã chọn "Tất cả trong 'Sữa &amp; Trứng'"</t>
+        </is>
+      </c>
+      <c r="J150" s="18" t="inlineStr">
+        <is>
+          <t>TBD — chưa xác nhận tap "‹ Tất cả danh mục" có (a) quay về danh sách danh mục cấp cao nhất VÀ đồng thời bỏ chọn hoàn toàn lựa chọn Danh mục đang có (badge về 0), hay (b) chỉ điều hướng UI về root mà KHÔNG bỏ chọn lựa chọn đã xác nhận trước đó (badge vẫn giữ nguyên). Không chấm Pass/Fail cho tới khi xác nhận. Xem QnA-40.</t>
+        </is>
+      </c>
+      <c r="K150" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L150" s="10" t="n"/>
+      <c r="M150" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N150" s="10" t="n"/>
+      <c r="O150" s="10" t="n"/>
+      <c r="P150" s="18" t="inlineStr">
+        <is>
+          <t>QnA-40</t>
+        </is>
+      </c>
+      <c r="Q150" s="18" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-40: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC2-TC2</t>
+        </is>
+      </c>
+      <c r="B151" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC2</t>
+        </is>
+      </c>
+      <c r="C151" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-009</t>
+        </is>
+      </c>
+      <c r="D151" s="18" t="inlineStr">
+        <is>
+          <t>FR-SF-01, FR-SF-04</t>
+        </is>
+      </c>
+      <c r="E151" s="18" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F151" s="18" t="inlineStr">
+        <is>
+          <t>Verify 3 preset percentile giá (&lt;30% thấp / 30-70% trung bình / &gt;70% cao) tính đúng theo tập kết quả hiện tại</t>
+        </is>
+      </c>
+      <c r="G151" s="18" t="inlineStr">
+        <is>
+          <t>Tập kết quả "sữa" có biên độ giá đa dạng, một số SKU đang có khuyến mãi giảm giá.</t>
+        </is>
+      </c>
+      <c r="H151" s="18" t="inlineStr">
+        <is>
+          <t>1. Tìm "sữa" (128 sản phẩm), mở Bộ lọc, tab Giá.
+2. Ghi lại khoảng giá cụ thể (VD "20.000đ - 35.000đ") hiển thị trên mỗi preset &lt;30%/30-70%/&gt;70%.
+3. Chọn preset "&lt;30% giá thấp", tap Áp dụng, kiểm tra toàn bộ SKU trả về có nằm trong khoảng giá đã hiển thị không.
+4. Đổi từ khoá khác (VD "bia", biên độ giá khác hẳn), lặp lại bước 1-2, xác nhận khoảng giá của 3 preset thay đổi theo đúng tập kết quả mới (không phải ngưỡng cố định toàn hệ thống).</t>
+        </is>
+      </c>
+      <c r="I151" s="18" t="inlineStr">
+        <is>
+          <t>"sữa" vs "bia", preset &lt;30%</t>
+        </is>
+      </c>
+      <c r="J151" s="18" t="inlineStr">
+        <is>
+          <t>TBD — khoảng giá của 3 preset phải tính động theo phân bố giá của TẬP KẾT QUẢ HIỆN TẠI (đổi từ khoá → đổi khoảng giá preset), không phải ngưỡng cố định; toàn bộ SKU trả về khi chọn preset phải nằm đúng trong khoảng giá đã hiển thị. Chưa xác nhận cơ sở tính là giá gốc hay giá sau khuyến mãi — xem QnA-41.</t>
+        </is>
+      </c>
+      <c r="K151" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L151" s="10" t="n"/>
+      <c r="M151" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N151" s="10" t="n"/>
+      <c r="O151" s="10" t="n"/>
+      <c r="P151" s="18" t="inlineStr">
+        <is>
+          <t>QnA-41</t>
+        </is>
+      </c>
+      <c r="Q151" s="18" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-41: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC9-TC1</t>
+        </is>
+      </c>
+      <c r="B152" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC9</t>
+        </is>
+      </c>
+      <c r="C152" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-009</t>
+        </is>
+      </c>
+      <c r="D152" s="18" t="inlineStr">
+        <is>
+          <t>FR-SF-04</t>
+        </is>
+      </c>
+      <c r="E152" s="18" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="F152" s="18" t="inlineStr">
+        <is>
+          <t>Chọn "Giao hàng tiêu chuẩn" — đã xác nhận: đúng 1 checkbox duy nhất trong tab</t>
+        </is>
+      </c>
+      <c r="G152" s="18" t="inlineStr">
+        <is>
+          <t>Tab Giao hàng chưa có điều kiện nào active.</t>
+        </is>
+      </c>
+      <c r="H152" s="18" t="inlineStr">
+        <is>
+          <t>1. Mở Bộ lọc, chuyển tab Giao hàng.
+2. Đếm và ghi lại toàn bộ tuỳ chọn hiển thị trong tab (BRD chỉ nêu "Giao hàng tiêu chuẩn").
+3. Chọn "Giao hàng tiêu chuẩn", quan sát badge tab Giao hàng.
+4. Tap Áp dụng, kiểm tra kết quả trả về.</t>
+        </is>
+      </c>
+      <c r="I152" s="18" t="inlineStr">
+        <is>
+          <t>Tab Giao hàng</t>
+        </is>
+      </c>
+      <c r="J152" s="18" t="inlineStr">
+        <is>
+          <t>Tab Giao hàng chỉ có ĐÚNG 1 tuỳ chọn: checkbox "Giao hàng tiêu chuẩn" (xác nhận theo storyboard bản cập nhật v0.1-20260819, thành phần #6 "Giao hàng &amp; các nhóm khác") — không phải danh sách nhiều lựa chọn. Badge tab Giao hàng chỉ có 2 trạng thái: 0 (chưa chọn) hoặc 1 (đã chọn). Kết quả sau lọc chỉ gồm SKU đủ điều kiện giao hàng tiêu chuẩn.</t>
+        </is>
+      </c>
+      <c r="K152" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L152" s="10" t="n"/>
+      <c r="M152" s="10" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N152" s="10" t="n"/>
+      <c r="O152" s="10" t="n"/>
+      <c r="P152" s="18" t="inlineStr">
+        <is>
+          <t>QnA-42</t>
+        </is>
+      </c>
+      <c r="Q152" s="18" t="inlineStr">
+        <is>
+          <t>RESOLVED — QnA-42: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC10-TC1</t>
+        </is>
+      </c>
+      <c r="B153" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC10</t>
+        </is>
+      </c>
+      <c r="C153" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-009</t>
+        </is>
+      </c>
+      <c r="D153" s="9" t="inlineStr">
+        <is>
+          <t>FR-SF-01, FR-SF-04</t>
+        </is>
+      </c>
+      <c r="E153" s="9" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="F153" s="9" t="inlineStr">
+        <is>
+          <t>Danh sách 5 mức Đánh giá đúng đặc tả, độc quyền chỉ chọn 1</t>
+        </is>
+      </c>
+      <c r="G153" s="9" t="inlineStr">
+        <is>
+          <t>Chưa chọn mức Đánh giá nào.</t>
+        </is>
+      </c>
+      <c r="H153" s="9" t="inlineStr">
+        <is>
+          <t>1. Mở Bộ lọc, chuyển tab Đánh giá.
+2. Đếm và đối chiếu tên 5 mức hiển thị với BRD (5 sao / Từ 4 sao trở lên / Từ 3 sao trở lên / Từ 2 sao trở lên / Từ 1 sao trở lên).
+3. Chọn "Từ 4 sao trở lên", quan sát badge tab Đánh giá.
+4. Chọn tiếp "Từ 3 sao trở lên" mà không bỏ chọn mức trước.</t>
+        </is>
+      </c>
+      <c r="I153" s="9" t="inlineStr">
+        <is>
+          <t>5 mức Đánh giá</t>
+        </is>
+      </c>
+      <c r="J153" s="9" t="inlineStr">
+        <is>
+          <t>Danh sách đúng 5 mức, đúng thứ tự và tên gọi theo BRD FR-SF-04; chọn mức thứ 2 ("Từ 3 sao trở lên") tự động bỏ chọn mức trước đó ("Từ 4 sao trở lên") — chỉ 1 mức active tại một thời điểm (badge tab Đánh giá luôn = 1 khi có chọn, giống tính chất độc quyền của tab Danh mục).</t>
+        </is>
+      </c>
+      <c r="K153" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L153" s="10" t="n"/>
+      <c r="M153" s="10" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N153" s="10" t="n"/>
+      <c r="O153" s="10" t="n"/>
+      <c r="P153" s="9" t="n"/>
+      <c r="Q153" s="9" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC10-TC2</t>
+        </is>
+      </c>
+      <c r="B154" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-009-SC10</t>
+        </is>
+      </c>
+      <c r="C154" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-009</t>
+        </is>
+      </c>
+      <c r="D154" s="9" t="inlineStr">
+        <is>
+          <t>FR-SF-01, FR-SF-04</t>
+        </is>
+      </c>
+      <c r="E154" s="9" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F154" s="9" t="inlineStr">
+        <is>
+          <t>Verify "Từ N sao trở lên" trả về đúng ngưỡng &gt;= N (bao gồm N và cao hơn)</t>
+        </is>
+      </c>
+      <c r="G154" s="9" t="inlineStr">
+        <is>
+          <t>Tập kết quả có SKU trải đều rating từ 1-5 sao.</t>
+        </is>
+      </c>
+      <c r="H154" s="9" t="inlineStr">
+        <is>
+          <t>1. Mở Bộ lọc, tab Đánh giá, chọn "Từ 4 sao trở lên".
+2. Tap Áp dụng.
+3. Kiểm tra rating của toàn bộ SKU trong kết quả trả về — xác nhận không có SKU nào rating &lt; 4.0.
+4. Kiểm tra có SKU rating = 5.0 vẫn xuất hiện trong kết quả (không bị hiểu nhầm là dải "chỉ đúng 4 sao").</t>
+        </is>
+      </c>
+      <c r="I154" s="9" t="inlineStr">
+        <is>
+          <t>"Từ 4 sao trở lên"</t>
+        </is>
+      </c>
+      <c r="J154" s="9" t="inlineStr">
+        <is>
+          <t>100% SKU trong kết quả có rating &gt;= 4.0 (bao gồm cả SKU 5 sao); không có SKU nào rating &lt; 4.0 lọt vào kết quả.</t>
+        </is>
+      </c>
+      <c r="K154" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L154" s="10" t="n"/>
+      <c r="M154" s="10" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N154" s="10" t="n"/>
+      <c r="O154" s="10" t="n"/>
+      <c r="P154" s="9" t="n"/>
+      <c r="Q154" s="9" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-011-SC1-TC4</t>
+        </is>
+      </c>
+      <c r="B155" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-011-SC1</t>
+        </is>
+      </c>
+      <c r="C155" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-011</t>
+        </is>
+      </c>
+      <c r="D155" s="9" t="inlineStr">
+        <is>
+          <t>Không có FR ID rõ ràng trong BRD — xem QnA-10</t>
+        </is>
+      </c>
+      <c r="E155" s="9" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="F155" s="9" t="inlineStr">
+        <is>
+          <t>Chạm vào Toast xác nhận — không có hành động nào xảy ra</t>
+        </is>
+      </c>
+      <c r="G155" s="9" t="inlineStr">
+        <is>
+          <t>Toast "Đã thêm vào giỏ hàng" đang hiển thị sau khi tap (+).</t>
+        </is>
+      </c>
+      <c r="H155" s="9" t="inlineStr">
+        <is>
+          <t>1. Tap (+) trên 1 Product Card, chờ Toast xác nhận xuất hiện.
+2. Trong lúc Toast còn hiển thị (chưa tự ẩn), chạm trực tiếp vào vùng thân Toast (ảnh/text, không phải nút đóng nếu có).
+3. Quan sát UI ngay sau khi chạm.
+4. Chờ hết 3 giây, xác nhận Toast tự ẩn bình thường như không có gì xảy ra.</t>
+        </is>
+      </c>
+      <c r="I155" s="9" t="inlineStr">
+        <is>
+          <t>Tap (+) → tap vào thân Toast</t>
+        </is>
+      </c>
+      <c r="J155" s="9" t="inlineStr">
+        <is>
+          <t>Chạm vào thân Toast KHÔNG kích hoạt bất kỳ hành động nào — không mở trang Giỏ hàng, không điều hướng sang PDP, không dismiss Toast sớm hơn 3 giây, không có hiệu ứng gì khác ngoài việc Toast tiếp tục đếm ngược và tự ẩn đúng theo thời gian đã định (3 giây) như khi không chạm vào.</t>
+        </is>
+      </c>
+      <c r="K155" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L155" s="10" t="n"/>
+      <c r="M155" s="10" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N155" s="10" t="n"/>
+      <c r="O155" s="10" t="n"/>
+      <c r="P155" s="9" t="n"/>
+      <c r="Q155" s="9" t="inlineStr">
+        <is>
+          <t>Hành vi hiện tại giả định thân Toast không có CTA tương tác (passive display); nếu QnA-08 chốt đổi CTA thành "Xem giỏ" (thêm nút bấm rõ ràng trong Toast), cần bổ sung TC riêng cho hành vi tap vào nút CTA đó — TC này chỉ xác nhận chạm vào phần THÂN Toast (ngoài vùng nút, nếu có) không gây hành động ngoài ý muốn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-012-SC1-TC4</t>
+        </is>
+      </c>
+      <c r="B156" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-012-SC1</t>
+        </is>
+      </c>
+      <c r="C156" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-012</t>
+        </is>
+      </c>
+      <c r="D156" s="18" t="inlineStr">
+        <is>
+          <t>FR-ZR-01, FR-ZR-02, FR-SM-07</t>
+        </is>
+      </c>
+      <c r="E156" s="18" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F156" s="18" t="inlineStr">
+        <is>
+          <t>Gợi ý Cross-sell (Basket Analysis) phản ánh đúng dữ liệu mua kèm thực tế — TBD công thức chính xác</t>
+        </is>
+      </c>
+      <c r="G156" s="18" t="inlineStr">
+        <is>
+          <t>Có dữ liệu lịch sử đơn hàng thể hiện rõ 1 cặp sản phẩm thường được mua cùng nhau (VD Bia Corona + Đậu phộng xuất hiện cùng đơn hàng với tần suất cao).</t>
+        </is>
+      </c>
+      <c r="H156" s="18" t="inlineStr">
+        <is>
+          <t>1. Tìm kiếm 1 từ khoá dẫn tới Zero Result cho sản phẩm hết hàng có dữ liệu mua kèm rõ ràng (VD "Bia Corona" hết hàng).
+2. Quan sát khối "Có thể bạn sẽ thích" — xác nhận sản phẩm mua kèm đã biết (VD Đậu phộng) có xuất hiện trong nhóm gợi ý Cross-sell không.
+3. Kiểm tra 1 sản phẩm hoàn toàn không liên quan (VD dụng cụ làm vườn) có bị gợi ý nhầm không.</t>
+        </is>
+      </c>
+      <c r="I156" s="18" t="inlineStr">
+        <is>
+          <t>"Bia Corona" (hết hàng, có dữ liệu mua kèm với Đậu phộng)</t>
+        </is>
+      </c>
+      <c r="J156" s="18" t="inlineStr">
+        <is>
+          <t>TBD — yêu cầu tối thiểu: sản phẩm mua kèm đã biết rõ trong dữ liệu (Đậu phộng) phải xuất hiện trong gợi ý Cross-sell; sản phẩm hoàn toàn không liên quan không được gợi ý. Công thức chính xác (ngưỡng support/confidence, cá nhân hoá hay tổng hợp, khung thời gian dữ liệu) chưa được xác nhận — không chấm Pass/Fail chi tiết cho tới khi có công thức chính thức. Xem QnA-45.</t>
+        </is>
+      </c>
+      <c r="K156" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L156" s="10" t="n"/>
+      <c r="M156" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N156" s="10" t="n"/>
+      <c r="O156" s="10" t="n"/>
+      <c r="P156" s="18" t="inlineStr">
+        <is>
+          <t>QnA-45</t>
+        </is>
+      </c>
+      <c r="Q156" s="18" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-45: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-012-SC1-TC5</t>
+        </is>
+      </c>
+      <c r="B157" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-012-SC1</t>
+        </is>
+      </c>
+      <c r="C157" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-012</t>
+        </is>
+      </c>
+      <c r="D157" s="18" t="inlineStr">
+        <is>
+          <t>FR-ZR-01, FR-ZR-02, FR-SM-07</t>
+        </is>
+      </c>
+      <c r="E157" s="18" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F157" s="18" t="inlineStr">
+        <is>
+          <t>Giới hạn tối đa số sản phẩm trong khối "Có thể bạn sẽ thích" khi cuộn tải thêm — TBD</t>
+        </is>
+      </c>
+      <c r="G157" s="18" t="inlineStr">
+        <is>
+          <t>Đang ở Zero Result Page với khối gợi ý hiển thị mặc định 10 sản phẩm (Best-seller fallback, danh sách đủ dài để test lazy load nhiều lần).</t>
+        </is>
+      </c>
+      <c r="H157" s="18" t="inlineStr">
+        <is>
+          <t>1. Vào Zero Result Page, xác nhận mặc định hiển thị 10 sản phẩm đầu.
+2. Cuộn xuống hết danh sách, chờ lazy load tải thêm.
+3. Lặp lại việc cuộn nhiều lần, đếm tổng số sản phẩm đã tải cho tới khi ngừng tải thêm hoặc đạt một ngưỡng rõ ràng.</t>
+        </is>
+      </c>
+      <c r="I157" s="18" t="inlineStr">
+        <is>
+          <t>Cuộn liên tục khối "Có thể bạn sẽ thích"</t>
+        </is>
+      </c>
+      <c r="J157" s="18" t="inlineStr">
+        <is>
+          <t>TBD — BRD chỉ xác nhận mặc định 10 sản phẩm (Lazy Loading), không nêu rõ giới hạn tối đa (dừng ở ngưỡng cụ thể hay tải theo hết dữ liệu Best-seller). Không chấm Pass/Fail định lượng cho tới khi xác nhận giới hạn tối đa chính thức. Xem QnA-46.</t>
+        </is>
+      </c>
+      <c r="K157" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L157" s="10" t="n"/>
+      <c r="M157" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N157" s="10" t="n"/>
+      <c r="O157" s="10" t="n"/>
+      <c r="P157" s="18" t="inlineStr">
+        <is>
+          <t>QnA-46</t>
+        </is>
+      </c>
+      <c r="Q157" s="18" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-46: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-012-SC4-TC1</t>
+        </is>
+      </c>
+      <c r="B158" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-012-SC4</t>
+        </is>
+      </c>
+      <c r="C158" s="9" t="inlineStr">
+        <is>
+          <t>SS-SCR-012</t>
+        </is>
+      </c>
+      <c r="D158" s="9" t="inlineStr">
+        <is>
+          <t>FR-ZR-01, FR-ZR-02, FR-SM-07, FR-PR-01 -&gt; FR-PR-05</t>
+        </is>
+      </c>
+      <c r="E158" s="9" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F158" s="9" t="inlineStr">
+        <is>
+          <t>Từ khoá khớp chính xác 1 SKU hết hàng nhưng còn SKU khác khớp còn hàng — vẫn ở lại SS-SCR-005, không kích hoạt Zero Result</t>
+        </is>
+      </c>
+      <c r="G158" s="9" t="inlineStr">
+        <is>
+          <t>Catalogue có ≥2 SKU cùng khớp trực tiếp 1 từ khoá, trong đó 1 SKU stock=0 và ≥1 SKU còn hàng.</t>
+        </is>
+      </c>
+      <c r="H158" s="9" t="inlineStr">
+        <is>
+          <t>1. Thiết lập dữ liệu: từ khoá "X" khớp trực tiếp SKU-A (hết hàng) và SKU-B (còn hàng).
+2. Tìm kiếm "X".
+3. Quan sát màn hình trả về (SS-SCR-005 hay SS-SCR-012).
+4. Nếu là SS-SCR-005, kiểm tra vị trí SKU-A trong danh sách kết quả.</t>
+        </is>
+      </c>
+      <c r="I158" s="9" t="inlineStr">
+        <is>
+          <t>Từ khoá "X" → SKU-A (hết hàng) + SKU-B (còn hàng)</t>
+        </is>
+      </c>
+      <c r="J158" s="9" t="inlineStr">
+        <is>
+          <t>Hệ thống trả về trang kết quả SS-SCR-005 (KHÔNG chuyển sang Zero Result Page); SKU-A (hết hàng) vẫn xuất hiện trong danh sách nhưng bị đẩy xuống vị trí cuối cùng (dưới mọi SKU còn hàng, kể cả những SKU có điểm relevance thấp hơn) theo đúng quy tắc Out-of-stock override; khối "Có thể bạn sẽ thích" không xuất hiện vì đây không phải luồng Zero Result.</t>
+        </is>
+      </c>
+      <c r="K158" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L158" s="10" t="n"/>
+      <c r="M158" s="10" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N158" s="10" t="n"/>
+      <c r="O158" s="10" t="n"/>
+      <c r="P158" s="9" t="n"/>
+      <c r="Q158" s="9" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-012-SC4-TC2</t>
+        </is>
+      </c>
+      <c r="B159" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-012-SC4</t>
+        </is>
+      </c>
+      <c r="C159" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-012</t>
+        </is>
+      </c>
+      <c r="D159" s="18" t="inlineStr">
+        <is>
+          <t>FR-ZR-01, FR-ZR-02, FR-SM-07, FR-PR-01 -&gt; FR-PR-05</t>
+        </is>
+      </c>
+      <c r="E159" s="18" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F159" s="18" t="inlineStr">
+        <is>
+          <t>Tất cả SKU khớp trực tiếp từ khoá đều hết hàng — TBD có kích hoạt Zero Result hay không</t>
+        </is>
+      </c>
+      <c r="G159" s="18" t="inlineStr">
+        <is>
+          <t>Catalogue có SKU khớp trực tiếp 1 từ khoá nhưng TOÀN BỘ đều stock=0 (không còn SKU nào khớp trực tiếp còn hàng).</t>
+        </is>
+      </c>
+      <c r="H159" s="18" t="inlineStr">
+        <is>
+          <t>1. Thiết lập dữ liệu: từ khoá "Y" chỉ khớp trực tiếp SKU-C, và SKU-C có stock=0 (không có SKU nào khác khớp trực tiếp).
+2. Tìm kiếm "Y".
+3. Quan sát màn hình trả về: có phải SS-SCR-005 (hiển thị SKU-C hết hàng, đơn độc trong danh sách) hay SS-SCR-012 (Zero Result, có khối "Có thể bạn sẽ thích")?</t>
+        </is>
+      </c>
+      <c r="I159" s="18" t="inlineStr">
+        <is>
+          <t>Từ khoá "Y" → chỉ khớp SKU-C (hết hàng)</t>
+        </is>
+      </c>
+      <c r="J159" s="18" t="inlineStr">
+        <is>
+          <t>TBD — chưa xác nhận hệ thống coi trường hợp này là (a) vẫn có 1 kết quả khớp (dù hết hàng) nên ở lại SS-SCR-005, hay (b) coi như "0 kết quả có thể mua" và chuyển sang luồng Zero Result Page (SS-SCR-012) với khối gợi ý Substitute/Cross-sell/Best-seller. Không chấm Pass/Fail cho tới khi xác nhận. Xem QnA-44.</t>
+        </is>
+      </c>
+      <c r="K159" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L159" s="10" t="n"/>
+      <c r="M159" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N159" s="10" t="n"/>
+      <c r="O159" s="10" t="n"/>
+      <c r="P159" s="18" t="inlineStr">
+        <is>
+          <t>QnA-44</t>
+        </is>
+      </c>
+      <c r="Q159" s="18" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-44: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-010-SC4-TC1</t>
+        </is>
+      </c>
+      <c r="B160" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-010-SC4</t>
+        </is>
+      </c>
+      <c r="C160" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-010</t>
+        </is>
+      </c>
+      <c r="D160" s="18" t="inlineStr">
+        <is>
+          <t>FR-SF-03</t>
+        </is>
+      </c>
+      <c r="E160" s="18" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F160" s="18" t="inlineStr">
+        <is>
+          <t>Tìm từ khoá mới tự động xoá bộ lọc của từ khoá cũ</t>
+        </is>
+      </c>
+      <c r="G160" s="18" t="inlineStr">
+        <is>
+          <t>Đang ở kết quả "sữa" với filter "Không đường" đang active (badge=1).</t>
+        </is>
+      </c>
+      <c r="H160" s="18" t="inlineStr">
+        <is>
+          <t>1. Ở trang kết quả "sữa", áp dụng filter "Không đường".
+2. Tap Search Bar, xoá "sữa", gõ từ khoá hoàn toàn khác "bia", submit tìm kiếm.
+3. Quan sát trang kết quả "bia" — kiểm tra badge nút Bộ lọc và có chip filter nào active không.</t>
+        </is>
+      </c>
+      <c r="I160" s="18" t="inlineStr">
+        <is>
+          <t>"sữa" (filter=Không đường) → tìm mới "bia"</t>
+        </is>
+      </c>
+      <c r="J160" s="18" t="inlineStr">
+        <is>
+          <t>Trang kết quả "bia" không còn filter "Không đường" nào active; badge nút Bộ lọc về 0/ẩn — bộ lọc đã tự động xoá khi đổi sang từ khoá mới hoàn toàn, đúng theo storyboard bản cập nhật (xem QnA-06, đã Resolved). Lưu ý: hành vi này áp dụng cho việc TÌM TỪ KHOÁ MỚI qua Search Bar — không áp dụng cho trường hợp chỉnh SỬA TRỰC TIẾP từ khoá hiện có ngay tại Search Bar của trang kết quả (nếu có luồng riêng, cần phân biệt rõ 2 luồng UX này).</t>
+        </is>
+      </c>
+      <c r="K160" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L160" s="10" t="n"/>
+      <c r="M160" s="10" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N160" s="10" t="n"/>
+      <c r="O160" s="10" t="n"/>
+      <c r="P160" s="18" t="inlineStr">
+        <is>
+          <t>QnA-06</t>
+        </is>
+      </c>
+      <c r="Q160" s="18" t="inlineStr">
+        <is>
+          <t>RESOLVED — QnA-06: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-013-SC1-TC4</t>
+        </is>
+      </c>
+      <c r="B161" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-013-SC1</t>
+        </is>
+      </c>
+      <c r="C161" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-013</t>
+        </is>
+      </c>
+      <c r="D161" s="18" t="inlineStr">
+        <is>
+          <t>FR-IS-01</t>
+        </is>
+      </c>
+      <c r="E161" s="18" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F161" s="18" t="inlineStr">
+        <is>
+          <t>Badge "Camera sau"/"Camera trước" hiển thị đúng theo camera đang active; nút Xoay đổi cả badge lẫn nguồn camera</t>
+        </is>
+      </c>
+      <c r="G161" s="18" t="inlineStr">
+        <is>
+          <t>Đang ở Camera Screen, camera mặc định = "Camera sau".</t>
+        </is>
+      </c>
+      <c r="H161" s="18" t="inlineStr">
+        <is>
+          <t>1. Mở Camera Screen, quan sát badge ở giữa header hiển thị "Camera sau".
+2. Tap nút "Xoay" (góc dưới phải).
+3. Quan sát badge có đổi thành "Camera trước" không, và khung ngắm có thực sự chuyển sang camera trước (selfie) không.
+4. Tap "Xoay" lần nữa, xác nhận quay lại "Camera sau" và khung ngắm camera sau.</t>
+        </is>
+      </c>
+      <c r="I161" s="18" t="inlineStr">
+        <is>
+          <t>Tap "Xoay" 2 lần liên tiếp</t>
+        </is>
+      </c>
+      <c r="J161" s="18" t="inlineStr">
+        <is>
+          <t>Badge và khung ngắm LUÔN đồng bộ với nhau tại mọi thời điểm — không có trường hợp badge ghi "Camera trước" nhưng khung ngắm vẫn hiển thị hình từ camera sau (hoặc ngược lại); mỗi lần tap "Xoay" cập nhật cả 2 ngay lập tức, không có độ trễ gây lệch trạng thái.</t>
+        </is>
+      </c>
+      <c r="K161" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L161" s="10" t="n"/>
+      <c r="M161" s="10" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N161" s="10" t="n"/>
+      <c r="O161" s="10" t="n"/>
+      <c r="P161" s="18" t="n"/>
+      <c r="Q161" s="18" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-013-SC1-TC5</t>
+        </is>
+      </c>
+      <c r="B162" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-013-SC1</t>
+        </is>
+      </c>
+      <c r="C162" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-013</t>
+        </is>
+      </c>
+      <c r="D162" s="18" t="inlineStr">
+        <is>
+          <t>FR-IS-01</t>
+        </is>
+      </c>
+      <c r="E162" s="18" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F162" s="18" t="inlineStr">
+        <is>
+          <t>Chụp ngay sau khi vừa xoay camera — ảnh chụp phải đúng từ camera mới, không dính race condition</t>
+        </is>
+      </c>
+      <c r="G162" s="18" t="inlineStr">
+        <is>
+          <t>Đang ở Camera Screen với "Camera sau" active.</t>
+        </is>
+      </c>
+      <c r="H162" s="18" t="inlineStr">
+        <is>
+          <t>1. Tap "Xoay" để chuyển sang "Camera trước".
+2. NGAY LẬP TỨC (không chờ) tap nút "Chụp".
+3. Kiểm tra ảnh vừa chụp có đúng là ảnh từ camera trước (góc nhìn selfie) hay vô tình vẫn chụp từ camera sau (do race condition khi camera chưa kịp khởi tạo xong).
+4. Lặp lại bước 1-3 nhiều lần (tap Xoay rồi Chụp liên tục, không có khoảng nghỉ) để kiểm tra tính ổn định.</t>
+        </is>
+      </c>
+      <c r="I162" s="18" t="inlineStr">
+        <is>
+          <t>Xoay → Chụp ngay (lặp lại nhiều lần)</t>
+        </is>
+      </c>
+      <c r="J162" s="18" t="inlineStr">
+        <is>
+          <t>Ảnh chụp luôn khớp chính xác với camera đang active tại thời điểm tap Chụp (không bao giờ chụp nhầm camera cũ); không crash hay đứng hình khi xoay+chụp liên tục dồn dập.</t>
+        </is>
+      </c>
+      <c r="K162" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L162" s="10" t="n"/>
+      <c r="M162" s="10" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N162" s="10" t="n"/>
+      <c r="O162" s="10" t="n"/>
+      <c r="P162" s="18" t="n"/>
+      <c r="Q162" s="18" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-014-SC1-TC4</t>
+        </is>
+      </c>
+      <c r="B163" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-014-SC1</t>
+        </is>
+      </c>
+      <c r="C163" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-014</t>
+        </is>
+      </c>
+      <c r="D163" s="18" t="inlineStr">
+        <is>
+          <t>FR-IS-02, FR-IS-04</t>
+        </is>
+      </c>
+      <c r="E163" s="18" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F163" s="18" t="inlineStr">
+        <is>
+          <t>Định dạng PNG được chấp nhận và xử lý đúng</t>
+        </is>
+      </c>
+      <c r="G163" s="18" t="inlineStr">
+        <is>
+          <t>Quyền truy cập thư viện đã cấp; có ảnh PNG hợp lệ trong khay.</t>
+        </is>
+      </c>
+      <c r="H163" s="18" t="inlineStr">
+        <is>
+          <t>1. Mở khay Gallery.
+2. Chọn 1 ảnh định dạng PNG (dung lượng hợp lệ, VD 2MB).
+3. Quan sát hệ thống có chấp nhận và chuyển sang Loading Screen hay không.</t>
+        </is>
+      </c>
+      <c r="I163" s="18" t="inlineStr">
+        <is>
+          <t>Ảnh PNG 2MB</t>
+        </is>
+      </c>
+      <c r="J163" s="18" t="inlineStr">
+        <is>
+          <t>Ảnh PNG được chấp nhận, không hiện Toast lỗi, chuyển thẳng sang Loading Screen (SS-SCR-004) — đúng theo FR-IS-04 (chấp nhận JPG/PNG/WEBP).</t>
+        </is>
+      </c>
+      <c r="K163" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L163" s="10" t="n"/>
+      <c r="M163" s="10" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N163" s="10" t="n"/>
+      <c r="O163" s="10" t="n"/>
+      <c r="P163" s="18" t="n"/>
+      <c r="Q163" s="18" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-014-SC1-TC5</t>
+        </is>
+      </c>
+      <c r="B164" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-014-SC1</t>
+        </is>
+      </c>
+      <c r="C164" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-014</t>
+        </is>
+      </c>
+      <c r="D164" s="18" t="inlineStr">
+        <is>
+          <t>FR-IS-02, FR-IS-04</t>
+        </is>
+      </c>
+      <c r="E164" s="18" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F164" s="18" t="inlineStr">
+        <is>
+          <t>Định dạng WEBP được chấp nhận — trước bản cập nhật này chưa có test case nào kiểm tra định dạng này</t>
+        </is>
+      </c>
+      <c r="G164" s="18" t="inlineStr">
+        <is>
+          <t>Quyền truy cập thư viện đã cấp; có ảnh WEBP hợp lệ trong khay.</t>
+        </is>
+      </c>
+      <c r="H164" s="18" t="inlineStr">
+        <is>
+          <t>1. Mở khay Gallery.
+2. Chọn 1 ảnh định dạng WEBP (dung lượng hợp lệ, VD 2MB).
+3. Quan sát hệ thống có chấp nhận và chuyển sang Loading Screen hay không.</t>
+        </is>
+      </c>
+      <c r="I164" s="18" t="inlineStr">
+        <is>
+          <t>Ảnh WEBP 2MB</t>
+        </is>
+      </c>
+      <c r="J164" s="18" t="inlineStr">
+        <is>
+          <t>Ảnh WEBP được chấp nhận, không hiện Toast lỗi, chuyển thẳng sang Loading Screen (SS-SCR-004) — đúng theo FR-IS-04 (chấp nhận JPG/PNG/WEBP). Đây là định dạng duy nhất trong danh sách BRD chưa từng được test riêng trước bản cập nhật này.</t>
+        </is>
+      </c>
+      <c r="K164" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L164" s="10" t="n"/>
+      <c r="M164" s="10" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N164" s="10" t="n"/>
+      <c r="O164" s="10" t="n"/>
+      <c r="P164" s="18" t="n"/>
+      <c r="Q164" s="18" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-014-SC4-TC1</t>
+        </is>
+      </c>
+      <c r="B165" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-014-SC4</t>
+        </is>
+      </c>
+      <c r="C165" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-014</t>
+        </is>
+      </c>
+      <c r="D165" s="18" t="inlineStr">
+        <is>
+          <t>FR-IS-02, FR-IS-04</t>
+        </is>
+      </c>
+      <c r="E165" s="18" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F165" s="18" t="inlineStr">
+        <is>
+          <t>Tap nút "X" trên header khay Gallery đóng về Camera Screen, không chọn ảnh</t>
+        </is>
+      </c>
+      <c r="G165" s="18" t="inlineStr">
+        <is>
+          <t>Khay "Ảnh gần đây" đang mở.</t>
+        </is>
+      </c>
+      <c r="H165" s="18" t="inlineStr">
+        <is>
+          <t>1. Mở khay Gallery từ Camera Screen.
+2. Tap nút "X" ở góc trên bên phải header khay.
+3. Quan sát màn hình sau khi đóng.</t>
+        </is>
+      </c>
+      <c r="I165" s="18" t="inlineStr">
+        <is>
+          <t>Tap "X"</t>
+        </is>
+      </c>
+      <c r="J165" s="18" t="inlineStr">
+        <is>
+          <t>Quay lại đúng Camera Screen (không chọn ảnh nào); camera vẫn đang chạy nền đúng như trạng thái trước khi mở khay (không phải khởi động lại từ đầu).</t>
+        </is>
+      </c>
+      <c r="K165" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L165" s="10" t="n"/>
+      <c r="M165" s="10" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N165" s="10" t="n"/>
+      <c r="O165" s="10" t="n"/>
+      <c r="P165" s="18" t="n"/>
+      <c r="Q165" s="18" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-014-SC4-TC2</t>
+        </is>
+      </c>
+      <c r="B166" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-014-SC4</t>
+        </is>
+      </c>
+      <c r="C166" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-014</t>
+        </is>
+      </c>
+      <c r="D166" s="18" t="inlineStr">
+        <is>
+          <t>FR-IS-02, FR-IS-04</t>
+        </is>
+      </c>
+      <c r="E166" s="18" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F166" s="18" t="inlineStr">
+        <is>
+          <t>Tap vào vùng tối bên ngoài khay Gallery cũng đóng khay, hành vi nhất quán với nút X</t>
+        </is>
+      </c>
+      <c r="G166" s="18" t="inlineStr">
+        <is>
+          <t>Khay "Ảnh gần đây" đang mở.</t>
+        </is>
+      </c>
+      <c r="H166" s="18" t="inlineStr">
+        <is>
+          <t>1. Mở khay Gallery từ Camera Screen.
+2. Tap vào vùng camera preview phía trên khay (nền tối/khu vực ngoài sheet, không tap vào bất kỳ ảnh nào trong lưới).
+3. Quan sát màn hình sau khi tap.</t>
+        </is>
+      </c>
+      <c r="I166" s="18" t="inlineStr">
+        <is>
+          <t>Tap vùng ngoài sheet</t>
+        </is>
+      </c>
+      <c r="J166" s="18" t="inlineStr">
+        <is>
+          <t>Khay đóng lại, quay về Camera Screen giống hệt hành vi của nút "X" (TC1) — không chọn ảnh nào, không có khác biệt hành vi giữa 2 cách đóng.</t>
+        </is>
+      </c>
+      <c r="K166" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L166" s="10" t="n"/>
+      <c r="M166" s="10" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N166" s="10" t="n"/>
+      <c r="O166" s="10" t="n"/>
+      <c r="P166" s="18" t="n"/>
+      <c r="Q166" s="18" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-015-SC1-TC4</t>
+        </is>
+      </c>
+      <c r="B167" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-015-SC1</t>
+        </is>
+      </c>
+      <c r="C167" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-015</t>
+        </is>
+      </c>
+      <c r="D167" s="18" t="inlineStr">
+        <is>
+          <t>FR-IS-03, FR-IS-07</t>
+        </is>
+      </c>
+      <c r="E167" s="18" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F167" s="18" t="inlineStr">
+        <is>
+          <t>Chụp/tải ảnh mới trong lúc đang ở trang kết quả ảnh — ảnh mới ghi đè hoàn toàn ảnh cũ</t>
+        </is>
+      </c>
+      <c r="G167" s="18" t="inlineStr">
+        <is>
+          <t>Đang ở trang kết quả ảnh (SS-SCR-015) với ảnh hộp sữa TH True Milk đã xử lý xong.</t>
+        </is>
+      </c>
+      <c r="H167" s="18" t="inlineStr">
+        <is>
+          <t>1. Ở trang kết quả ảnh hiện tại (ảnh A: hộp sữa TH True Milk), tap icon Camera trên Search Bar để mở lại Camera Screen.
+2. Chụp 1 ảnh HOÀN TOÀN KHÁC (ảnh B: hộp sữa Vinamilk).
+3. Chờ xử lý xong, quan sát trang kết quả ảnh mới.
+4. Kiểm tra thumbnail trong ô tìm kiếm, danh sách sản phẩm, và trạng thái Sort/Filter có phải hoàn toàn của ảnh B hay còn sót lại dữ liệu/trạng thái nào của ảnh A không.</t>
+        </is>
+      </c>
+      <c r="I167" s="18" t="inlineStr">
+        <is>
+          <t>Ảnh A (TH True Milk) → chụp ảnh B (Vinamilk)</t>
+        </is>
+      </c>
+      <c r="J167" s="18" t="inlineStr">
+        <is>
+          <t>Ảnh B ghi đè hoàn toàn ảnh A: thumbnail trong ô tìm kiếm đổi thành ảnh B; danh sách kết quả là của ảnh B (không còn sản phẩm chỉ liên quan tới ảnh A); mọi bộ lọc/sắp xếp đang áp dụng cho ảnh A trước đó reset về mặc định cho truy vấn mới (tương tự hành vi đổi từ khoá mới đã xác nhận ở SS-SCR-010-SC4).</t>
+        </is>
+      </c>
+      <c r="K167" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L167" s="10" t="n"/>
+      <c r="M167" s="10" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N167" s="10" t="n"/>
+      <c r="O167" s="10" t="n"/>
+      <c r="P167" s="18" t="n"/>
+      <c r="Q167" s="18" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-015-SC1-TC5</t>
+        </is>
+      </c>
+      <c r="B168" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-015-SC1</t>
+        </is>
+      </c>
+      <c r="C168" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-015</t>
+        </is>
+      </c>
+      <c r="D168" s="18" t="inlineStr">
+        <is>
+          <t>FR-IS-03, FR-IS-07</t>
+        </is>
+      </c>
+      <c r="E168" s="18" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F168" s="18" t="inlineStr">
+        <is>
+          <t>Sau khi chụp ảnh hoặc chọn ảnh từ thư viện thành công, ảnh load đúng vào ô tìm kiếm (Search Bar) trên trang kết quả</t>
+        </is>
+      </c>
+      <c r="G168" s="18" t="inlineStr">
+        <is>
+          <t>Đã xử lý xong 1 lượt tìm bằng ảnh.</t>
+        </is>
+      </c>
+      <c r="H168" s="18" t="inlineStr">
+        <is>
+          <t>1. Thực hiện chụp ảnh trực tiếp (SS-SCR-013) thành công, quan sát ô tìm kiếm trên trang kết quả (SS-SCR-015).
+2. Lặp lại nhưng lần này CHỌN ảnh từ thư viện (SS-SCR-014) thay vì chụp trực tiếp, quan sát ô tìm kiếm.</t>
+        </is>
+      </c>
+      <c r="I168" s="18" t="inlineStr">
+        <is>
+          <t>Luồng Chụp ảnh / Luồng Chọn ảnh thư viện</t>
+        </is>
+      </c>
+      <c r="J168" s="18" t="inlineStr">
+        <is>
+          <t>Ở CẢ 2 luồng, ảnh vừa xử lý (chụp trực tiếp hoặc chọn từ thư viện) đều hiển thị đúng dưới dạng thumbnail thu nhỏ NGAY TRONG ô tìm kiếm (thay thế vị trí từ khoá text), không có khác biệt về hành vi hiển thị thumbnail giữa 2 nguồn ảnh đầu vào.</t>
+        </is>
+      </c>
+      <c r="K168" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L168" s="10" t="n"/>
+      <c r="M168" s="10" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N168" s="10" t="n"/>
+      <c r="O168" s="10" t="n"/>
+      <c r="P168" s="18" t="n"/>
+      <c r="Q168" s="18" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-016-SC1-TC3</t>
+        </is>
+      </c>
+      <c r="B169" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-016-SC1</t>
+        </is>
+      </c>
+      <c r="C169" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-016</t>
+        </is>
+      </c>
+      <c r="D169" s="18" t="inlineStr">
+        <is>
+          <t>FR-IS-05</t>
+        </is>
+      </c>
+      <c r="E169" s="18" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+      <c r="F169" s="18" t="inlineStr">
+        <is>
+          <t>Nhấn nút Back trên header màn lỗi "Không nhận diện được" — TBD đích đến</t>
+        </is>
+      </c>
+      <c r="G169" s="18" t="inlineStr">
+        <is>
+          <t>Đang ở màn hình lỗi "Không nhận diện được" (SS-SCR-016) sau khi upload ảnh mờ.</t>
+        </is>
+      </c>
+      <c r="H169" s="18" t="inlineStr">
+        <is>
+          <t>1. Upload ảnh mờ, xác nhận màn lỗi "Không nhận diện được" hiện ra.
+2. Tap nút "Back" ở góc trên bên trái header (không tap "Thử lại" hay "Tìm bằng từ khoá").
+3. Quan sát màn hình được điều hướng tới.</t>
+        </is>
+      </c>
+      <c r="I169" s="18" t="inlineStr">
+        <is>
+          <t>Tap "Back" trên header</t>
+        </is>
+      </c>
+      <c r="J169" s="18" t="inlineStr">
+        <is>
+          <t>TBD — chưa xác nhận nút Back có hành vi giống hệt "Thử lại" (quay lại Camera Screen) hay khác biệt (thoát hẳn về màn hình đã mở luồng tìm ảnh, VD Pre-search hoặc trang kết quả trước đó). Yêu cầu tối thiểu: không crash, không kẹt lại đúng màn lỗi. Không chấm Pass/Fail cho tới khi xác nhận. Xem QnA-50.</t>
+        </is>
+      </c>
+      <c r="K169" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L169" s="10" t="n"/>
+      <c r="M169" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N169" s="10" t="n"/>
+      <c r="O169" s="10" t="n"/>
+      <c r="P169" s="18" t="inlineStr">
+        <is>
+          <t>QnA-50</t>
+        </is>
+      </c>
+      <c r="Q169" s="18" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-50: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-018-SC1-TC4</t>
+        </is>
+      </c>
+      <c r="B170" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-018-SC1</t>
+        </is>
+      </c>
+      <c r="C170" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-018</t>
+        </is>
+      </c>
+      <c r="D170" s="18" t="inlineStr">
+        <is>
+          <t>FR-VS-04, FR-VS-05</t>
+        </is>
+      </c>
+      <c r="E170" s="18" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="F170" s="18" t="inlineStr">
+        <is>
+          <t>Transcript hợp lệ nhưng không khớp sản phẩm nào (câu vô nghĩa với catalogue) → chuyển đúng sang Zero Result giống luồng Text</t>
+        </is>
+      </c>
+      <c r="G170" s="18" t="inlineStr">
+        <is>
+          <t>Voice-to-text xử lý xong, chuỗi transcript hợp lệ (không rỗng) nhưng không khớp catalogue.</t>
+        </is>
+      </c>
+      <c r="H170" s="18" t="inlineStr">
+        <is>
+          <t>1. Nói một câu rõ ràng nhưng không phải tên sản phẩm hợp lệ (VD "xịt muỗi Tesla").
+2. Để hệ thống transcribe thành công (không rơi vào luồng lỗi nhận diện giọng nói SS-SCR-019).
+3. Quan sát trang được điều hướng tới.</t>
+        </is>
+      </c>
+      <c r="I170" s="18" t="inlineStr">
+        <is>
+          <t>"xịt muỗi Tesla" (giọng nói)</t>
+        </is>
+      </c>
+      <c r="J170" s="18" t="inlineStr">
+        <is>
+          <t>Vì transcript hợp lệ, không rỗng, hệ thống KHÔNG chuyển sang màn lỗi giọng nói (SS-SCR-019, chỉ dành cho trường hợp không nghe rõ/transcript rỗng — xem SC2). Vì catalogue không có SKU khớp, hệ thống áp dụng đúng cơ chế Zero Result Prevention 3 tầng giống hệt luồng Text Search: hiển thị trang "Không tìm thấy kết quả" (SS-SCR-012) với khối "Có thể bạn sẽ thích", không phải trang trắng hay lỗi giọng nói.</t>
+        </is>
+      </c>
+      <c r="K170" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L170" s="10" t="n"/>
+      <c r="M170" s="10" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N170" s="10" t="n"/>
+      <c r="O170" s="10" t="n"/>
+      <c r="P170" s="18" t="n"/>
+      <c r="Q170" s="18" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-019-SC1-TC3</t>
+        </is>
+      </c>
+      <c r="B171" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-019-SC1</t>
+        </is>
+      </c>
+      <c r="C171" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-019</t>
+        </is>
+      </c>
+      <c r="D171" s="18" t="inlineStr">
+        <is>
+          <t>FR-VS-06</t>
+        </is>
+      </c>
+      <c r="E171" s="18" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+      <c r="F171" s="18" t="inlineStr">
+        <is>
+          <t>Nhấn nút Back trên header màn lỗi "Không nhận diện được" (giọng nói) — TBD đích đến</t>
+        </is>
+      </c>
+      <c r="G171" s="18" t="inlineStr">
+        <is>
+          <t>Đang ở màn hình lỗi "Không nhận diện được" (SS-SCR-019) sau khi thu âm không rõ.</t>
+        </is>
+      </c>
+      <c r="H171" s="18" t="inlineStr">
+        <is>
+          <t>1. Thu âm với tiếng ồn/im lặng, xác nhận màn lỗi "Không nhận diện được" hiện ra.
+2. Tap nút "Back" ở góc trên bên trái header (không tap "Thử lại" hay "Tìm bằng từ khoá").
+3. Quan sát màn hình được điều hướng tới.</t>
+        </is>
+      </c>
+      <c r="I171" s="18" t="inlineStr">
+        <is>
+          <t>Tap "Back" trên header</t>
+        </is>
+      </c>
+      <c r="J171" s="18" t="inlineStr">
+        <is>
+          <t>TBD — chưa xác nhận nút Back có hành vi giống hệt "Thử lại" (mở lại lớp thu âm) hay khác biệt (thoát hẳn về màn hình đã mở luồng tìm giọng nói, VD Pre-search hoặc trang kết quả trước đó) — cùng câu hỏi mở với SS-SCR-016-SC1-TC3 (luồng ảnh). Yêu cầu tối thiểu: không crash, không kẹt lại đúng màn lỗi. Không chấm Pass/Fail cho tới khi xác nhận. Xem QnA-50.</t>
+        </is>
+      </c>
+      <c r="K171" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L171" s="10" t="n"/>
+      <c r="M171" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N171" s="10" t="n"/>
+      <c r="O171" s="10" t="n"/>
+      <c r="P171" s="18" t="inlineStr">
+        <is>
+          <t>QnA-50</t>
+        </is>
+      </c>
+      <c r="Q171" s="18" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-50: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-017-SC4-TC1</t>
+        </is>
+      </c>
+      <c r="B172" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-017-SC4</t>
+        </is>
+      </c>
+      <c r="C172" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-017</t>
+        </is>
+      </c>
+      <c r="D172" s="18" t="inlineStr">
+        <is>
+          <t>FR-VS-01, FR-VS-03</t>
+        </is>
+      </c>
+      <c r="E172" s="18" t="inlineStr">
+        <is>
+          <t>Multilingual</t>
+        </is>
+      </c>
+      <c r="F172" s="18" t="inlineStr">
+        <is>
+          <t>Nói tiếng Anh — hệ thống tự nhận diện đúng ngôn ngữ và transcribe chính xác</t>
+        </is>
+      </c>
+      <c r="G172" s="18" t="inlineStr">
+        <is>
+          <t>Quyền Micro đã cấp; UI hệ thống đang ở tiếng Việt (không đổi ngôn ngữ app).</t>
+        </is>
+      </c>
+      <c r="H172" s="18" t="inlineStr">
+        <is>
+          <t>1. Tap icon Mic, bắt đầu thu âm.
+2. Nói 1 câu tiếng Anh rõ ràng (VD "fresh milk one liter").
+3. Kết thúc thu âm, quan sát văn bản nhận diện và kết quả trả về.</t>
+        </is>
+      </c>
+      <c r="I172" s="18" t="inlineStr">
+        <is>
+          <t>"fresh milk one liter" (tiếng Anh)</t>
+        </is>
+      </c>
+      <c r="J172" s="18" t="inlineStr">
+        <is>
+          <t>Hệ thống tự động nhận diện đây là tiếng Anh mà KHÔNG cần khách chọn ngôn ngữ thủ công trước đó; transcript hiển thị đúng câu tiếng Anh đã nói; kết quả tìm kiếm trả về sản phẩm sữa tươi liên quan (áp dụng logic đa ngôn ngữ FR-SM-02 để map sang catalog tiếng Việt).</t>
+        </is>
+      </c>
+      <c r="K172" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L172" s="10" t="n"/>
+      <c r="M172" s="10" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N172" s="10" t="n"/>
+      <c r="O172" s="10" t="n"/>
+      <c r="P172" s="18" t="n"/>
+      <c r="Q172" s="18" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-017-SC4-TC2</t>
+        </is>
+      </c>
+      <c r="B173" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-017-SC4</t>
+        </is>
+      </c>
+      <c r="C173" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-017</t>
+        </is>
+      </c>
+      <c r="D173" s="18" t="inlineStr">
+        <is>
+          <t>FR-VS-01, FR-VS-03</t>
+        </is>
+      </c>
+      <c r="E173" s="18" t="inlineStr">
+        <is>
+          <t>Multilingual</t>
+        </is>
+      </c>
+      <c r="F173" s="18" t="inlineStr">
+        <is>
+          <t>Nói tiếng Hàn — hệ thống tự nhận diện đúng ngôn ngữ và transcribe chính xác</t>
+        </is>
+      </c>
+      <c r="G173" s="18" t="inlineStr">
+        <is>
+          <t>Quyền Micro đã cấp; UI hệ thống đang ở tiếng Việt.</t>
+        </is>
+      </c>
+      <c r="H173" s="18" t="inlineStr">
+        <is>
+          <t>1. Tap icon Mic, bắt đầu thu âm.
+2. Nói 1 câu tiếng Hàn rõ ràng (tên sản phẩm phổ biến, VD tương đương "sữa tươi").
+3. Kết thúc thu âm, quan sát văn bản nhận diện và kết quả trả về.</t>
+        </is>
+      </c>
+      <c r="I173" s="18" t="inlineStr">
+        <is>
+          <t>Câu tiếng Hàn (tương đương "sữa tươi")</t>
+        </is>
+      </c>
+      <c r="J173" s="18" t="inlineStr">
+        <is>
+          <t>Hệ thống tự động nhận diện đây là tiếng Hàn mà không cần chọn thủ công; transcript hiển thị đúng; kết quả tìm kiếm trả về sản phẩm liên quan.</t>
+        </is>
+      </c>
+      <c r="K173" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L173" s="10" t="n"/>
+      <c r="M173" s="10" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N173" s="10" t="n"/>
+      <c r="O173" s="10" t="n"/>
+      <c r="P173" s="18" t="n"/>
+      <c r="Q173" s="18" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-017-SC4-TC3</t>
+        </is>
+      </c>
+      <c r="B174" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-017-SC4</t>
+        </is>
+      </c>
+      <c r="C174" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-017</t>
+        </is>
+      </c>
+      <c r="D174" s="18" t="inlineStr">
+        <is>
+          <t>FR-VS-01, FR-VS-03</t>
+        </is>
+      </c>
+      <c r="E174" s="18" t="inlineStr">
+        <is>
+          <t>Multilingual</t>
+        </is>
+      </c>
+      <c r="F174" s="18" t="inlineStr">
+        <is>
+          <t>Nói tiếng Trung — hệ thống tự nhận diện đúng ngôn ngữ và transcribe chính xác</t>
+        </is>
+      </c>
+      <c r="G174" s="18" t="inlineStr">
+        <is>
+          <t>Quyền Micro đã cấp; UI hệ thống đang ở tiếng Việt.</t>
+        </is>
+      </c>
+      <c r="H174" s="18" t="inlineStr">
+        <is>
+          <t>1. Tap icon Mic, bắt đầu thu âm.
+2. Nói 1 câu tiếng Trung rõ ràng (tên sản phẩm phổ biến, VD tương đương "sữa tươi").
+3. Kết thúc thu âm, quan sát văn bản nhận diện và kết quả trả về.</t>
+        </is>
+      </c>
+      <c r="I174" s="18" t="inlineStr">
+        <is>
+          <t>Câu tiếng Trung (tương đương "sữa tươi")</t>
+        </is>
+      </c>
+      <c r="J174" s="18" t="inlineStr">
+        <is>
+          <t>Hệ thống tự động nhận diện đây là tiếng Trung mà không cần chọn thủ công; transcript hiển thị đúng; kết quả tìm kiếm trả về sản phẩm liên quan.</t>
+        </is>
+      </c>
+      <c r="K174" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L174" s="10" t="n"/>
+      <c r="M174" s="10" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N174" s="10" t="n"/>
+      <c r="O174" s="10" t="n"/>
+      <c r="P174" s="18" t="n"/>
+      <c r="Q174" s="18" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-017-SC4-TC4</t>
+        </is>
+      </c>
+      <c r="B175" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-017-SC4</t>
+        </is>
+      </c>
+      <c r="C175" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-017</t>
+        </is>
+      </c>
+      <c r="D175" s="18" t="inlineStr">
+        <is>
+          <t>FR-VS-01, FR-VS-03</t>
+        </is>
+      </c>
+      <c r="E175" s="18" t="inlineStr">
+        <is>
+          <t>Multilingual</t>
+        </is>
+      </c>
+      <c r="F175" s="18" t="inlineStr">
+        <is>
+          <t>Nói tiếng Nga — hệ thống tự nhận diện đúng ngôn ngữ và transcribe chính xác</t>
+        </is>
+      </c>
+      <c r="G175" s="18" t="inlineStr">
+        <is>
+          <t>Quyền Micro đã cấp; UI hệ thống đang ở tiếng Việt.</t>
+        </is>
+      </c>
+      <c r="H175" s="18" t="inlineStr">
+        <is>
+          <t>1. Tap icon Mic, bắt đầu thu âm.
+2. Nói 1 câu tiếng Nga rõ ràng (tên sản phẩm phổ biến, VD tương đương "sữa tươi").
+3. Kết thúc thu âm, quan sát văn bản nhận diện và kết quả trả về.</t>
+        </is>
+      </c>
+      <c r="I175" s="18" t="inlineStr">
+        <is>
+          <t>Câu tiếng Nga (tương đương "sữa tươi")</t>
+        </is>
+      </c>
+      <c r="J175" s="18" t="inlineStr">
+        <is>
+          <t>Hệ thống tự động nhận diện đây là tiếng Nga mà không cần chọn thủ công; transcript hiển thị đúng; kết quả tìm kiếm trả về sản phẩm liên quan.</t>
+        </is>
+      </c>
+      <c r="K175" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L175" s="10" t="n"/>
+      <c r="M175" s="10" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N175" s="10" t="n"/>
+      <c r="O175" s="10" t="n"/>
+      <c r="P175" s="18" t="n"/>
+      <c r="Q175" s="18" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-017-SC4-TC5</t>
+        </is>
+      </c>
+      <c r="B176" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-017-SC4</t>
+        </is>
+      </c>
+      <c r="C176" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-017</t>
+        </is>
+      </c>
+      <c r="D176" s="18" t="inlineStr">
+        <is>
+          <t>FR-VS-01, FR-VS-03</t>
+        </is>
+      </c>
+      <c r="E176" s="18" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F176" s="18" t="inlineStr">
+        <is>
+          <t>Đổi ngôn ngữ nói giữa các lượt liên tiếp — hệ thống không bị "kẹt" theo ngôn ngữ lượt trước</t>
+        </is>
+      </c>
+      <c r="G176" s="18" t="inlineStr">
+        <is>
+          <t>Quyền Micro đã cấp.</t>
+        </is>
+      </c>
+      <c r="H176" s="18" t="inlineStr">
+        <is>
+          <t>1. Lượt 1: nói tiếng Việt ("sữa tươi"), xác nhận kết quả đúng.
+2. Ngay lượt kế tiếp: nói tiếng Anh ("fresh milk"), quan sát hệ thống có tự nhận diện đúng ngôn ngữ MỚI hay vẫn cố hiểu theo tiếng Việt của lượt trước.
+3. Lặp lại đổi sang tiếng Hàn ở lượt thứ 3.</t>
+        </is>
+      </c>
+      <c r="I176" s="18" t="inlineStr">
+        <is>
+          <t>VI → EN → KR (3 lượt liên tiếp)</t>
+        </is>
+      </c>
+      <c r="J176" s="18" t="inlineStr">
+        <is>
+          <t>Mỗi lượt thu âm được nhận diện ngôn ngữ ĐỘC LẬP, không bị ảnh hưởng bởi ngôn ngữ đã nói ở lượt ngay trước đó; cả 3 lượt đều transcribe đúng ngôn ngữ tương ứng.</t>
+        </is>
+      </c>
+      <c r="K176" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L176" s="10" t="n"/>
+      <c r="M176" s="10" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N176" s="10" t="n"/>
+      <c r="O176" s="10" t="n"/>
+      <c r="P176" s="18" t="n"/>
+      <c r="Q176" s="18" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-018-SC3-TC1</t>
+        </is>
+      </c>
+      <c r="B177" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-018-SC3</t>
+        </is>
+      </c>
+      <c r="C177" s="18" t="inlineStr">
+        <is>
+          <t>SS-SCR-018</t>
+        </is>
+      </c>
+      <c r="D177" s="18" t="inlineStr">
+        <is>
+          <t>FR-VS-08, NFR-005</t>
+        </is>
+      </c>
+      <c r="E177" s="18" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="F177" s="18" t="inlineStr">
+        <is>
+          <t>p95 thời gian phản hồi tìm kiếm giọng nói — đo thực tế, chưa chấm Pass/Fail do ngưỡng còn mâu thuẫn (FR-VS-08 vs NFR-005)</t>
+        </is>
+      </c>
+      <c r="G177" s="18" t="inlineStr">
+        <is>
+          <t>Điều kiện mạng bình thường.</t>
+        </is>
+      </c>
+      <c r="H177" s="18" t="inlineStr">
+        <is>
+          <t>1. Thực hiện 30+ lượt tìm kiếm giọng nói với câu nói chuẩn, điều kiện mạng bình thường.
+2. Đo thời gian từ khi kết thúc thu âm (auto-stop hoặc manual stop) tới khi sản phẩm đầu tiên hiển thị trên trang kết quả, cho từng lượt (bao gồm cả thời gian chuyển đổi giọng nói thành văn bản, theo đúng phạm vi đo của FR-VS-08/NFR-005).
+3. Tính p95 của tập số liệu.</t>
+        </is>
+      </c>
+      <c r="I177" s="18" t="inlineStr">
+        <is>
+          <t>Giọng nói chuẩn x ≥30 lượt</t>
+        </is>
+      </c>
+      <c r="J177" s="18" t="inlineStr">
+        <is>
+          <t>TBD — đo được số liệu p95 thực tế, nhưng KHÔNG chấm Pass/Fail cho tới khi xác nhận ngưỡng chính thức là 4.000ms (NFR-005) hay 6.000ms (FR-VS-08). Xem QnA-30.</t>
+        </is>
+      </c>
+      <c r="K177" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L177" s="10" t="n"/>
+      <c r="M177" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N177" s="10" t="n"/>
+      <c r="O177" s="10" t="n"/>
+      <c r="P177" s="18" t="inlineStr">
+        <is>
+          <t>QnA-30</t>
+        </is>
+      </c>
+      <c r="Q177" s="18" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-30: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:Q104"/>
@@ -13222,7 +18768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -14285,6 +19831,110 @@
       <c r="M22" s="10" t="n"/>
       <c r="N22" s="9" t="n"/>
     </row>
+    <row r="23">
+      <c r="A23" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>INT-13-SC2</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Hiệu năng &amp; Khả năng chịu tải (Performance/NFR)</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>FR-GD-03, NFR-009</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>Behavior</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>Khi hệ thống AI Search (ngữ nghĩa) gặp sự cố/timeout, tự động hạ cấp (Graceful Degradation) sang thuật toán tìm kiếm Keyword cơ bản, không hiển thị lỗi kỹ thuật cho khách hàng.</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>AI Search Service, Basic Keyword Search Engine (fallback), API Gateway</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>Có thể giả lập AI Search Service down/timeout (chaos testing hoặc feature-flag tắt AI service) trong môi trường test.</t>
+        </is>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>Khi AI Search Service không khả dụng, request tìm kiếm tự động chuyển sang thuật toán Keyword cơ bản; khách hàng vẫn nhận được kết quả tìm kiếm hợp lý (không phải trang trắng, không phải 0 kết quả do lỗi hệ thống); tuyệt đối KHÔNG hiển thị popup lỗi hay text kỹ thuật (VD "AI service unavailable", stack trace, mã lỗi 5xx) lên UI; khi AI Search Service phục hồi, hệ thống tự động chuyển lại dùng AI Search mà không cần thao tác thủ công.</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="n"/>
+      <c r="K23" s="10" t="n"/>
+      <c r="L23" s="10" t="n"/>
+      <c r="M23" s="10" t="inlineStr">
+        <is>
+          <t>Lấp khoảng trống đã ghi nhận tại QnA-32 ("chưa có test case nào kiểm tra hành vi Graceful Degradation thực tế"). NFR-009 mô tả đúng hành vi này gần như nguyên văn, dùng làm căn cứ REQ ID rõ ràng hơn — QnA-32 vẫn còn mở riêng cho câu hỏi tách FR-GD-01 khỏi FR-GD-03.</t>
+        </is>
+      </c>
+      <c r="N23" s="9" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>INT-13-SC3</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Hiệu năng &amp; Khả năng chịu tải (Performance/NFR)</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>FR-GD-01, NFR-001</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>Đo P95 thời gian phản hồi tìm kiếm văn bản ở mức tải BÌNH THƯỜNG (không phải tải đỉnh/load spike đã test ở INT-13-SC1) — đối chiếu đúng ngưỡng 300ms P95 theo FR-GD-01/NFR-001.</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>AI Search Service, API Gateway, Monitoring</t>
+        </is>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>Môi trường test mô phỏng tải trung bình hằng ngày (không phải peak).</t>
+        </is>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>Ở mức tải trung bình, P95 thời gian phản hồi tìm kiếm văn bản ≤300ms; khác biệt với ngưỡng ≤1.000ms đã test riêng cho tải đỉnh ở INT-13-SC1 (ngưỡng "ngày cao điểm" theo ghi chú BRD KPI-01).</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="n"/>
+      <c r="K24" s="10" t="n"/>
+      <c r="L24" s="10" t="n"/>
+      <c r="M24" s="10" t="n"/>
+      <c r="N24" s="9" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
@@ -14300,7 +19950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q31"/>
+  <dimension ref="A1:Q34"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="2"/>
@@ -16430,6 +22080,222 @@
           <t>Rủi ro pháp lý đã được BA ghi nhận trong BRD (RSK-05/DEP-08) — không phải QC tự phát hiện, nhưng cần nhắc lại ở đây vì ảnh hưởng trực tiếp tới nhiều module tích hợp (INT-04, INT-11).</t>
         </is>
       </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>INT-13-SC2-TC1</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>INT-13-SC2</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>Hiệu năng &amp; Khả năng chịu tải (Performance/NFR)</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>FR-GD-03, NFR-009</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>Behavior</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>AI Search sập/timeout → tự động fallback Keyword search, không hiện lỗi kỹ thuật</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>Môi trường test có thể giả lập AI Search Service trả lỗi/timeout (VD tắt service qua feature flag hoặc chặn network tới AI endpoint).</t>
+        </is>
+      </c>
+      <c r="H32" s="9" t="inlineStr">
+        <is>
+          <t>1. Giả lập AI Search Service timeout/down.
+2. Thực hiện tìm kiếm văn bản bình thường (VD "sữa tươi").
+3. Quan sát UI: có hiển thị kết quả nào không, có popup/text lỗi kỹ thuật nào xuất hiện không.
+4. Kiểm tra kết quả trả về có phải từ thuật toán Keyword cơ bản (so sánh với kết quả AI Search bình thường trước đó — VD mất khả năng hiểu đồng nghĩa/ngữ nghĩa, chỉ khớp từ khoá thô).
+5. Khôi phục AI Search Service, lặp lại tìm kiếm, xác nhận hệ thống tự chuyển lại dùng AI Search.</t>
+        </is>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>"sữa tươi", giả lập AI Search down rồi khôi phục</t>
+        </is>
+      </c>
+      <c r="J32" s="9" t="inlineStr">
+        <is>
+          <t>Bước 3: khách hàng vẫn nhận được trang kết quả có sản phẩm (không trắng, không lỗi hiển thị); tuyệt đối không có popup/toast/text kỹ thuật nào (VD "AI service unavailable", mã lỗi 5xx, stack trace). Bước 4: kết quả phản ánh đúng đặc điểm tìm kiếm Keyword cơ bản (có thể kém chính xác hơn AI nhưng vẫn hợp lý, không rỗng). Bước 5: sau khi AI Search phục hồi, hệ thống tự động dùng lại AI Search mà không cần deploy lại hay thao tác thủ công nào từ vận hành.</t>
+        </is>
+      </c>
+      <c r="K32" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L32" s="10" t="n"/>
+      <c r="M32" s="10" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N32" s="10" t="n"/>
+      <c r="O32" s="10" t="n"/>
+      <c r="P32" s="9" t="n"/>
+      <c r="Q32" s="9" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="18" t="inlineStr">
+        <is>
+          <t>INT-13-SC2-TC2</t>
+        </is>
+      </c>
+      <c r="B33" s="18" t="inlineStr">
+        <is>
+          <t>INT-13-SC2</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>Hiệu năng &amp; Khả năng chịu tải (Performance/NFR)</t>
+        </is>
+      </c>
+      <c r="D33" s="18" t="inlineStr">
+        <is>
+          <t>FR-GD-03, NFR-009</t>
+        </is>
+      </c>
+      <c r="E33" s="18" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="F33" s="18" t="inlineStr">
+        <is>
+          <t>Thời gian phản hồi trong chế độ fallback Keyword search — TBD có cùng ngưỡng SLA 300ms không</t>
+        </is>
+      </c>
+      <c r="G33" s="18" t="inlineStr">
+        <is>
+          <t>AI Search Service đang down/timeout (fallback mode active).</t>
+        </is>
+      </c>
+      <c r="H33" s="18" t="inlineStr">
+        <is>
+          <t>1. Trong lúc fallback đang active, thực hiện tìm kiếm và đo thời gian phản hồi (nhiều lượt để tính P95).
+2. So sánh với ngưỡng 300ms P95 (NFR-001/FR-GD-01) áp dụng cho chế độ AI Search bình thường.</t>
+        </is>
+      </c>
+      <c r="I33" s="18" t="inlineStr">
+        <is>
+          <t>Đo P95 thời gian phản hồi trong chế độ fallback</t>
+        </is>
+      </c>
+      <c r="J33" s="18" t="inlineStr">
+        <is>
+          <t>TBD — BRD không nói rõ ngưỡng hiệu năng có được nới lỏng trong chế độ fallback (thuật toán Keyword đơn giản hơn AI, có thể nhanh hơn hoặc chậm hơn tuỳ hạ tầng) hay vẫn giữ đúng SLA 300ms P95 như chế độ bình thường. Không chấm Pass/Fail định lượng cho tới khi BA/TD xác nhận ngưỡng SLA áp dụng trong chế độ fallback. Xem QnA-43.</t>
+        </is>
+      </c>
+      <c r="K33" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L33" s="10" t="n"/>
+      <c r="M33" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N33" s="10" t="n"/>
+      <c r="O33" s="10" t="n"/>
+      <c r="P33" s="18" t="inlineStr">
+        <is>
+          <t>QnA-43</t>
+        </is>
+      </c>
+      <c r="Q33" s="18" t="inlineStr">
+        <is>
+          <t>OPEN — QnA-43: xem chi tiết trong file QnA log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>INT-13-SC3-TC1</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>INT-13-SC3</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Hiệu năng &amp; Khả năng chịu tải (Performance/NFR)</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>FR-GD-01, NFR-001</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>P95 thời gian phản hồi tìm kiếm văn bản ở tải trung bình đúng SLA 300ms (FR-GD-01/NFR-001)</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>Môi trường test mô phỏng tải trung bình hằng ngày (baseline traffic, không phải 5x như INT-13-SC1).</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>1. Chạy load test ở mức tải trung bình (baseline, 1x) trong 15 phút.
+2. Đo P95 thời gian phản hồi API tìm kiếm văn bản trong suốt thời gian test.
+3. So sánh với ngưỡng 300ms theo NFR-001/FR-GD-01.</t>
+        </is>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>Tải = 1x trung bình (baseline), 15 phút</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="inlineStr">
+        <is>
+          <t>P95 thời gian phản hồi ≤300ms — đây là phép đo riêng biệt và NGHIÊM NGẶT HƠN so với ngưỡng ≤1.000ms đã test cho tải đỉnh (5x) ở INT-13-SC1-TC1; 2 test case bổ trợ nhau để phủ đủ cả điều kiện tải bình thường lẫn tải đỉnh theo đúng 2 ngưỡng khác nhau trong BRD (300ms P95 chuẩn theo NFR-001 vs ≤1.000ms ngày cao điểm theo ghi chú KPI-01).</t>
+        </is>
+      </c>
+      <c r="K34" s="9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L34" s="10" t="n"/>
+      <c r="M34" s="10" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="N34" s="10" t="n"/>
+      <c r="O34" s="10" t="n"/>
+      <c r="P34" s="9" t="n"/>
+      <c r="Q34" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -16469,6 +22335,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -16483,7 +22350,7 @@
         </is>
       </c>
       <c r="B4" s="13">
-        <f>COUNTA('UI Test Scenarios'!$B$3:$B$70)+COUNTA('Integration Test Scenarios'!$B$3:$B$22)</f>
+        <f>COUNTA('UI Test Scenarios'!$B$3:$B$85)+COUNTA('Integration Test Scenarios'!$B$3:$B$24)</f>
         <v/>
       </c>
     </row>
@@ -16494,10 +22361,11 @@
         </is>
       </c>
       <c r="B5" s="13">
-        <f>COUNTA('UI Test Cases'!$A$3:$A$114)+COUNTA('Integration Test Cases'!$A$3:$A$31)</f>
+        <f>COUNTA('UI Test Cases'!$A$3:$A$177)+COUNTA('Integration Test Cases'!$A$3:$A$34)</f>
         <v/>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
@@ -16517,7 +22385,7 @@
         </is>
       </c>
       <c r="B8" s="13">
-        <f>COUNTIF('UI Test Cases'!$M$3:$M$114,"Pass")</f>
+        <f>COUNTIF('UI Test Cases'!$M$3:$M$177,"Pass")</f>
         <v/>
       </c>
       <c r="D8" s="13" t="inlineStr">
@@ -16526,7 +22394,7 @@
         </is>
       </c>
       <c r="E8" s="13">
-        <f>COUNTIF('Integration Test Cases'!$M$3:$M$31,"Pass")</f>
+        <f>COUNTIF('Integration Test Cases'!$M$3:$M$34,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -16537,7 +22405,7 @@
         </is>
       </c>
       <c r="B9" s="13">
-        <f>COUNTIF('UI Test Cases'!$M$3:$M$114,"Fail")</f>
+        <f>COUNTIF('UI Test Cases'!$M$3:$M$177,"Fail")</f>
         <v/>
       </c>
       <c r="D9" s="13" t="inlineStr">
@@ -16546,7 +22414,7 @@
         </is>
       </c>
       <c r="E9" s="13">
-        <f>COUNTIF('Integration Test Cases'!$M$3:$M$31,"Fail")</f>
+        <f>COUNTIF('Integration Test Cases'!$M$3:$M$34,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -16557,7 +22425,7 @@
         </is>
       </c>
       <c r="B10" s="13">
-        <f>COUNTIF('UI Test Cases'!$M$3:$M$114,"Blocked")</f>
+        <f>COUNTIF('UI Test Cases'!$M$3:$M$177,"Blocked")</f>
         <v/>
       </c>
       <c r="D10" s="13" t="inlineStr">
@@ -16566,7 +22434,7 @@
         </is>
       </c>
       <c r="E10" s="13">
-        <f>COUNTIF('Integration Test Cases'!$M$3:$M$31,"Blocked")</f>
+        <f>COUNTIF('Integration Test Cases'!$M$3:$M$34,"Blocked")</f>
         <v/>
       </c>
     </row>
@@ -16577,7 +22445,7 @@
         </is>
       </c>
       <c r="B11" s="13">
-        <f>COUNTIF('UI Test Cases'!$M$3:$M$114,"N/A")</f>
+        <f>COUNTIF('UI Test Cases'!$M$3:$M$177,"N/A")</f>
         <v/>
       </c>
       <c r="D11" s="13" t="inlineStr">
@@ -16586,7 +22454,7 @@
         </is>
       </c>
       <c r="E11" s="13">
-        <f>COUNTIF('Integration Test Cases'!$M$3:$M$31,"N/A")</f>
+        <f>COUNTIF('Integration Test Cases'!$M$3:$M$34,"N/A")</f>
         <v/>
       </c>
     </row>
@@ -16597,7 +22465,7 @@
         </is>
       </c>
       <c r="B12" s="13">
-        <f>COUNTIF('UI Test Cases'!$M$3:$M$114,"Not Run")</f>
+        <f>COUNTIF('UI Test Cases'!$M$3:$M$177,"Not Run")</f>
         <v/>
       </c>
       <c r="D12" s="13" t="inlineStr">
@@ -16606,7 +22474,7 @@
         </is>
       </c>
       <c r="E12" s="13">
-        <f>COUNTIF('Integration Test Cases'!$M$3:$M$31,"Not Run")</f>
+        <f>COUNTIF('Integration Test Cases'!$M$3:$M$34,"Not Run")</f>
         <v/>
       </c>
     </row>
@@ -16637,7 +22505,7 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTA('UI Test Scenarios'!$B$3:$B$70)</f>
+        <f>COUNTA('UI Test Scenarios'!$B$3:$B$85)</f>
         <v/>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -16646,7 +22514,7 @@
         </is>
       </c>
       <c r="E14" s="13">
-        <f>COUNTA('Integration Test Scenarios'!$B$3:$B$22)</f>
+        <f>COUNTA('Integration Test Scenarios'!$B$3:$B$24)</f>
         <v/>
       </c>
     </row>
@@ -16657,7 +22525,7 @@
         </is>
       </c>
       <c r="B15" s="13">
-        <f>COUNTA('UI Test Cases'!$A$3:$A$114)</f>
+        <f>COUNTA('UI Test Cases'!$A$3:$A$177)</f>
         <v/>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -16666,7 +22534,7 @@
         </is>
       </c>
       <c r="E15" s="13">
-        <f>COUNTA('Integration Test Cases'!$A$3:$A$31)</f>
+        <f>COUNTA('Integration Test Cases'!$A$3:$A$34)</f>
         <v/>
       </c>
     </row>
@@ -16677,7 +22545,7 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIF('UI Test Cases'!$P$3:$P$114,"QnA*")</f>
+        <f>COUNTIF('UI Test Cases'!$P$3:$P$177,"QnA*")</f>
         <v/>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -16686,10 +22554,11 @@
         </is>
       </c>
       <c r="E16" s="13">
-        <f>COUNTIF('Integration Test Cases'!$P$3:$P$31,"QnA*")</f>
+        <f>COUNTIF('Integration Test Cases'!$P$3:$P$34,"QnA*")</f>
         <v/>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
@@ -16704,7 +22573,7 @@
         </is>
       </c>
       <c r="B19" s="13">
-        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$70,"A. Search Bar &amp; Pre-search")</f>
+        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$85,"A. Search Bar &amp; Pre-search")</f>
         <v/>
       </c>
     </row>
@@ -16715,7 +22584,7 @@
         </is>
       </c>
       <c r="B20" s="13">
-        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$70,"B. Autocomplete")</f>
+        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$85,"B. Autocomplete")</f>
         <v/>
       </c>
     </row>
@@ -16726,7 +22595,7 @@
         </is>
       </c>
       <c r="B21" s="13">
-        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$70,"C. Auto-Correct Banner")</f>
+        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$85,"C. Auto-Correct Banner")</f>
         <v/>
       </c>
     </row>
@@ -16737,7 +22606,7 @@
         </is>
       </c>
       <c r="B22" s="13">
-        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$70,"D. Search Processing / Loading")</f>
+        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$85,"D. Search Processing / Loading")</f>
         <v/>
       </c>
     </row>
@@ -16748,7 +22617,7 @@
         </is>
       </c>
       <c r="B23" s="13">
-        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$70,"E. Search Results — Grid")</f>
+        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$85,"E. Search Results — Grid")</f>
         <v/>
       </c>
     </row>
@@ -16759,7 +22628,7 @@
         </is>
       </c>
       <c r="B24" s="13">
-        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$70,"F. Search Results — List")</f>
+        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$85,"F. Search Results — List")</f>
         <v/>
       </c>
     </row>
@@ -16770,7 +22639,7 @@
         </is>
       </c>
       <c r="B25" s="13">
-        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$70,"G. Sort")</f>
+        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$85,"G. Sort")</f>
         <v/>
       </c>
     </row>
@@ -16781,7 +22650,7 @@
         </is>
       </c>
       <c r="B26" s="13">
-        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$70,"H. Smart Filter / Detailed Filter")</f>
+        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$85,"H. Smart Filter / Detailed Filter")</f>
         <v/>
       </c>
     </row>
@@ -16792,7 +22661,7 @@
         </is>
       </c>
       <c r="B27" s="13">
-        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$70,"I. Filter Applied State")</f>
+        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$85,"I. Filter Applied State")</f>
         <v/>
       </c>
     </row>
@@ -16803,7 +22672,7 @@
         </is>
       </c>
       <c r="B28" s="13">
-        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$70,"J. Add to Cart")</f>
+        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$85,"J. Add to Cart")</f>
         <v/>
       </c>
     </row>
@@ -16814,7 +22683,7 @@
         </is>
       </c>
       <c r="B29" s="13">
-        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$70,"K. Zero-Result Recovery")</f>
+        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$85,"K. Zero-Result Recovery")</f>
         <v/>
       </c>
     </row>
@@ -16825,7 +22694,7 @@
         </is>
       </c>
       <c r="B30" s="13">
-        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$70,"L. Image Search — Camera")</f>
+        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$85,"L. Image Search — Camera")</f>
         <v/>
       </c>
     </row>
@@ -16836,7 +22705,7 @@
         </is>
       </c>
       <c r="B31" s="13">
-        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$70,"M. Image Search — Gallery")</f>
+        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$85,"M. Image Search — Gallery")</f>
         <v/>
       </c>
     </row>
@@ -16847,7 +22716,7 @@
         </is>
       </c>
       <c r="B32" s="13">
-        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$70,"N. Image Search — Recognition Result")</f>
+        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$85,"N. Image Search — Recognition Result")</f>
         <v/>
       </c>
     </row>
@@ -16858,7 +22727,7 @@
         </is>
       </c>
       <c r="B33" s="13">
-        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$70,"O. Image Search — Fail")</f>
+        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$85,"O. Image Search — Fail")</f>
         <v/>
       </c>
     </row>
@@ -16869,7 +22738,7 @@
         </is>
       </c>
       <c r="B34" s="13">
-        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$70,"P. Voice Search — Listening")</f>
+        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$85,"P. Voice Search — Listening")</f>
         <v/>
       </c>
     </row>
@@ -16880,7 +22749,7 @@
         </is>
       </c>
       <c r="B35" s="13">
-        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$70,"Q. Voice Search — Result")</f>
+        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$85,"Q. Voice Search — Result")</f>
         <v/>
       </c>
     </row>
@@ -16891,7 +22760,7 @@
         </is>
       </c>
       <c r="B36" s="13">
-        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$70,"R. Voice Search — Fail")</f>
+        <f>COUNTIF('UI Test Scenarios'!$D$3:$D$85,"R. Voice Search — Fail")</f>
         <v/>
       </c>
     </row>
@@ -16906,6 +22775,7 @@
         <v/>
       </c>
     </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
@@ -16920,7 +22790,7 @@
         </is>
       </c>
       <c r="B40" s="13">
-        <f>COUNTIF('Integration Test Scenarios'!$C$3:$C$22,"Công cụ xếp hạng tìm kiếm (Search Ranking Engine)")</f>
+        <f>COUNTIF('Integration Test Scenarios'!$C$3:$C$24,"Công cụ xếp hạng tìm kiếm (Search Ranking Engine)")</f>
         <v/>
       </c>
     </row>
@@ -16931,7 +22801,7 @@
         </is>
       </c>
       <c r="B41" s="13">
-        <f>COUNTIF('Integration Test Scenarios'!$C$3:$C$22,"Hiểu truy vấn — Đồng nghĩa &amp; Đa ngôn ngữ (Query Understanding)")</f>
+        <f>COUNTIF('Integration Test Scenarios'!$C$3:$C$24,"Hiểu truy vấn — Đồng nghĩa &amp; Đa ngôn ngữ (Query Understanding)")</f>
         <v/>
       </c>
     </row>
@@ -16942,7 +22812,7 @@
         </is>
       </c>
       <c r="B42" s="13">
-        <f>COUNTIF('Integration Test Scenarios'!$C$3:$C$22,"Autocomplete &amp; Sửa lỗi chính tả — Backend")</f>
+        <f>COUNTIF('Integration Test Scenarios'!$C$3:$C$24,"Autocomplete &amp; Sửa lỗi chính tả — Backend")</f>
         <v/>
       </c>
     </row>
@@ -16953,7 +22823,7 @@
         </is>
       </c>
       <c r="B43" s="13">
-        <f>COUNTIF('Integration Test Scenarios'!$C$3:$C$22,"Cá nhân hoá — Tích hợp OMS (Order History)")</f>
+        <f>COUNTIF('Integration Test Scenarios'!$C$3:$C$24,"Cá nhân hoá — Tích hợp OMS (Order History)")</f>
         <v/>
       </c>
     </row>
@@ -16964,7 +22834,7 @@
         </is>
       </c>
       <c r="B44" s="13">
-        <f>COUNTIF('Integration Test Scenarios'!$C$3:$C$22,"Sponsored Ads — Tích hợp Retail Media")</f>
+        <f>COUNTIF('Integration Test Scenarios'!$C$3:$C$24,"Sponsored Ads — Tích hợp Retail Media")</f>
         <v/>
       </c>
     </row>
@@ -16975,7 +22845,7 @@
         </is>
       </c>
       <c r="B45" s="13">
-        <f>COUNTIF('Integration Test Scenarios'!$C$3:$C$22,"Tìm bằng ảnh — Tích hợp Computer Vision Service")</f>
+        <f>COUNTIF('Integration Test Scenarios'!$C$3:$C$24,"Tìm bằng ảnh — Tích hợp Computer Vision Service")</f>
         <v/>
       </c>
     </row>
@@ -16986,7 +22856,7 @@
         </is>
       </c>
       <c r="B46" s="13">
-        <f>COUNTIF('Integration Test Scenarios'!$C$3:$C$22,"Tìm bằng giọng nói — Tích hợp Speech-to-Text Service")</f>
+        <f>COUNTIF('Integration Test Scenarios'!$C$3:$C$24,"Tìm bằng giọng nói — Tích hợp Speech-to-Text Service")</f>
         <v/>
       </c>
     </row>
@@ -16997,7 +22867,7 @@
         </is>
       </c>
       <c r="B47" s="13">
-        <f>COUNTIF('Integration Test Scenarios'!$C$3:$C$22,"Thêm giỏ hàng — Tích hợp Cart/OMS Transactional")</f>
+        <f>COUNTIF('Integration Test Scenarios'!$C$3:$C$24,"Thêm giỏ hàng — Tích hợp Cart/OMS Transactional")</f>
         <v/>
       </c>
     </row>
@@ -17008,7 +22878,7 @@
         </is>
       </c>
       <c r="B48" s="13">
-        <f>COUNTIF('Integration Test Scenarios'!$C$3:$C$22,"Catalog &amp; Inventory — Đồng bộ tồn kho thời gian thực")</f>
+        <f>COUNTIF('Integration Test Scenarios'!$C$3:$C$24,"Catalog &amp; Inventory — Đồng bộ tồn kho thời gian thực")</f>
         <v/>
       </c>
     </row>
@@ -17019,7 +22889,7 @@
         </is>
       </c>
       <c r="B49" s="13">
-        <f>COUNTIF('Integration Test Scenarios'!$C$3:$C$22,"Zero-Result Fallback Engine — Thuật toán gợi ý thay thế")</f>
+        <f>COUNTIF('Integration Test Scenarios'!$C$3:$C$24,"Zero-Result Fallback Engine — Thuật toán gợi ý thay thế")</f>
         <v/>
       </c>
     </row>
@@ -17030,7 +22900,7 @@
         </is>
       </c>
       <c r="B50" s="13">
-        <f>COUNTIF('Integration Test Scenarios'!$C$3:$C$22,"Auth &amp; Session — Guest vs Member")</f>
+        <f>COUNTIF('Integration Test Scenarios'!$C$3:$C$24,"Auth &amp; Session — Guest vs Member")</f>
         <v/>
       </c>
     </row>
@@ -17041,7 +22911,7 @@
         </is>
       </c>
       <c r="B51" s="13">
-        <f>COUNTIF('Integration Test Scenarios'!$C$3:$C$22,"Analytics &amp; Event Logging")</f>
+        <f>COUNTIF('Integration Test Scenarios'!$C$3:$C$24,"Analytics &amp; Event Logging")</f>
         <v/>
       </c>
     </row>
@@ -17052,7 +22922,7 @@
         </is>
       </c>
       <c r="B52" s="13">
-        <f>COUNTIF('Integration Test Scenarios'!$C$3:$C$22,"Hiệu năng &amp; Khả năng chịu tải (Performance/NFR)")</f>
+        <f>COUNTIF('Integration Test Scenarios'!$C$3:$C$24,"Hiệu năng &amp; Khả năng chịu tải (Performance/NFR)")</f>
         <v/>
       </c>
     </row>
@@ -17063,7 +22933,7 @@
         </is>
       </c>
       <c r="B53" s="13">
-        <f>COUNTIF('Integration Test Scenarios'!$C$3:$C$22,"Bảo mật &amp; Quyền riêng tư dữ liệu (Security/PDPL)")</f>
+        <f>COUNTIF('Integration Test Scenarios'!$C$3:$C$24,"Bảo mật &amp; Quyền riêng tư dữ liệu (Security/PDPL)")</f>
         <v/>
       </c>
     </row>
@@ -17078,6 +22948,7 @@
         <v/>
       </c>
     </row>
+    <row r="55"/>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
@@ -17092,7 +22963,7 @@
         </is>
       </c>
       <c r="B57" s="13">
-        <f>COUNTIF('UI Test Cases'!$E$3:$E$114,"Normal")</f>
+        <f>COUNTIF('UI Test Cases'!$E$3:$E$177,"Normal")</f>
         <v/>
       </c>
     </row>
@@ -17103,7 +22974,7 @@
         </is>
       </c>
       <c r="B58" s="13">
-        <f>COUNTIF('UI Test Cases'!$E$3:$E$114,"Functional")</f>
+        <f>COUNTIF('UI Test Cases'!$E$3:$E$177,"Functional")</f>
         <v/>
       </c>
     </row>
@@ -17114,7 +22985,7 @@
         </is>
       </c>
       <c r="B59" s="13">
-        <f>COUNTIF('UI Test Cases'!$E$3:$E$114,"Validation")</f>
+        <f>COUNTIF('UI Test Cases'!$E$3:$E$177,"Validation")</f>
         <v/>
       </c>
     </row>
@@ -17125,7 +22996,7 @@
         </is>
       </c>
       <c r="B60" s="13">
-        <f>COUNTIF('UI Test Cases'!$E$3:$E$114,"Negative")</f>
+        <f>COUNTIF('UI Test Cases'!$E$3:$E$177,"Negative")</f>
         <v/>
       </c>
     </row>
@@ -17136,7 +23007,7 @@
         </is>
       </c>
       <c r="B61" s="13">
-        <f>COUNTIF('UI Test Cases'!$E$3:$E$114,"Boundary")</f>
+        <f>COUNTIF('UI Test Cases'!$E$3:$E$177,"Boundary")</f>
         <v/>
       </c>
     </row>
@@ -17147,7 +23018,7 @@
         </is>
       </c>
       <c r="B62" s="13">
-        <f>COUNTIF('UI Test Cases'!$E$3:$E$114,"Edge")</f>
+        <f>COUNTIF('UI Test Cases'!$E$3:$E$177,"Edge")</f>
         <v/>
       </c>
     </row>
@@ -17158,7 +23029,7 @@
         </is>
       </c>
       <c r="B63" s="13">
-        <f>COUNTIF('UI Test Cases'!$E$3:$E$114,"Exception")</f>
+        <f>COUNTIF('UI Test Cases'!$E$3:$E$177,"Exception")</f>
         <v/>
       </c>
     </row>
@@ -17169,7 +23040,7 @@
         </is>
       </c>
       <c r="B64" s="13">
-        <f>COUNTIF('UI Test Cases'!$E$3:$E$114,"Integration")</f>
+        <f>COUNTIF('UI Test Cases'!$E$3:$E$177,"Integration")</f>
         <v/>
       </c>
     </row>
@@ -17180,7 +23051,7 @@
         </is>
       </c>
       <c r="B65" s="13">
-        <f>COUNTIF('UI Test Cases'!$E$3:$E$114,"Performance")</f>
+        <f>COUNTIF('UI Test Cases'!$E$3:$E$177,"Performance")</f>
         <v/>
       </c>
     </row>
@@ -17191,7 +23062,7 @@
         </is>
       </c>
       <c r="B66" s="13">
-        <f>COUNTIF('UI Test Cases'!$E$3:$E$114,"Sponsored")</f>
+        <f>COUNTIF('UI Test Cases'!$E$3:$E$177,"Sponsored")</f>
         <v/>
       </c>
     </row>
@@ -17202,7 +23073,7 @@
         </is>
       </c>
       <c r="B67" s="13">
-        <f>COUNTIF('UI Test Cases'!$E$3:$E$114,"Ranking")</f>
+        <f>COUNTIF('UI Test Cases'!$E$3:$E$177,"Ranking")</f>
         <v/>
       </c>
     </row>
@@ -17213,7 +23084,7 @@
         </is>
       </c>
       <c r="B68" s="13">
-        <f>COUNTIF('UI Test Cases'!$E$3:$E$114,"No-result")</f>
+        <f>COUNTIF('UI Test Cases'!$E$3:$E$177,"No-result")</f>
         <v/>
       </c>
     </row>
@@ -17224,7 +23095,7 @@
         </is>
       </c>
       <c r="B69" s="13">
-        <f>COUNTIF('UI Test Cases'!$E$3:$E$114,"Typo")</f>
+        <f>COUNTIF('UI Test Cases'!$E$3:$E$177,"Typo")</f>
         <v/>
       </c>
     </row>
@@ -17235,7 +23106,7 @@
         </is>
       </c>
       <c r="B70" s="13">
-        <f>COUNTIF('UI Test Cases'!$E$3:$E$114,"Sort")</f>
+        <f>COUNTIF('UI Test Cases'!$E$3:$E$177,"Sort")</f>
         <v/>
       </c>
     </row>
@@ -17246,7 +23117,7 @@
         </is>
       </c>
       <c r="B71" s="13">
-        <f>COUNTIF('UI Test Cases'!$E$3:$E$114,"Filter")</f>
+        <f>COUNTIF('UI Test Cases'!$E$3:$E$177,"Filter")</f>
         <v/>
       </c>
     </row>
@@ -17261,6 +23132,7 @@
         <v/>
       </c>
     </row>
+    <row r="73"/>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
@@ -17275,7 +23147,7 @@
         </is>
       </c>
       <c r="B75" s="13">
-        <f>COUNTIF('Integration Test Cases'!$E$3:$E$31,"Functional")</f>
+        <f>COUNTIF('Integration Test Cases'!$E$3:$E$34,"Functional")</f>
         <v/>
       </c>
     </row>
@@ -17286,7 +23158,7 @@
         </is>
       </c>
       <c r="B76" s="13">
-        <f>COUNTIF('Integration Test Cases'!$E$3:$E$31,"Behavior")</f>
+        <f>COUNTIF('Integration Test Cases'!$E$3:$E$34,"Behavior")</f>
         <v/>
       </c>
     </row>
@@ -17297,7 +23169,7 @@
         </is>
       </c>
       <c r="B77" s="13">
-        <f>COUNTIF('Integration Test Cases'!$E$3:$E$31,"Integration")</f>
+        <f>COUNTIF('Integration Test Cases'!$E$3:$E$34,"Integration")</f>
         <v/>
       </c>
     </row>
@@ -17308,7 +23180,7 @@
         </is>
       </c>
       <c r="B78" s="13">
-        <f>COUNTIF('Integration Test Cases'!$E$3:$E$31,"Boundary")</f>
+        <f>COUNTIF('Integration Test Cases'!$E$3:$E$34,"Boundary")</f>
         <v/>
       </c>
     </row>
@@ -17319,7 +23191,7 @@
         </is>
       </c>
       <c r="B79" s="13">
-        <f>COUNTIF('Integration Test Cases'!$E$3:$E$31,"Negative")</f>
+        <f>COUNTIF('Integration Test Cases'!$E$3:$E$34,"Negative")</f>
         <v/>
       </c>
     </row>
@@ -17330,7 +23202,7 @@
         </is>
       </c>
       <c r="B80" s="13">
-        <f>COUNTIF('Integration Test Cases'!$E$3:$E$31,"Performance")</f>
+        <f>COUNTIF('Integration Test Cases'!$E$3:$E$34,"Performance")</f>
         <v/>
       </c>
     </row>
@@ -17341,7 +23213,7 @@
         </is>
       </c>
       <c r="B81" s="13">
-        <f>COUNTIF('Integration Test Cases'!$E$3:$E$31,"Security")</f>
+        <f>COUNTIF('Integration Test Cases'!$E$3:$E$34,"Security")</f>
         <v/>
       </c>
     </row>
